--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1252A0E-3AB3-405B-9A82-0A146441D87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9348043F-8E29-4F3B-ACF8-2A7B285F7691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -175,7 +175,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -333,13 +333,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1">
@@ -348,7 +348,7 @@
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1">
@@ -806,7 +806,9 @@
         <v>1145</v>
       </c>
       <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="J2" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -840,7 +842,9 @@
         <v>1145</v>
       </c>
       <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="J3" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="K3" s="4" t="s">
         <v>29</v>
       </c>
@@ -876,7 +880,9 @@
       <c r="I4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="K4" s="4" t="s">
         <v>29</v>
       </c>
@@ -910,7 +916,9 @@
         <v>1145</v>
       </c>
       <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="J5" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="K5" s="4" t="s">
         <v>30</v>
       </c>
@@ -944,7 +952,9 @@
         <v>1145</v>
       </c>
       <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="J6" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="K6" s="4" t="s">
         <v>30</v>
       </c>
@@ -978,7 +988,9 @@
         <v>1145</v>
       </c>
       <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
+      <c r="J7" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="K7" s="4" t="s">
         <v>30</v>
       </c>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9348043F-8E29-4F3B-ACF8-2A7B285F7691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A08CF95-D9BE-4052-B53D-389BAE3DA098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料頁" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$BA$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$BB$1</definedName>
     <definedName name="全健康保險費" localSheetId="0">資料頁!$H$2:$H$10</definedName>
     <definedName name="序號" localSheetId="0">資料頁!$A$2:$A$10</definedName>
     <definedName name="投保薪額">資料頁!$E$2:$E$10</definedName>
@@ -41,15 +41,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -150,10 +147,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>業務承辦人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>a001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -167,6 +160,26 @@
   </si>
   <si>
     <t>投保薪額</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>業務承辦人姓名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>業務承辦人證號</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林小明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>王小花</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳小美</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -175,7 +188,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -313,33 +326,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1">
@@ -348,13 +361,13 @@
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -395,9 +408,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -435,9 +448,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -470,26 +483,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -522,26 +518,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -718,31 +697,32 @@
   <sheetPr codeName="工作表2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="10.5" style="4" customWidth="1"/>
-    <col min="15" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="17.75" style="4" customWidth="1"/>
-    <col min="20" max="23" width="9" style="4" customWidth="1"/>
-    <col min="24" max="24" width="16.375" style="4" customWidth="1"/>
-    <col min="25" max="53" width="9" style="4" customWidth="1"/>
-    <col min="54" max="16384" width="9" style="4"/>
+    <col min="11" max="11" width="17.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="59.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" style="4" customWidth="1"/>
+    <col min="16" max="19" width="9" style="4" customWidth="1"/>
+    <col min="20" max="20" width="17.77734375" style="4" customWidth="1"/>
+    <col min="21" max="24" width="9" style="4" customWidth="1"/>
+    <col min="25" max="25" width="16.33203125" style="4" customWidth="1"/>
+    <col min="26" max="54" width="9" style="4" customWidth="1"/>
+    <col min="55" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -756,7 +736,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>12</v>
@@ -774,13 +754,16 @@
         <v>1</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -806,17 +789,18 @@
         <v>1145</v>
       </c>
       <c r="I2" s="14"/>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="14"/>
+      <c r="K2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -842,17 +826,18 @@
         <v>1145</v>
       </c>
       <c r="I3" s="14"/>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="14"/>
+      <c r="K3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -880,17 +865,18 @@
       <c r="I4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="14"/>
+      <c r="K4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -916,17 +902,18 @@
         <v>1145</v>
       </c>
       <c r="I5" s="14"/>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="14"/>
+      <c r="K5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -952,17 +939,18 @@
         <v>1145</v>
       </c>
       <c r="I6" s="14"/>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="14"/>
+      <c r="K6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -988,17 +976,18 @@
         <v>1145</v>
       </c>
       <c r="I7" s="14"/>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="14"/>
+      <c r="K7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1026,13 +1015,16 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1062,13 +1054,16 @@
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1096,15 +1091,41 @@
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="10" t="s">
         <v>10</v>
       </c>
+    </row>
+    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="15"/>
+    </row>
+    <row r="12" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="15"/>
+    </row>
+    <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="15"/>
+    </row>
+    <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="15"/>
+    </row>
+    <row r="17" spans="4:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="15"/>
+    </row>
+    <row r="18" spans="4:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="15"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <autoFilter ref="A1:BA1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1AD115-302D-4999-BB75-302AF6964CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34932D26-1ECA-4181-BFFC-E333B602AA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="114">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -425,6 +425,10 @@
     <t>嚴麟,測試</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>4040,1234</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -600,7 +604,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8117,8 +8121,8 @@
       <c r="H199" s="1">
         <v>2565</v>
       </c>
-      <c r="K199" s="15">
-        <v>40401234</v>
+      <c r="K199" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="L199" s="8" t="s">
         <v>112</v>
@@ -8152,8 +8156,8 @@
       <c r="H200" s="1">
         <v>2216</v>
       </c>
-      <c r="K200" s="15">
-        <v>40401234</v>
+      <c r="K200" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="L200" s="8" t="s">
         <v>112</v>
@@ -8187,8 +8191,8 @@
       <c r="H201" s="1">
         <v>2032</v>
       </c>
-      <c r="K201" s="15">
-        <v>40401234</v>
+      <c r="K201" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="L201" s="8" t="s">
         <v>112</v>
@@ -8222,8 +8226,8 @@
       <c r="H202" s="1">
         <v>2216</v>
       </c>
-      <c r="K202" s="15">
-        <v>40401234</v>
+      <c r="K202" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="L202" s="8" t="s">
         <v>112</v>
@@ -8257,8 +8261,8 @@
       <c r="H203" s="1">
         <v>2216</v>
       </c>
-      <c r="K203" s="15">
-        <v>40401234</v>
+      <c r="K203" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="L203" s="8" t="s">
         <v>112</v>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34932D26-1ECA-4181-BFFC-E333B602AA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5A01D89-AE14-4CC0-8567-593A00BA4440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4092" yWindow="2604" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料頁" sheetId="1" r:id="rId1"/>
@@ -41,15 +41,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="112">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -248,9 +245,6 @@
     <t>加/退</t>
   </si>
   <si>
-    <t>10/1薪調</t>
-  </si>
-  <si>
     <t>教育部_技專校院高等教育深耕計畫附錄2原資中心</t>
   </si>
   <si>
@@ -269,16 +263,7 @@
     <t>經濟部_AI新秀計畫培訓補助計畫</t>
   </si>
   <si>
-    <t>1150223離職退保</t>
-  </si>
-  <si>
-    <t>1150228離職退保</t>
-  </si>
-  <si>
     <t>1150316離職</t>
-  </si>
-  <si>
-    <t>1150430離職退保</t>
   </si>
   <si>
     <t>1150515離職</t>
@@ -410,10 +395,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1150630離職退保</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>退保</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -429,6 +410,18 @@
     <t>4040,1234</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>1150630離職</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1150430離職</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1150223離職</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -437,7 +430,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -642,9 +635,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -682,9 +675,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -717,26 +710,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -769,26 +745,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -966,31 +925,31 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:M295"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="59.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="59.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" style="1" customWidth="1"/>
     <col min="16" max="19" width="9" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.75" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.77734375" style="1" customWidth="1"/>
     <col min="21" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="16.375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="16.33203125" style="1" customWidth="1"/>
     <col min="26" max="54" width="9" style="1" customWidth="1"/>
     <col min="55" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="11" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="11" customFormat="1" ht="39" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
@@ -1031,12 +990,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="17.25" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
@@ -1070,12 +1029,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="17.25" customHeight="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -1109,12 +1068,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="17.25" customHeight="1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
@@ -1145,12 +1104,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="17.25" customHeight="1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -1184,12 +1143,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="17.25" customHeight="1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
@@ -1223,12 +1182,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="17.25" customHeight="1">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>25</v>
@@ -1262,12 +1221,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="17.25" customHeight="1">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>26</v>
@@ -1299,12 +1258,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="17.25" customHeight="1">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
@@ -1335,12 +1294,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="17.25" customHeight="1">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -1374,12 +1333,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="17.25" customHeight="1">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>27</v>
@@ -1412,12 +1371,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="17.25" customHeight="1">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>28</v>
@@ -1450,12 +1409,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="17.25" customHeight="1">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>29</v>
@@ -1485,12 +1444,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="17.25" customHeight="1">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>30</v>
@@ -1517,15 +1476,15 @@
         <v>32</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="17.25" customHeight="1">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>31</v>
@@ -1555,15 +1514,15 @@
         <v>32</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="17.25" customHeight="1">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>32</v>
@@ -1590,15 +1549,15 @@
         <v>32</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="17.25" customHeight="1">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>33</v>
@@ -1625,15 +1584,15 @@
         <v>33</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="17.25" customHeight="1">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>34</v>
@@ -1663,15 +1622,15 @@
         <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="17.25" customHeight="1">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>35</v>
@@ -1701,15 +1660,15 @@
         <v>50</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="17.25" customHeight="1">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>36</v>
@@ -1739,15 +1698,15 @@
         <v>50</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="17.25" customHeight="1">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>37</v>
@@ -1777,15 +1736,15 @@
         <v>50</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="17.25" customHeight="1">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>38</v>
@@ -1815,15 +1774,15 @@
         <v>50</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="17.25" customHeight="1">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>39</v>
@@ -1850,15 +1809,15 @@
         <v>50</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="17.25" customHeight="1">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>40</v>
@@ -1885,15 +1844,15 @@
         <v>50</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="17.25" customHeight="1">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>41</v>
@@ -1920,15 +1879,15 @@
         <v>50</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="17.25" customHeight="1">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>42</v>
@@ -1958,15 +1917,15 @@
         <v>50</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="17.25" customHeight="1">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>43</v>
@@ -1993,15 +1952,15 @@
         <v>50</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="17.25" customHeight="1">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>44</v>
@@ -2009,6 +1968,9 @@
       <c r="D28" s="8">
         <v>11501</v>
       </c>
+      <c r="E28" s="8">
+        <v>38200</v>
+      </c>
       <c r="F28" s="8">
         <v>2033</v>
       </c>
@@ -2022,7 +1984,7 @@
         <v>58</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K28">
         <v>7015</v>
@@ -2031,15 +1993,15 @@
         <v>50</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="17.25" customHeight="1">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>45</v>
@@ -2066,15 +2028,15 @@
         <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="17.25" customHeight="1">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>46</v>
@@ -2095,21 +2057,21 @@
         <v>1757</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="17.25" customHeight="1">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>47</v>
@@ -2139,15 +2101,15 @@
         <v>47</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="17.25" customHeight="1">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>48</v>
@@ -2174,15 +2136,15 @@
         <v>48</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="17.25" customHeight="1">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>13</v>
@@ -2212,12 +2174,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="17.25" customHeight="1">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>14</v>
@@ -2247,12 +2209,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="17.25" customHeight="1">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>15</v>
@@ -2282,12 +2244,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="17.25" customHeight="1">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>16</v>
@@ -2317,12 +2279,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="17.25" customHeight="1">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>17</v>
@@ -2352,12 +2314,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="17.25" customHeight="1">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>25</v>
@@ -2387,12 +2349,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="17.25" customHeight="1">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>26</v>
@@ -2422,12 +2384,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="17.25" customHeight="1">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>19</v>
@@ -2457,12 +2419,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="17.25" customHeight="1">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>20</v>
@@ -2492,12 +2454,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="17.25" customHeight="1">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>27</v>
@@ -2527,12 +2489,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="17.25" customHeight="1">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>28</v>
@@ -2562,12 +2524,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="17.25" customHeight="1">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>29</v>
@@ -2597,12 +2559,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="17.25" customHeight="1">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>30</v>
@@ -2629,15 +2591,15 @@
         <v>32</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="17.25" customHeight="1">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>31</v>
@@ -2664,15 +2626,15 @@
         <v>32</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="17.25" customHeight="1">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>32</v>
@@ -2699,15 +2661,15 @@
         <v>32</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="17.25" customHeight="1">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>33</v>
@@ -2734,15 +2696,15 @@
         <v>33</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="17.25" customHeight="1">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>34</v>
@@ -2769,15 +2731,15 @@
         <v>50</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="17.25" customHeight="1">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>35</v>
@@ -2801,7 +2763,7 @@
         <v>59</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="K50">
         <v>7015</v>
@@ -2810,15 +2772,15 @@
         <v>50</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="17.25" customHeight="1">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>36</v>
@@ -2845,15 +2807,15 @@
         <v>50</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="17.25" customHeight="1">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>37</v>
@@ -2874,10 +2836,10 @@
         <v>1849</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K52">
         <v>7015</v>
@@ -2886,15 +2848,15 @@
         <v>50</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="17.25" customHeight="1">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>49</v>
@@ -2918,7 +2880,7 @@
         <v>58</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K53">
         <v>7015</v>
@@ -2927,15 +2889,15 @@
         <v>50</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="17.25" customHeight="1">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>38</v>
@@ -2962,15 +2924,15 @@
         <v>50</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="17.25" customHeight="1">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>39</v>
@@ -2997,15 +2959,15 @@
         <v>50</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="17.25" customHeight="1">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>40</v>
@@ -3032,15 +2994,15 @@
         <v>50</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="17.25" customHeight="1">
       <c r="A57" s="1">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>41</v>
@@ -3064,7 +3026,7 @@
         <v>59</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="K57">
         <v>7015</v>
@@ -3073,15 +3035,15 @@
         <v>50</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="17.25" customHeight="1">
       <c r="A58" s="1">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>42</v>
@@ -3108,15 +3070,15 @@
         <v>50</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="17.25" customHeight="1">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>43</v>
@@ -3143,15 +3105,15 @@
         <v>50</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="17.25" customHeight="1">
       <c r="A60" s="1">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>44</v>
@@ -3178,15 +3140,15 @@
         <v>50</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="17.25" customHeight="1">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="e">
-        <v>#N/A</v>
+      <c r="B61" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>50</v>
@@ -3194,6 +3156,9 @@
       <c r="D61" s="8">
         <v>11502</v>
       </c>
+      <c r="E61" s="8">
+        <v>38200</v>
+      </c>
       <c r="F61" s="8">
         <v>2372</v>
       </c>
@@ -3207,7 +3172,7 @@
         <v>58</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K61">
         <v>7015</v>
@@ -3216,15 +3181,15 @@
         <v>50</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="17.25" customHeight="1">
       <c r="A62" s="1">
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>45</v>
@@ -3251,15 +3216,15 @@
         <v>45</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="17.25" customHeight="1">
       <c r="A63" s="1">
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>46</v>
@@ -3280,21 +3245,21 @@
         <v>1757</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="17.25" customHeight="1">
       <c r="A64" s="1">
         <v>64</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>47</v>
@@ -3321,15 +3286,15 @@
         <v>47</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="17.25" customHeight="1">
       <c r="A65" s="1">
         <v>65</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>48</v>
@@ -3356,15 +3321,15 @@
         <v>48</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="17.25" customHeight="1">
       <c r="A66" s="1">
         <v>66</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>13</v>
@@ -3394,12 +3359,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="17.25" customHeight="1">
       <c r="A67" s="1">
         <v>67</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>14</v>
@@ -3429,12 +3394,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="17.25" customHeight="1">
       <c r="A68" s="1">
         <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>15</v>
@@ -3464,12 +3429,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="17.25" customHeight="1">
       <c r="A69" s="1">
         <v>69</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>16</v>
@@ -3499,12 +3464,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="17.25" customHeight="1">
       <c r="A70" s="1">
         <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>17</v>
@@ -3537,12 +3502,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="17.25" customHeight="1">
       <c r="A71" s="1">
         <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>25</v>
@@ -3575,12 +3540,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="17.25" customHeight="1">
       <c r="A72" s="1">
         <v>72</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>26</v>
@@ -3610,12 +3575,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="17.25" customHeight="1">
       <c r="A73" s="1">
         <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>19</v>
@@ -3648,12 +3613,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="17.25" customHeight="1">
       <c r="A74" s="1">
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>20</v>
@@ -3683,12 +3648,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="17.25" customHeight="1">
       <c r="A75" s="1">
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>27</v>
@@ -3718,12 +3683,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="17.25" customHeight="1">
       <c r="A76" s="1">
         <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>28</v>
@@ -3753,12 +3718,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="17.25" customHeight="1">
       <c r="A77" s="1">
         <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>29</v>
@@ -3788,12 +3753,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="17.25" customHeight="1">
       <c r="A78" s="1">
         <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>30</v>
@@ -3820,15 +3785,15 @@
         <v>32</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="17.25" customHeight="1">
       <c r="A79" s="1">
         <v>79</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>31</v>
@@ -3855,15 +3820,15 @@
         <v>32</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="17.25" customHeight="1">
       <c r="A80" s="1">
         <v>80</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>32</v>
@@ -3890,15 +3855,15 @@
         <v>32</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="17.25" customHeight="1">
       <c r="A81" s="1">
         <v>81</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>33</v>
@@ -3922,7 +3887,7 @@
         <v>59</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
@@ -3931,15 +3896,15 @@
         <v>33</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="17.25" customHeight="1">
       <c r="A82" s="1">
         <v>82</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>37</v>
@@ -3947,6 +3912,9 @@
       <c r="D82" s="8">
         <v>11503</v>
       </c>
+      <c r="E82" s="8">
+        <v>36300</v>
+      </c>
       <c r="F82" s="8">
         <v>106</v>
       </c>
@@ -3960,7 +3928,7 @@
         <v>58</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K82">
         <v>1615</v>
@@ -3969,15 +3937,15 @@
         <v>37</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="17.25" customHeight="1">
       <c r="A83" s="1">
         <v>83</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>51</v>
@@ -3985,6 +3953,9 @@
       <c r="D83" s="8">
         <v>11503</v>
       </c>
+      <c r="E83" s="8">
+        <v>38200</v>
+      </c>
       <c r="F83" s="8">
         <v>1695</v>
       </c>
@@ -3998,7 +3969,7 @@
         <v>58</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K83">
         <v>7015</v>
@@ -4007,15 +3978,15 @@
         <v>50</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="17.25" customHeight="1">
       <c r="A84" s="1">
         <v>84</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>34</v>
@@ -4042,15 +4013,15 @@
         <v>50</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="17.25" customHeight="1">
       <c r="A85" s="1">
         <v>85</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>52</v>
@@ -4074,7 +4045,7 @@
         <v>60</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K85">
         <v>7015</v>
@@ -4083,15 +4054,15 @@
         <v>50</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="17.25" customHeight="1">
       <c r="A86" s="1">
         <v>86</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>36</v>
@@ -4118,15 +4089,15 @@
         <v>50</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="17.25" customHeight="1">
       <c r="A87" s="1">
         <v>87</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>53</v>
@@ -4150,7 +4121,7 @@
         <v>58</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K87">
         <v>7015</v>
@@ -4159,15 +4130,15 @@
         <v>50</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="17.25" customHeight="1">
       <c r="A88" s="1">
         <v>88</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>54</v>
@@ -4191,7 +4162,7 @@
         <v>58</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K88">
         <v>7015</v>
@@ -4200,15 +4171,15 @@
         <v>50</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="17.25" customHeight="1">
       <c r="A89" s="1">
         <v>89</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>38</v>
@@ -4235,15 +4206,15 @@
         <v>50</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="17.25" customHeight="1">
       <c r="A90" s="1">
         <v>90</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>39</v>
@@ -4273,15 +4244,15 @@
         <v>50</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="17.25" customHeight="1">
       <c r="A91" s="1">
         <v>91</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>40</v>
@@ -4308,15 +4279,15 @@
         <v>50</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="17.25" customHeight="1">
       <c r="A92" s="1">
         <v>93</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>42</v>
@@ -4343,15 +4314,15 @@
         <v>50</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="17.25" customHeight="1">
       <c r="A93" s="1">
         <v>94</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>43</v>
@@ -4378,15 +4349,15 @@
         <v>50</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="17.25" customHeight="1">
       <c r="A94" s="1">
         <v>95</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>44</v>
@@ -4414,15 +4385,15 @@
         <v>50</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="17.25" customHeight="1">
       <c r="A95" s="1">
         <v>96</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>50</v>
@@ -4449,15 +4420,15 @@
         <v>50</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="17.25" customHeight="1">
       <c r="A96" s="1">
         <v>97</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>45</v>
@@ -4484,15 +4455,15 @@
         <v>45</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="17.25" customHeight="1">
       <c r="A97" s="1">
         <v>98</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>46</v>
@@ -4513,21 +4484,21 @@
         <v>1757</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="17.25" customHeight="1">
       <c r="A98" s="1">
         <v>99</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>47</v>
@@ -4554,15 +4525,15 @@
         <v>47</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="17.25" customHeight="1">
       <c r="A99" s="1">
         <v>100</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>48</v>
@@ -4589,15 +4560,15 @@
         <v>48</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="17.25" customHeight="1">
       <c r="A100" s="1">
         <v>101</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>13</v>
@@ -4627,12 +4598,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="17.25" customHeight="1">
       <c r="A101" s="1">
         <v>102</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>14</v>
@@ -4662,12 +4633,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="17.25" customHeight="1">
       <c r="A102" s="1">
         <v>103</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>15</v>
@@ -4697,12 +4668,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="17.25" customHeight="1">
       <c r="A103" s="1">
         <v>104</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>16</v>
@@ -4732,12 +4703,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="17.25" customHeight="1">
       <c r="A104" s="1">
         <v>105</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>17</v>
@@ -4767,12 +4738,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="17.25" customHeight="1">
       <c r="A105" s="1">
         <v>106</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>25</v>
@@ -4802,12 +4773,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="17.25" customHeight="1">
       <c r="A106" s="1">
         <v>107</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>26</v>
@@ -4837,12 +4808,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="17.25" customHeight="1">
       <c r="A107" s="1">
         <v>108</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>19</v>
@@ -4872,12 +4843,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="17.25" customHeight="1">
       <c r="A108" s="1">
         <v>109</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>20</v>
@@ -4907,12 +4878,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="17.25" customHeight="1">
       <c r="A109" s="1">
         <v>110</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>27</v>
@@ -4942,12 +4913,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="17.25" customHeight="1">
       <c r="A110" s="1">
         <v>111</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>28</v>
@@ -4977,12 +4948,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="17.25" customHeight="1">
       <c r="A111" s="1">
         <v>112</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>29</v>
@@ -5012,12 +4983,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="17.25" customHeight="1">
       <c r="A112" s="1">
         <v>113</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>30</v>
@@ -5044,15 +5015,15 @@
         <v>32</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="17.25" customHeight="1">
       <c r="A113" s="1">
         <v>114</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>31</v>
@@ -5079,15 +5050,15 @@
         <v>32</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="17.25" customHeight="1">
       <c r="A114" s="1">
         <v>115</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>32</v>
@@ -5114,15 +5085,15 @@
         <v>32</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="17.25" customHeight="1">
       <c r="A115" s="1">
         <v>116</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>37</v>
@@ -5149,15 +5120,15 @@
         <v>37</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="17.25" customHeight="1">
       <c r="A116" s="1">
         <v>117</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>51</v>
@@ -5184,15 +5155,15 @@
         <v>50</v>
       </c>
       <c r="M116" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" ht="17.25" customHeight="1">
       <c r="A117" s="1">
         <v>118</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>34</v>
@@ -5216,7 +5187,7 @@
         <v>59</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="K117">
         <v>7015</v>
@@ -5225,15 +5196,15 @@
         <v>50</v>
       </c>
       <c r="M117" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="17.25" customHeight="1">
       <c r="A118" s="1">
         <v>119</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>36</v>
@@ -5260,15 +5231,15 @@
         <v>50</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="17.25" customHeight="1">
       <c r="A119" s="1">
         <v>120</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>53</v>
@@ -5295,15 +5266,15 @@
         <v>50</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="17.25" customHeight="1">
       <c r="A120" s="1">
         <v>121</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>54</v>
@@ -5330,15 +5301,15 @@
         <v>50</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="17.25" customHeight="1">
       <c r="A121" s="1">
         <v>122</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>38</v>
@@ -5365,15 +5336,15 @@
         <v>50</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="17.25" customHeight="1">
       <c r="A122" s="1">
         <v>123</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>39</v>
@@ -5400,15 +5371,15 @@
         <v>50</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" ht="17.25" customHeight="1">
       <c r="A123" s="1">
         <v>124</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>40</v>
@@ -5435,15 +5406,15 @@
         <v>50</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" ht="17.25" customHeight="1">
       <c r="A124" s="1">
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>42</v>
@@ -5470,15 +5441,15 @@
         <v>50</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="17.25" customHeight="1">
       <c r="A125" s="1">
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>43</v>
@@ -5505,15 +5476,15 @@
         <v>50</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" ht="17.25" customHeight="1">
       <c r="A126" s="1">
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>44</v>
@@ -5540,15 +5511,15 @@
         <v>50</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" ht="17.25" customHeight="1">
       <c r="A127" s="1">
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>50</v>
@@ -5575,15 +5546,15 @@
         <v>50</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" ht="17.25" customHeight="1">
       <c r="A128" s="1">
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>45</v>
@@ -5610,15 +5581,15 @@
         <v>45</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="17.25" customHeight="1">
       <c r="A129" s="1">
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>46</v>
@@ -5639,21 +5610,21 @@
         <v>1757</v>
       </c>
       <c r="K129" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="17.25" customHeight="1">
       <c r="A130" s="1">
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>47</v>
@@ -5680,15 +5651,15 @@
         <v>47</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="17.25" customHeight="1">
       <c r="A131" s="1">
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>48</v>
@@ -5715,15 +5686,15 @@
         <v>48</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="17.25" customHeight="1">
       <c r="A132" s="1">
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>13</v>
@@ -5753,12 +5724,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="17.25" customHeight="1">
       <c r="A133" s="1">
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>14</v>
@@ -5788,12 +5759,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="17.25" customHeight="1">
       <c r="A134" s="1">
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>15</v>
@@ -5823,12 +5794,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="17.25" customHeight="1">
       <c r="A135" s="1">
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>16</v>
@@ -5858,12 +5829,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="17.25" customHeight="1">
       <c r="A136" s="1">
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>17</v>
@@ -5893,12 +5864,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="17.25" customHeight="1">
       <c r="A137" s="1">
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>25</v>
@@ -5928,12 +5899,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="17.25" customHeight="1">
       <c r="A138" s="1">
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>26</v>
@@ -5957,7 +5928,7 @@
         <v>59</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K138">
         <v>6262</v>
@@ -5969,12 +5940,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="17.25" customHeight="1">
       <c r="A139" s="1">
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>18</v>
@@ -5998,7 +5969,7 @@
         <v>58</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K139">
         <v>6262</v>
@@ -6010,12 +5981,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="17.25" customHeight="1">
       <c r="A140" s="1">
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>19</v>
@@ -6045,12 +6016,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="17.25" customHeight="1">
       <c r="A141" s="1">
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>20</v>
@@ -6080,12 +6051,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="17.25" customHeight="1">
       <c r="A142" s="1">
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>27</v>
@@ -6118,12 +6089,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="17.25" customHeight="1">
       <c r="A143" s="1">
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>28</v>
@@ -6153,12 +6124,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="17.25" customHeight="1">
       <c r="A144" s="1">
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>29</v>
@@ -6188,12 +6159,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="17.25" customHeight="1">
       <c r="A145" s="1">
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>30</v>
@@ -6220,15 +6191,15 @@
         <v>32</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" ht="17.25" customHeight="1">
       <c r="A146" s="1">
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>31</v>
@@ -6255,15 +6226,15 @@
         <v>32</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" ht="17.25" customHeight="1">
       <c r="A147" s="1">
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>32</v>
@@ -6290,15 +6261,15 @@
         <v>32</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" ht="17.25" customHeight="1">
       <c r="A148" s="1">
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>37</v>
@@ -6325,15 +6296,15 @@
         <v>37</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" ht="17.25" customHeight="1">
       <c r="A149" s="1">
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>51</v>
@@ -6360,15 +6331,15 @@
         <v>50</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="17.25" customHeight="1">
       <c r="A150" s="1">
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>52</v>
@@ -6392,7 +6363,7 @@
         <v>58</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K150">
         <v>7015</v>
@@ -6401,15 +6372,15 @@
         <v>50</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="17.25" customHeight="1">
       <c r="A151" s="1">
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>36</v>
@@ -6436,15 +6407,15 @@
         <v>50</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="17.25" customHeight="1">
       <c r="A152" s="1">
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>53</v>
@@ -6471,15 +6442,15 @@
         <v>50</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="17.25" customHeight="1">
       <c r="A153" s="1">
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>54</v>
@@ -6506,15 +6477,15 @@
         <v>50</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="17.25" customHeight="1">
       <c r="A154" s="1">
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>38</v>
@@ -6541,15 +6512,15 @@
         <v>50</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="17.25" customHeight="1">
       <c r="A155" s="1">
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>39</v>
@@ -6576,15 +6547,15 @@
         <v>50</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="17.25" customHeight="1">
       <c r="A156" s="1">
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>40</v>
@@ -6611,15 +6582,15 @@
         <v>50</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" ht="17.25" customHeight="1">
       <c r="A157" s="1">
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>55</v>
@@ -6643,7 +6614,7 @@
         <v>58</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K157">
         <v>7015</v>
@@ -6652,15 +6623,15 @@
         <v>50</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="17.25" customHeight="1">
       <c r="A158" s="1">
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>42</v>
@@ -6687,15 +6658,15 @@
         <v>50</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="17.25" customHeight="1">
       <c r="A159" s="1">
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>43</v>
@@ -6722,15 +6693,15 @@
         <v>50</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="17.25" customHeight="1">
       <c r="A160" s="1">
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>44</v>
@@ -6757,15 +6728,15 @@
         <v>50</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" ht="17.25" customHeight="1">
       <c r="A161" s="1">
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>50</v>
@@ -6792,15 +6763,15 @@
         <v>50</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="17.25" customHeight="1">
       <c r="A162" s="1">
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>45</v>
@@ -6827,15 +6798,15 @@
         <v>45</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="17.25" customHeight="1">
       <c r="A163" s="1">
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>46</v>
@@ -6856,21 +6827,21 @@
         <v>1757</v>
       </c>
       <c r="K163" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L163" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="17.25" customHeight="1">
       <c r="A164" s="1">
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>47</v>
@@ -6897,15 +6868,15 @@
         <v>47</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="17.25" customHeight="1">
       <c r="A165" s="1">
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>48</v>
@@ -6932,15 +6903,15 @@
         <v>48</v>
       </c>
       <c r="M165" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="17.25" customHeight="1">
       <c r="A166" s="1">
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>13</v>
@@ -6970,12 +6941,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="17.25" customHeight="1">
       <c r="A167" s="1">
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>14</v>
@@ -7005,12 +6976,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="17.25" customHeight="1">
       <c r="A168" s="1">
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>15</v>
@@ -7040,12 +7011,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="17.25" customHeight="1">
       <c r="A169" s="1">
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>16</v>
@@ -7075,12 +7046,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="17.25" customHeight="1">
       <c r="A170" s="1">
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>17</v>
@@ -7110,12 +7081,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" ht="17.25" customHeight="1">
       <c r="A171" s="1">
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>25</v>
@@ -7145,12 +7116,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" ht="17.25" customHeight="1">
       <c r="A172" s="1">
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>18</v>
@@ -7180,12 +7151,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" ht="17.25" customHeight="1">
       <c r="A173" s="1">
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>19</v>
@@ -7215,12 +7186,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" ht="17.25" customHeight="1">
       <c r="A174" s="1">
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>20</v>
@@ -7250,12 +7221,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" ht="17.25" customHeight="1">
       <c r="A175" s="1">
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>27</v>
@@ -7285,12 +7256,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" ht="17.25" customHeight="1">
       <c r="A176" s="1">
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>28</v>
@@ -7320,12 +7291,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="17.25" customHeight="1">
       <c r="A177" s="1">
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>29</v>
@@ -7355,12 +7326,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" ht="17.25" customHeight="1">
       <c r="A178" s="1">
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>30</v>
@@ -7387,15 +7358,15 @@
         <v>32</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" ht="17.25" customHeight="1">
       <c r="A179" s="1">
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>31</v>
@@ -7422,15 +7393,15 @@
         <v>32</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="180" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" ht="17.25" customHeight="1">
       <c r="A180" s="1">
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>32</v>
@@ -7457,15 +7428,15 @@
         <v>32</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" ht="17.25" customHeight="1">
       <c r="A181" s="1">
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>37</v>
@@ -7492,15 +7463,15 @@
         <v>37</v>
       </c>
       <c r="M181" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" ht="17.25" customHeight="1">
       <c r="A182" s="1">
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>51</v>
@@ -7527,15 +7498,15 @@
         <v>50</v>
       </c>
       <c r="M182" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" ht="17.25" customHeight="1">
       <c r="A183" s="1">
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>52</v>
@@ -7562,15 +7533,15 @@
         <v>50</v>
       </c>
       <c r="M183" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="17.25" customHeight="1">
       <c r="A184" s="1">
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>36</v>
@@ -7597,15 +7568,15 @@
         <v>50</v>
       </c>
       <c r="M184" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" ht="17.25" customHeight="1">
       <c r="A185" s="1">
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>53</v>
@@ -7632,15 +7603,15 @@
         <v>50</v>
       </c>
       <c r="M185" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" ht="17.25" customHeight="1">
       <c r="A186" s="1">
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>54</v>
@@ -7667,15 +7638,15 @@
         <v>50</v>
       </c>
       <c r="M186" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" ht="17.25" customHeight="1">
       <c r="A187" s="1">
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>38</v>
@@ -7702,15 +7673,15 @@
         <v>50</v>
       </c>
       <c r="M187" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" ht="17.25" customHeight="1">
       <c r="A188" s="1">
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>39</v>
@@ -7737,15 +7708,15 @@
         <v>50</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" ht="17.25" customHeight="1">
       <c r="A189" s="1">
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>40</v>
@@ -7772,15 +7743,15 @@
         <v>50</v>
       </c>
       <c r="M189" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" ht="17.25" customHeight="1">
       <c r="A190" s="1">
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>55</v>
@@ -7807,15 +7778,15 @@
         <v>50</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="191" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" ht="17.25" customHeight="1">
       <c r="A191" s="1">
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>42</v>
@@ -7842,15 +7813,15 @@
         <v>50</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" ht="17.25" customHeight="1">
       <c r="A192" s="1">
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>43</v>
@@ -7877,15 +7848,15 @@
         <v>50</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" ht="17.25" customHeight="1">
       <c r="A193" s="1">
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>44</v>
@@ -7912,15 +7883,15 @@
         <v>50</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" ht="17.25" customHeight="1">
       <c r="A194" s="1">
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>50</v>
@@ -7947,15 +7918,15 @@
         <v>50</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" ht="17.25" customHeight="1">
       <c r="A195" s="1">
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>45</v>
@@ -7988,15 +7959,15 @@
         <v>45</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" ht="17.25" customHeight="1">
       <c r="A196" s="1">
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>46</v>
@@ -8017,21 +7988,21 @@
         <v>1757</v>
       </c>
       <c r="K196" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L196" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="17.25" customHeight="1">
       <c r="A197" s="1">
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C197" s="8" t="s">
         <v>47</v>
@@ -8058,15 +8029,15 @@
         <v>47</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" ht="17.25" customHeight="1">
       <c r="A198" s="1">
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C198" s="8" t="s">
         <v>48</v>
@@ -8093,15 +8064,15 @@
         <v>48</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="199" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="17.25" customHeight="1">
       <c r="A199" s="1">
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C199" s="8" t="s">
         <v>13</v>
@@ -8122,21 +8093,21 @@
         <v>2565</v>
       </c>
       <c r="K199" s="15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L199" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M199" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" ht="17.25" customHeight="1">
       <c r="A200" s="1">
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C200" s="8" t="s">
         <v>14</v>
@@ -8157,21 +8128,21 @@
         <v>2216</v>
       </c>
       <c r="K200" s="15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L200" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" ht="17.25" customHeight="1">
       <c r="A201" s="1">
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>15</v>
@@ -8192,21 +8163,21 @@
         <v>2032</v>
       </c>
       <c r="K201" s="15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L201" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M201" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" ht="17.25" customHeight="1">
       <c r="A202" s="1">
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C202" s="8" t="s">
         <v>16</v>
@@ -8227,21 +8198,21 @@
         <v>2216</v>
       </c>
       <c r="K202" s="15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L202" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M202" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" ht="17.25" customHeight="1">
       <c r="A203" s="1">
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C203" s="8" t="s">
         <v>17</v>
@@ -8262,21 +8233,21 @@
         <v>2216</v>
       </c>
       <c r="K203" s="15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L203" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M203" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" ht="17.25" customHeight="1">
       <c r="A204" s="1">
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C204" s="8" t="s">
         <v>25</v>
@@ -8306,12 +8277,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" ht="17.25" customHeight="1">
       <c r="A205" s="1">
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C205" s="8" t="s">
         <v>18</v>
@@ -8341,12 +8312,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" ht="17.25" customHeight="1">
       <c r="A206" s="1">
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C206" s="8" t="s">
         <v>19</v>
@@ -8376,12 +8347,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" ht="17.25" customHeight="1">
       <c r="A207" s="1">
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>20</v>
@@ -8411,12 +8382,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" ht="17.25" customHeight="1">
       <c r="A208" s="1">
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C208" s="8" t="s">
         <v>27</v>
@@ -8446,12 +8417,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" ht="17.25" customHeight="1">
       <c r="A209" s="1">
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C209" s="8" t="s">
         <v>28</v>
@@ -8481,12 +8452,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" ht="17.25" customHeight="1">
       <c r="A210" s="1">
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C210" s="8" t="s">
         <v>29</v>
@@ -8516,12 +8487,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" ht="17.25" customHeight="1">
       <c r="A211" s="1">
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C211" s="8" t="s">
         <v>30</v>
@@ -8548,15 +8519,15 @@
         <v>32</v>
       </c>
       <c r="M211" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="212" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" ht="17.25" customHeight="1">
       <c r="A212" s="1">
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C212" s="8" t="s">
         <v>31</v>
@@ -8583,15 +8554,15 @@
         <v>32</v>
       </c>
       <c r="M212" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" ht="17.25" customHeight="1">
       <c r="A213" s="1">
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C213" s="8" t="s">
         <v>32</v>
@@ -8618,15 +8589,15 @@
         <v>32</v>
       </c>
       <c r="M213" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="214" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" ht="17.25" customHeight="1">
       <c r="A214" s="1">
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C214" s="8" t="s">
         <v>37</v>
@@ -8653,15 +8624,15 @@
         <v>37</v>
       </c>
       <c r="M214" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" ht="17.25" customHeight="1">
       <c r="A215" s="1">
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C215" s="8" t="s">
         <v>51</v>
@@ -8688,15 +8659,15 @@
         <v>50</v>
       </c>
       <c r="M215" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" ht="17.25" customHeight="1">
       <c r="A216" s="1">
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C216" s="8" t="s">
         <v>52</v>
@@ -8723,15 +8694,15 @@
         <v>50</v>
       </c>
       <c r="M216" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" ht="17.25" customHeight="1">
       <c r="A217" s="1">
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C217" s="8" t="s">
         <v>36</v>
@@ -8758,15 +8729,15 @@
         <v>50</v>
       </c>
       <c r="M217" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="218" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" ht="17.25" customHeight="1">
       <c r="A218" s="1">
         <v>220</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C218" s="8" t="s">
         <v>53</v>
@@ -8793,15 +8764,15 @@
         <v>50</v>
       </c>
       <c r="M218" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" ht="17.25" customHeight="1">
       <c r="A219" s="1">
         <v>221</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C219" s="8" t="s">
         <v>54</v>
@@ -8828,15 +8799,15 @@
         <v>50</v>
       </c>
       <c r="M219" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" ht="17.25" customHeight="1">
       <c r="A220" s="1">
         <v>222</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C220" s="8" t="s">
         <v>38</v>
@@ -8863,15 +8834,15 @@
         <v>50</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" ht="17.25" customHeight="1">
       <c r="A221" s="1">
         <v>223</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C221" s="8" t="s">
         <v>39</v>
@@ -8898,15 +8869,15 @@
         <v>50</v>
       </c>
       <c r="M221" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" ht="17.25" customHeight="1">
       <c r="A222" s="1">
         <v>224</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C222" s="8" t="s">
         <v>40</v>
@@ -8933,15 +8904,15 @@
         <v>50</v>
       </c>
       <c r="M222" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="223" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" ht="17.25" customHeight="1">
       <c r="A223" s="1">
         <v>225</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C223" s="8" t="s">
         <v>55</v>
@@ -8968,15 +8939,15 @@
         <v>50</v>
       </c>
       <c r="M223" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" ht="17.25" customHeight="1">
       <c r="A224" s="1">
         <v>226</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C224" s="8" t="s">
         <v>42</v>
@@ -9003,15 +8974,15 @@
         <v>50</v>
       </c>
       <c r="M224" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" ht="17.25" customHeight="1">
       <c r="A225" s="1">
         <v>227</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C225" s="8" t="s">
         <v>43</v>
@@ -9038,15 +9009,15 @@
         <v>50</v>
       </c>
       <c r="M225" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" ht="17.25" customHeight="1">
       <c r="A226" s="1">
         <v>228</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C226" s="8" t="s">
         <v>44</v>
@@ -9073,15 +9044,15 @@
         <v>50</v>
       </c>
       <c r="M226" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" ht="17.25" customHeight="1">
       <c r="A227" s="1">
         <v>229</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C227" s="8" t="s">
         <v>50</v>
@@ -9108,15 +9079,15 @@
         <v>50</v>
       </c>
       <c r="M227" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" ht="17.25" customHeight="1">
       <c r="A228" s="1">
         <v>230</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C228" s="8" t="s">
         <v>46</v>
@@ -9137,21 +9108,21 @@
         <v>1757</v>
       </c>
       <c r="K228" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L228" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M228" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" ht="17.25" customHeight="1">
       <c r="A229" s="1">
         <v>231</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>47</v>
@@ -9178,15 +9149,15 @@
         <v>47</v>
       </c>
       <c r="M229" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" ht="17.25" customHeight="1">
       <c r="A230" s="1">
         <v>232</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C230" s="8" t="s">
         <v>48</v>
@@ -9213,15 +9184,15 @@
         <v>48</v>
       </c>
       <c r="M230" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" ht="17.25" customHeight="1">
       <c r="A231" s="1">
         <v>233</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>13</v>
@@ -9251,12 +9222,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" ht="17.25" customHeight="1">
       <c r="A232" s="1">
         <v>234</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C232" s="8" t="s">
         <v>14</v>
@@ -9286,12 +9257,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" ht="17.25" customHeight="1">
       <c r="A233" s="1">
         <v>235</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>15</v>
@@ -9321,12 +9292,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" ht="17.25" customHeight="1">
       <c r="A234" s="1">
         <v>236</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C234" s="8" t="s">
         <v>16</v>
@@ -9356,12 +9327,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" ht="17.25" customHeight="1">
       <c r="A235" s="1">
         <v>237</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C235" s="8" t="s">
         <v>17</v>
@@ -9391,12 +9362,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" ht="17.25" customHeight="1">
       <c r="A236" s="1">
         <v>238</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C236" s="8" t="s">
         <v>25</v>
@@ -9426,12 +9397,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" ht="17.25" customHeight="1">
       <c r="A237" s="1">
         <v>239</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>18</v>
@@ -9461,12 +9432,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" ht="17.25" customHeight="1">
       <c r="A238" s="1">
         <v>240</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C238" s="8" t="s">
         <v>19</v>
@@ -9496,12 +9467,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" ht="17.25" customHeight="1">
       <c r="A239" s="1">
         <v>241</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C239" s="8" t="s">
         <v>20</v>
@@ -9531,12 +9502,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" ht="17.25" customHeight="1">
       <c r="A240" s="1">
         <v>242</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C240" s="8" t="s">
         <v>27</v>
@@ -9566,12 +9537,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" ht="17.25" customHeight="1">
       <c r="A241" s="1">
         <v>243</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C241" s="8" t="s">
         <v>28</v>
@@ -9601,12 +9572,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" ht="17.25" customHeight="1">
       <c r="A242" s="1">
         <v>244</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C242" s="8" t="s">
         <v>29</v>
@@ -9636,12 +9607,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" ht="17.25" customHeight="1">
       <c r="A243" s="1">
         <v>245</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C243" s="8" t="s">
         <v>30</v>
@@ -9665,7 +9636,7 @@
         <v>59</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K243">
         <v>3020</v>
@@ -9674,15 +9645,15 @@
         <v>32</v>
       </c>
       <c r="M243" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="244" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" ht="17.25" customHeight="1">
       <c r="A244" s="1">
         <v>246</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C244" s="8" t="s">
         <v>31</v>
@@ -9709,15 +9680,15 @@
         <v>32</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="245" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" ht="17.25" customHeight="1">
       <c r="A245" s="1">
         <v>247</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C245" s="8" t="s">
         <v>32</v>
@@ -9744,15 +9715,15 @@
         <v>32</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="246" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" ht="17.25" customHeight="1">
       <c r="A246" s="1">
         <v>248</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C246" s="8" t="s">
         <v>37</v>
@@ -9779,15 +9750,15 @@
         <v>37</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="247" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" ht="17.25" customHeight="1">
       <c r="A247" s="1">
         <v>249</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C247" s="8" t="s">
         <v>51</v>
@@ -9814,15 +9785,15 @@
         <v>50</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="248" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" ht="17.25" customHeight="1">
       <c r="A248" s="1">
         <v>250</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C248" s="8" t="s">
         <v>52</v>
@@ -9849,15 +9820,15 @@
         <v>50</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="249" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" ht="17.25" customHeight="1">
       <c r="A249" s="1">
         <v>251</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C249" s="8" t="s">
         <v>36</v>
@@ -9884,15 +9855,15 @@
         <v>50</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="250" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" ht="17.25" customHeight="1">
       <c r="A250" s="1">
         <v>252</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C250" s="8" t="s">
         <v>53</v>
@@ -9919,15 +9890,15 @@
         <v>50</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="251" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" ht="17.25" customHeight="1">
       <c r="A251" s="1">
         <v>253</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C251" s="8" t="s">
         <v>54</v>
@@ -9954,15 +9925,15 @@
         <v>50</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="252" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" ht="17.25" customHeight="1">
       <c r="A252" s="1">
         <v>254</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C252" s="8" t="s">
         <v>38</v>
@@ -9989,15 +9960,15 @@
         <v>50</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="253" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" ht="17.25" customHeight="1">
       <c r="A253" s="1">
         <v>255</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C253" s="8" t="s">
         <v>39</v>
@@ -10024,15 +9995,15 @@
         <v>50</v>
       </c>
       <c r="M253" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="254" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" ht="17.25" customHeight="1">
       <c r="A254" s="1">
         <v>256</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C254" s="8" t="s">
         <v>40</v>
@@ -10059,15 +10030,15 @@
         <v>50</v>
       </c>
       <c r="M254" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="255" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" ht="17.25" customHeight="1">
       <c r="A255" s="1">
         <v>257</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C255" s="8" t="s">
         <v>55</v>
@@ -10094,15 +10065,15 @@
         <v>50</v>
       </c>
       <c r="M255" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="256" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" ht="17.25" customHeight="1">
       <c r="A256" s="1">
         <v>258</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C256" s="8" t="s">
         <v>42</v>
@@ -10129,15 +10100,15 @@
         <v>50</v>
       </c>
       <c r="M256" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="257" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" ht="17.25" customHeight="1">
       <c r="A257" s="1">
         <v>259</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C257" s="8" t="s">
         <v>43</v>
@@ -10164,15 +10135,15 @@
         <v>50</v>
       </c>
       <c r="M257" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="258" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" ht="17.25" customHeight="1">
       <c r="A258" s="1">
         <v>260</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C258" s="8" t="s">
         <v>44</v>
@@ -10199,15 +10170,15 @@
         <v>50</v>
       </c>
       <c r="M258" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="259" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" ht="17.25" customHeight="1">
       <c r="A259" s="1">
         <v>261</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C259" s="8" t="s">
         <v>50</v>
@@ -10234,15 +10205,15 @@
         <v>50</v>
       </c>
       <c r="M259" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="260" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" ht="17.25" customHeight="1">
       <c r="A260" s="1">
         <v>262</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C260" s="8" t="s">
         <v>46</v>
@@ -10263,21 +10234,21 @@
         <v>1757</v>
       </c>
       <c r="K260" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L260" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M260" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="261" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" ht="17.25" customHeight="1">
       <c r="A261" s="1">
         <v>263</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C261" s="8" t="s">
         <v>47</v>
@@ -10304,15 +10275,15 @@
         <v>47</v>
       </c>
       <c r="M261" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="262" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" ht="17.25" customHeight="1">
       <c r="A262" s="1">
         <v>264</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C262" s="8" t="s">
         <v>48</v>
@@ -10336,7 +10307,7 @@
         <v>59</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K262">
         <v>9982</v>
@@ -10345,15 +10316,15 @@
         <v>48</v>
       </c>
       <c r="M262" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="263" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" ht="17.25" customHeight="1">
       <c r="A263" s="1">
         <v>265</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C263" s="8" t="s">
         <v>13</v>
@@ -10383,12 +10354,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" ht="17.25" customHeight="1">
       <c r="A264" s="1">
         <v>266</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C264" s="8" t="s">
         <v>14</v>
@@ -10418,12 +10389,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" ht="17.25" customHeight="1">
       <c r="A265" s="1">
         <v>267</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C265" s="8" t="s">
         <v>15</v>
@@ -10456,12 +10427,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" ht="17.25" customHeight="1">
       <c r="A266" s="1">
         <v>268</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C266" s="8" t="s">
         <v>16</v>
@@ -10491,12 +10462,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" ht="17.25" customHeight="1">
       <c r="A267" s="1">
         <v>269</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>17</v>
@@ -10526,12 +10497,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" ht="17.25" customHeight="1">
       <c r="A268" s="1">
         <v>270</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C268" s="8" t="s">
         <v>25</v>
@@ -10561,12 +10532,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" ht="17.25" customHeight="1">
       <c r="A269" s="1">
         <v>271</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C269" s="8" t="s">
         <v>18</v>
@@ -10596,12 +10567,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" ht="17.25" customHeight="1">
       <c r="A270" s="1">
         <v>272</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C270" s="8" t="s">
         <v>19</v>
@@ -10631,12 +10602,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" ht="17.25" customHeight="1">
       <c r="A271" s="1">
         <v>273</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C271" s="8" t="s">
         <v>20</v>
@@ -10666,12 +10637,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" ht="17.25" customHeight="1">
       <c r="A272" s="1">
         <v>274</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C272" s="8" t="s">
         <v>27</v>
@@ -10701,12 +10672,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" ht="17.25" customHeight="1">
       <c r="A273" s="1">
         <v>275</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C273" s="8" t="s">
         <v>28</v>
@@ -10736,12 +10707,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" ht="17.25" customHeight="1">
       <c r="A274" s="1">
         <v>276</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C274" s="8" t="s">
         <v>29</v>
@@ -10771,12 +10742,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" ht="17.25" customHeight="1">
       <c r="A275" s="1">
         <v>277</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C275" s="8" t="s">
         <v>56</v>
@@ -10800,7 +10771,7 @@
         <v>58</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K275">
         <v>3020</v>
@@ -10809,15 +10780,15 @@
         <v>32</v>
       </c>
       <c r="M275" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="276" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" ht="17.25" customHeight="1">
       <c r="A276" s="1">
         <v>278</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C276" s="8" t="s">
         <v>31</v>
@@ -10844,15 +10815,15 @@
         <v>32</v>
       </c>
       <c r="M276" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="277" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" ht="17.25" customHeight="1">
       <c r="A277" s="1">
         <v>279</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C277" s="8" t="s">
         <v>32</v>
@@ -10879,15 +10850,15 @@
         <v>32</v>
       </c>
       <c r="M277" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="278" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" ht="17.25" customHeight="1">
       <c r="A278" s="1">
         <v>280</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C278" s="8" t="s">
         <v>37</v>
@@ -10914,15 +10885,15 @@
         <v>37</v>
       </c>
       <c r="M278" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="279" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" ht="17.25" customHeight="1">
       <c r="A279" s="1">
         <v>281</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C279" s="8" t="s">
         <v>51</v>
@@ -10949,15 +10920,15 @@
         <v>50</v>
       </c>
       <c r="M279" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="280" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" ht="17.25" customHeight="1">
       <c r="A280" s="1">
         <v>282</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C280" s="8" t="s">
         <v>52</v>
@@ -10984,15 +10955,15 @@
         <v>50</v>
       </c>
       <c r="M280" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="281" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" ht="17.25" customHeight="1">
       <c r="A281" s="1">
         <v>283</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C281" s="8" t="s">
         <v>34</v>
@@ -11016,7 +10987,7 @@
         <v>58</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K281">
         <v>7015</v>
@@ -11025,15 +10996,15 @@
         <v>50</v>
       </c>
       <c r="M281" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="282" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" ht="17.25" customHeight="1">
       <c r="A282" s="1">
         <v>284</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C282" s="8" t="s">
         <v>36</v>
@@ -11060,15 +11031,15 @@
         <v>50</v>
       </c>
       <c r="M282" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="283" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" ht="17.25" customHeight="1">
       <c r="A283" s="1">
         <v>285</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C283" s="8" t="s">
         <v>53</v>
@@ -11095,15 +11066,15 @@
         <v>50</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="284" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" ht="17.25" customHeight="1">
       <c r="A284" s="1">
         <v>286</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C284" s="8" t="s">
         <v>54</v>
@@ -11130,15 +11101,15 @@
         <v>50</v>
       </c>
       <c r="M284" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="285" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" ht="17.25" customHeight="1">
       <c r="A285" s="1">
         <v>287</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C285" s="8" t="s">
         <v>38</v>
@@ -11165,15 +11136,15 @@
         <v>50</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="286" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" ht="17.25" customHeight="1">
       <c r="A286" s="1">
         <v>288</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C286" s="8" t="s">
         <v>39</v>
@@ -11184,6 +11155,9 @@
       <c r="E286" s="8">
         <v>48200</v>
       </c>
+      <c r="F286" s="8">
+        <v>0</v>
+      </c>
       <c r="G286" s="8">
         <v>0</v>
       </c>
@@ -11194,7 +11168,7 @@
         <v>59</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K286">
         <v>7015</v>
@@ -11203,15 +11177,15 @@
         <v>50</v>
       </c>
       <c r="M286" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="287" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" ht="17.25" customHeight="1">
       <c r="A287" s="1">
         <v>289</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C287" s="8" t="s">
         <v>40</v>
@@ -11238,15 +11212,15 @@
         <v>50</v>
       </c>
       <c r="M287" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="288" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" ht="17.25" customHeight="1">
       <c r="A288" s="1">
         <v>290</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C288" s="8" t="s">
         <v>55</v>
@@ -11273,15 +11247,15 @@
         <v>50</v>
       </c>
       <c r="M288" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="289" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" ht="17.25" customHeight="1">
       <c r="A289" s="1">
         <v>291</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C289" s="8" t="s">
         <v>42</v>
@@ -11308,15 +11282,15 @@
         <v>50</v>
       </c>
       <c r="M289" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="290" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" ht="17.25" customHeight="1">
       <c r="A290" s="1">
         <v>292</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C290" s="8" t="s">
         <v>43</v>
@@ -11343,15 +11317,15 @@
         <v>50</v>
       </c>
       <c r="M290" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="291" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" ht="17.25" customHeight="1">
       <c r="A291" s="1">
         <v>293</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C291" s="8" t="s">
         <v>44</v>
@@ -11371,9 +11345,6 @@
       <c r="H291" s="1">
         <v>1849</v>
       </c>
-      <c r="I291" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="K291">
         <v>7015</v>
       </c>
@@ -11381,15 +11352,15 @@
         <v>50</v>
       </c>
       <c r="M291" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="292" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" ht="17.25" customHeight="1">
       <c r="A292" s="1">
         <v>294</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C292" s="8" t="s">
         <v>50</v>
@@ -11416,15 +11387,15 @@
         <v>50</v>
       </c>
       <c r="M292" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="293" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" ht="17.25" customHeight="1">
       <c r="A293" s="1">
         <v>295</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C293" s="8" t="s">
         <v>46</v>
@@ -11445,21 +11416,21 @@
         <v>1757</v>
       </c>
       <c r="K293" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L293" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M293" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="294" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" ht="17.25" customHeight="1">
       <c r="A294" s="1">
         <v>296</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C294" s="8" t="s">
         <v>47</v>
@@ -11489,10 +11460,10 @@
         <v>47</v>
       </c>
       <c r="M294" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="295" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" ht="17.25" customHeight="1">
       <c r="K295"/>
     </row>
   </sheetData>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84C4973-44AE-44DB-A657-2AD975F561E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E01472D-64C7-4630-8D82-71046F49DCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="資料表" sheetId="1" r:id="rId1"/>
+    <sheet name="資料頁" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C52A448-E97E-4116-8667-CEAD225191EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B881BE1-D9E3-4318-8084-219D4449C9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料頁" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$M$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$M$295</definedName>
     <definedName name="全健康保險費" localSheetId="0">資料頁!$H$2:$H$10</definedName>
     <definedName name="序號" localSheetId="0">資料頁!$A$2:$A$10</definedName>
     <definedName name="投保薪額">資料頁!$E$2:$E$10</definedName>
@@ -41,12 +41,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="117">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -422,6 +425,24 @@
     <t>嚴麟</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>會計室</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加保</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李芷盈</t>
+  </si>
+  <si>
+    <t>1150812到職</t>
+  </si>
+  <si>
+    <t>教育部_補助大專校院精進校務經營計畫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -430,7 +451,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -507,6 +528,13 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -549,7 +577,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -594,10 +622,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -635,9 +675,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -675,9 +715,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -710,9 +750,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -745,9 +802,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -924,32 +998,32 @@
   <sheetPr codeName="工作表2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M295"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" customHeight="1"/>
+  <dimension ref="A1:M296"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.21875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="59.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="59.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5" style="1" customWidth="1"/>
     <col min="16" max="19" width="9" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.77734375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.75" style="1" customWidth="1"/>
     <col min="21" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="16.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="16.375" style="1" customWidth="1"/>
     <col min="26" max="54" width="9" style="1" customWidth="1"/>
     <col min="55" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="11" customFormat="1" ht="39" customHeight="1">
+    <row r="1" spans="1:13" s="11" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
@@ -990,8 +1064,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="17.25" customHeight="1">
+    <row r="2" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1019,7 +1094,7 @@
         <v>57</v>
       </c>
       <c r="J2" s="6"/>
-      <c r="K2">
+      <c r="K2" s="16">
         <v>4040</v>
       </c>
       <c r="L2" s="8" t="s">
@@ -1029,8 +1104,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1">
+    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <f t="shared" ref="A3:A66" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1058,7 +1134,7 @@
         <v>57</v>
       </c>
       <c r="J3" s="6"/>
-      <c r="K3">
+      <c r="K3" s="16">
         <v>4040</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -1068,8 +1144,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="17.25" customHeight="1">
+    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1094,7 +1171,7 @@
         <v>2032</v>
       </c>
       <c r="J4" s="6"/>
-      <c r="K4">
+      <c r="K4" s="16">
         <v>4040</v>
       </c>
       <c r="L4" s="8" t="s">
@@ -1104,8 +1181,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="17.25" customHeight="1">
+    <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1133,7 +1211,7 @@
         <v>57</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="K5">
+      <c r="K5" s="16">
         <v>4040</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -1143,8 +1221,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="17.25" customHeight="1">
+    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1172,7 +1251,7 @@
         <v>57</v>
       </c>
       <c r="J6" s="6"/>
-      <c r="K6">
+      <c r="K6" s="16">
         <v>4040</v>
       </c>
       <c r="L6" s="8" t="s">
@@ -1182,8 +1261,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="17.25" customHeight="1">
+    <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1211,7 +1291,7 @@
         <v>57</v>
       </c>
       <c r="J7" s="6"/>
-      <c r="K7">
+      <c r="K7" s="16">
         <v>6262</v>
       </c>
       <c r="L7" s="1" t="s">
@@ -1221,8 +1301,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="17.25" customHeight="1">
+    <row r="8" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1248,7 +1329,7 @@
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8">
+      <c r="K8" s="16">
         <v>6262</v>
       </c>
       <c r="L8" s="1" t="s">
@@ -1258,8 +1339,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="17.25" customHeight="1">
+    <row r="9" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1284,7 +1366,7 @@
         <v>2332</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9">
+      <c r="K9" s="16">
         <v>6262</v>
       </c>
       <c r="L9" s="1" t="s">
@@ -1294,8 +1376,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="17.25" customHeight="1">
+    <row r="10" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1323,7 +1406,7 @@
         <v>57</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10">
+      <c r="K10" s="16">
         <v>6919</v>
       </c>
       <c r="L10" s="8" t="s">
@@ -1333,8 +1416,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="17.25" customHeight="1">
+    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1361,7 +1445,7 @@
       <c r="I11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="16">
         <v>6919</v>
       </c>
       <c r="L11" s="8" t="s">
@@ -1371,8 +1455,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="17.25" customHeight="1">
+    <row r="12" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1399,7 +1484,7 @@
       <c r="I12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="16">
         <v>6919</v>
       </c>
       <c r="L12" s="8" t="s">
@@ -1409,8 +1494,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="17.25" customHeight="1">
+    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1434,7 +1520,7 @@
       <c r="H13" s="1">
         <v>3233</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="16">
         <v>6919</v>
       </c>
       <c r="L13" s="8" t="s">
@@ -1444,8 +1530,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="17.25" customHeight="1">
+    <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1469,7 +1556,7 @@
       <c r="H14" s="1">
         <v>2032</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="16">
         <v>3020</v>
       </c>
       <c r="L14" s="8" t="s">
@@ -1479,8 +1566,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="17.25" customHeight="1">
+    <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1507,7 +1595,7 @@
       <c r="I15" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="16">
         <v>3020</v>
       </c>
       <c r="L15" s="8" t="s">
@@ -1517,8 +1605,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="17.25" customHeight="1">
+    <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1542,7 +1631,7 @@
       <c r="H16" s="1">
         <v>2032</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="16">
         <v>3020</v>
       </c>
       <c r="L16" s="8" t="s">
@@ -1552,8 +1641,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="17.25" customHeight="1">
+    <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1587,8 +1677,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="17.25" customHeight="1">
+    <row r="18" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1615,7 +1706,7 @@
       <c r="I18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="16">
         <v>7015</v>
       </c>
       <c r="L18" s="8" t="s">
@@ -1625,8 +1716,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="17.25" customHeight="1">
+    <row r="19" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1653,7 +1745,7 @@
       <c r="I19" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="16">
         <v>7015</v>
       </c>
       <c r="L19" s="8" t="s">
@@ -1663,8 +1755,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="17.25" customHeight="1">
+    <row r="20" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1691,7 +1784,7 @@
       <c r="I20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="16">
         <v>7015</v>
       </c>
       <c r="L20" s="8" t="s">
@@ -1701,8 +1794,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="17.25" customHeight="1">
+    <row r="21" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1729,7 +1823,7 @@
       <c r="I21" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="16">
         <v>7015</v>
       </c>
       <c r="L21" s="8" t="s">
@@ -1739,8 +1833,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="17.25" customHeight="1">
+    <row r="22" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1767,7 +1862,7 @@
       <c r="I22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="16">
         <v>7015</v>
       </c>
       <c r="L22" s="8" t="s">
@@ -1777,8 +1872,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="17.25" customHeight="1">
+    <row r="23" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1802,7 +1898,7 @@
       <c r="H23" s="1">
         <v>1849</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="16">
         <v>7015</v>
       </c>
       <c r="L23" s="8" t="s">
@@ -1812,8 +1908,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="17.25" customHeight="1">
+    <row r="24" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1837,7 +1934,7 @@
       <c r="H24" s="1">
         <v>1849</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="16">
         <v>7015</v>
       </c>
       <c r="L24" s="8" t="s">
@@ -1847,8 +1944,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="17.25" customHeight="1">
+    <row r="25" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1872,7 +1970,7 @@
       <c r="H25" s="1">
         <v>1849</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="16">
         <v>7015</v>
       </c>
       <c r="L25" s="8" t="s">
@@ -1882,8 +1980,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="17.25" customHeight="1">
+    <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1910,7 +2009,7 @@
       <c r="I26" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="16">
         <v>7015</v>
       </c>
       <c r="L26" s="8" t="s">
@@ -1920,8 +2019,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="17.25" customHeight="1">
+    <row r="27" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1945,7 +2045,7 @@
       <c r="H27" s="1">
         <v>1849</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="16">
         <v>7015</v>
       </c>
       <c r="L27" s="8" t="s">
@@ -1955,8 +2055,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="17.25" customHeight="1">
+    <row r="28" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1986,7 +2087,7 @@
       <c r="J28" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="16">
         <v>7015</v>
       </c>
       <c r="L28" s="8" t="s">
@@ -1996,8 +2097,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="17.25" customHeight="1">
+    <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2031,8 +2133,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="17.25" customHeight="1">
+    <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -2056,7 +2159,7 @@
       <c r="H30" s="1">
         <v>1757</v>
       </c>
-      <c r="K30" s="14" t="s">
+      <c r="K30" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L30" s="8" t="s">
@@ -2066,8 +2169,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="17.25" customHeight="1">
+    <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2094,7 +2198,7 @@
       <c r="I31" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="16">
         <v>8990</v>
       </c>
       <c r="L31" s="8" t="s">
@@ -2104,8 +2208,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="17.25" customHeight="1">
+    <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -2129,7 +2234,7 @@
       <c r="H32" s="1">
         <v>1757</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="16">
         <v>9982</v>
       </c>
       <c r="L32" s="8" t="s">
@@ -2139,8 +2244,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="17.25" customHeight="1">
+    <row r="33" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2164,7 +2270,7 @@
       <c r="H33" s="1">
         <v>2565</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="16">
         <v>4040</v>
       </c>
       <c r="L33" s="8" t="s">
@@ -2174,8 +2280,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="17.25" customHeight="1">
+    <row r="34" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -2199,7 +2306,7 @@
       <c r="H34" s="1">
         <v>2216</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="16">
         <v>4040</v>
       </c>
       <c r="L34" s="8" t="s">
@@ -2209,8 +2316,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="17.25" customHeight="1">
+    <row r="35" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2234,7 +2342,7 @@
       <c r="H35" s="1">
         <v>2032</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="16">
         <v>4040</v>
       </c>
       <c r="L35" s="8" t="s">
@@ -2244,8 +2352,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="17.25" customHeight="1">
+    <row r="36" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2269,7 +2378,7 @@
       <c r="H36" s="1">
         <v>2216</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="16">
         <v>4040</v>
       </c>
       <c r="L36" s="8" t="s">
@@ -2279,8 +2388,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="17.25" customHeight="1">
+    <row r="37" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2304,7 +2414,7 @@
       <c r="H37" s="1">
         <v>2124</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="16">
         <v>4040</v>
       </c>
       <c r="L37" s="8" t="s">
@@ -2314,8 +2424,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="17.25" customHeight="1">
+    <row r="38" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2339,7 +2450,7 @@
       <c r="H38" s="1">
         <v>2565</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="16">
         <v>6262</v>
       </c>
       <c r="L38" s="1" t="s">
@@ -2349,8 +2460,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="17.25" customHeight="1">
+    <row r="39" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2374,7 +2486,7 @@
       <c r="H39" s="1">
         <v>2449</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="16">
         <v>6262</v>
       </c>
       <c r="L39" s="1" t="s">
@@ -2384,8 +2496,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="17.25" customHeight="1">
+    <row r="40" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -2409,7 +2522,7 @@
       <c r="H40" s="1">
         <v>2332</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="16">
         <v>6262</v>
       </c>
       <c r="L40" s="1" t="s">
@@ -2419,8 +2532,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="17.25" customHeight="1">
+    <row r="41" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -2444,7 +2558,7 @@
       <c r="H41" s="1">
         <v>1849</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="16">
         <v>6919</v>
       </c>
       <c r="L41" s="8" t="s">
@@ -2454,8 +2568,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="17.25" customHeight="1">
+    <row r="42" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -2479,7 +2594,7 @@
       <c r="H42" s="1">
         <v>2216</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="16">
         <v>6919</v>
       </c>
       <c r="L42" s="8" t="s">
@@ -2489,8 +2604,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="17.25" customHeight="1">
+    <row r="43" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -2514,7 +2630,7 @@
       <c r="H43" s="1">
         <v>2032</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="16">
         <v>6919</v>
       </c>
       <c r="L43" s="8" t="s">
@@ -2524,8 +2640,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="17.25" customHeight="1">
+    <row r="44" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -2549,7 +2666,7 @@
       <c r="H44" s="1">
         <v>3233</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="16">
         <v>6919</v>
       </c>
       <c r="L44" s="8" t="s">
@@ -2559,8 +2676,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="17.25" customHeight="1">
+    <row r="45" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2584,7 +2702,7 @@
       <c r="H45" s="1">
         <v>2032</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="16">
         <v>3020</v>
       </c>
       <c r="L45" s="8" t="s">
@@ -2594,8 +2712,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="17.25" customHeight="1">
+    <row r="46" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2619,7 +2738,7 @@
       <c r="H46" s="1">
         <v>2032</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="16">
         <v>3020</v>
       </c>
       <c r="L46" s="8" t="s">
@@ -2629,8 +2748,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="17.25" customHeight="1">
+    <row r="47" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -2654,7 +2774,7 @@
       <c r="H47" s="1">
         <v>2032</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="16">
         <v>3020</v>
       </c>
       <c r="L47" s="8" t="s">
@@ -2664,8 +2784,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="17.25" customHeight="1">
+    <row r="48" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -2699,8 +2820,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="17.25" customHeight="1">
+    <row r="49" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -2724,7 +2846,7 @@
       <c r="H49" s="1">
         <v>2449</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="16">
         <v>7015</v>
       </c>
       <c r="L49" s="8" t="s">
@@ -2734,8 +2856,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="17.25" customHeight="1">
+    <row r="50" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -2765,7 +2888,7 @@
       <c r="J50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="16">
         <v>7015</v>
       </c>
       <c r="L50" s="8" t="s">
@@ -2775,8 +2898,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="17.25" customHeight="1">
+    <row r="51" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -2800,7 +2924,7 @@
       <c r="H51" s="1">
         <v>1849</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="16">
         <v>7015</v>
       </c>
       <c r="L51" s="8" t="s">
@@ -2810,8 +2934,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="17.25" customHeight="1">
+    <row r="52" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -2841,7 +2966,7 @@
       <c r="J52" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="16">
         <v>7015</v>
       </c>
       <c r="L52" s="8" t="s">
@@ -2851,8 +2976,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="17.25" customHeight="1">
+    <row r="53" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -2882,7 +3008,7 @@
       <c r="J53" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="16">
         <v>7015</v>
       </c>
       <c r="L53" s="8" t="s">
@@ -2892,8 +3018,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="17.25" customHeight="1">
+    <row r="54" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -2917,7 +3044,7 @@
       <c r="H54" s="1">
         <v>1849</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="16">
         <v>7015</v>
       </c>
       <c r="L54" s="8" t="s">
@@ -2927,8 +3054,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="17.25" customHeight="1">
+    <row r="55" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -2952,7 +3080,7 @@
       <c r="H55" s="1">
         <v>1849</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="16">
         <v>7015</v>
       </c>
       <c r="L55" s="8" t="s">
@@ -2962,8 +3090,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="17.25" customHeight="1">
+    <row r="56" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -2987,7 +3116,7 @@
       <c r="H56" s="1">
         <v>1849</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="16">
         <v>7015</v>
       </c>
       <c r="L56" s="8" t="s">
@@ -2997,8 +3126,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="17.25" customHeight="1">
+    <row r="57" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -3028,7 +3158,7 @@
       <c r="J57" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="16">
         <v>7015</v>
       </c>
       <c r="L57" s="8" t="s">
@@ -3038,8 +3168,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="17.25" customHeight="1">
+    <row r="58" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -3063,7 +3194,7 @@
       <c r="H58" s="1">
         <v>1940</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="16">
         <v>7015</v>
       </c>
       <c r="L58" s="8" t="s">
@@ -3073,8 +3204,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="17.25" customHeight="1">
+    <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -3098,7 +3230,7 @@
       <c r="H59" s="1">
         <v>1849</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="16">
         <v>7015</v>
       </c>
       <c r="L59" s="8" t="s">
@@ -3108,8 +3240,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="17.25" customHeight="1">
+    <row r="60" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -3133,7 +3266,7 @@
       <c r="H60" s="1">
         <v>1849</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="16">
         <v>7015</v>
       </c>
       <c r="L60" s="8" t="s">
@@ -3143,8 +3276,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="17.25" customHeight="1">
+    <row r="61" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -3174,7 +3308,7 @@
       <c r="J61" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="16">
         <v>7015</v>
       </c>
       <c r="L61" s="8" t="s">
@@ -3184,9 +3318,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="17.25" customHeight="1">
+    <row r="62" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>62</v>
+        <f t="shared" si="0"/>
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>88</v>
@@ -3219,9 +3354,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="17.25" customHeight="1">
+    <row r="63" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>63</v>
+        <f t="shared" si="0"/>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>90</v>
@@ -3244,7 +3380,7 @@
       <c r="H63" s="1">
         <v>1757</v>
       </c>
-      <c r="K63" s="14" t="s">
+      <c r="K63" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L63" s="8" t="s">
@@ -3254,9 +3390,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="17.25" customHeight="1">
+    <row r="64" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>64</v>
+        <f t="shared" si="0"/>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>92</v>
@@ -3279,7 +3416,7 @@
       <c r="H64" s="1">
         <v>2332</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="16">
         <v>8990</v>
       </c>
       <c r="L64" s="8" t="s">
@@ -3289,9 +3426,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="17.25" customHeight="1">
+    <row r="65" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>65</v>
+        <f t="shared" si="0"/>
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>94</v>
@@ -3314,7 +3452,7 @@
       <c r="H65" s="1">
         <v>1757</v>
       </c>
-      <c r="K65">
+      <c r="K65" s="16">
         <v>9982</v>
       </c>
       <c r="L65" s="8" t="s">
@@ -3324,9 +3462,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="17.25" customHeight="1">
+    <row r="66" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>66</v>
+        <f t="shared" si="0"/>
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>96</v>
@@ -3349,7 +3488,7 @@
       <c r="H66" s="1">
         <v>2565</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="16">
         <v>4040</v>
       </c>
       <c r="L66" s="8" t="s">
@@ -3359,9 +3498,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="17.25" customHeight="1">
+    <row r="67" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>67</v>
+        <f t="shared" ref="A67:A130" si="1">ROW()-1</f>
+        <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>96</v>
@@ -3384,7 +3524,7 @@
       <c r="H67" s="1">
         <v>2216</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="16">
         <v>4040</v>
       </c>
       <c r="L67" s="8" t="s">
@@ -3394,9 +3534,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="17.25" customHeight="1">
+    <row r="68" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>68</v>
+        <f t="shared" si="1"/>
+        <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>96</v>
@@ -3419,7 +3560,7 @@
       <c r="H68" s="1">
         <v>2032</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="16">
         <v>4040</v>
       </c>
       <c r="L68" s="8" t="s">
@@ -3429,9 +3570,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="17.25" customHeight="1">
+    <row r="69" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>69</v>
+        <f t="shared" si="1"/>
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>96</v>
@@ -3454,7 +3596,7 @@
       <c r="H69" s="1">
         <v>2216</v>
       </c>
-      <c r="K69">
+      <c r="K69" s="16">
         <v>4040</v>
       </c>
       <c r="L69" s="8" t="s">
@@ -3464,9 +3606,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="17.25" customHeight="1">
+    <row r="70" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>70</v>
+        <f t="shared" si="1"/>
+        <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>96</v>
@@ -3492,7 +3635,7 @@
       <c r="I70" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="16">
         <v>4040</v>
       </c>
       <c r="L70" s="8" t="s">
@@ -3502,9 +3645,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="17.25" customHeight="1">
+    <row r="71" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>71</v>
+        <f t="shared" si="1"/>
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>75</v>
@@ -3530,7 +3674,7 @@
       <c r="I71" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="16">
         <v>6262</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -3540,9 +3684,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="17.25" customHeight="1">
+    <row r="72" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>72</v>
+        <f t="shared" si="1"/>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>75</v>
@@ -3565,7 +3710,7 @@
       <c r="H72" s="1">
         <v>2449</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="16">
         <v>6262</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -3575,9 +3720,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="17.25" customHeight="1">
+    <row r="73" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>73</v>
+        <f t="shared" si="1"/>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>75</v>
@@ -3603,7 +3749,7 @@
       <c r="I73" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="16">
         <v>6262</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -3613,9 +3759,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="17.25" customHeight="1">
+    <row r="74" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>74</v>
+        <f t="shared" si="1"/>
+        <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>76</v>
@@ -3638,7 +3785,7 @@
       <c r="H74" s="1">
         <v>1849</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="16">
         <v>6919</v>
       </c>
       <c r="L74" s="8" t="s">
@@ -3648,9 +3795,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="17.25" customHeight="1">
+    <row r="75" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>75</v>
+        <f t="shared" si="1"/>
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
@@ -3673,7 +3821,7 @@
       <c r="H75" s="1">
         <v>2216</v>
       </c>
-      <c r="K75">
+      <c r="K75" s="16">
         <v>6919</v>
       </c>
       <c r="L75" s="8" t="s">
@@ -3683,9 +3831,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="17.25" customHeight="1">
+    <row r="76" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>76</v>
+        <f t="shared" si="1"/>
+        <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>76</v>
@@ -3708,7 +3857,7 @@
       <c r="H76" s="1">
         <v>2032</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="16">
         <v>6919</v>
       </c>
       <c r="L76" s="8" t="s">
@@ -3718,9 +3867,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="17.25" customHeight="1">
+    <row r="77" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>77</v>
+        <f t="shared" si="1"/>
+        <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>78</v>
@@ -3743,7 +3893,7 @@
       <c r="H77" s="1">
         <v>3233</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="16">
         <v>6919</v>
       </c>
       <c r="L77" s="8" t="s">
@@ -3753,9 +3903,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="17.25" customHeight="1">
+    <row r="78" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>78</v>
+        <f t="shared" si="1"/>
+        <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>82</v>
@@ -3778,7 +3929,7 @@
       <c r="H78" s="1">
         <v>2032</v>
       </c>
-      <c r="K78">
+      <c r="K78" s="16">
         <v>3020</v>
       </c>
       <c r="L78" s="8" t="s">
@@ -3788,9 +3939,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="17.25" customHeight="1">
+    <row r="79" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>79</v>
+        <f t="shared" si="1"/>
+        <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>82</v>
@@ -3813,7 +3965,7 @@
       <c r="H79" s="1">
         <v>2032</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="16">
         <v>3020</v>
       </c>
       <c r="L79" s="8" t="s">
@@ -3823,9 +3975,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="17.25" customHeight="1">
+    <row r="80" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>82</v>
@@ -3848,7 +4001,7 @@
       <c r="H80" s="1">
         <v>2032</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="16">
         <v>3020</v>
       </c>
       <c r="L80" s="8" t="s">
@@ -3858,9 +4011,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="17.25" customHeight="1">
+    <row r="81" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>81</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>80</v>
@@ -3899,9 +4053,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="17.25" customHeight="1">
+    <row r="82" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>82</v>
+        <f t="shared" si="1"/>
+        <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>84</v>
@@ -3930,7 +4085,7 @@
       <c r="J82" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="16">
         <v>1615</v>
       </c>
       <c r="L82" s="8" t="s">
@@ -3940,9 +4095,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="17.25" customHeight="1">
+    <row r="83" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>83</v>
+        <f t="shared" si="1"/>
+        <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>84</v>
@@ -3971,7 +4127,7 @@
       <c r="J83" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="16">
         <v>7015</v>
       </c>
       <c r="L83" s="8" t="s">
@@ -3981,9 +4137,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="17.25" customHeight="1">
+    <row r="84" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>84</v>
+        <f t="shared" si="1"/>
+        <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>84</v>
@@ -4006,7 +4163,7 @@
       <c r="H84" s="1">
         <v>649</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="16">
         <v>7015</v>
       </c>
       <c r="L84" s="8" t="s">
@@ -4016,9 +4173,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="17.25" customHeight="1">
+    <row r="85" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>85</v>
+        <f t="shared" si="1"/>
+        <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>84</v>
@@ -4047,7 +4205,7 @@
       <c r="J85" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="16">
         <v>7015</v>
       </c>
       <c r="L85" s="8" t="s">
@@ -4057,9 +4215,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="17.25" customHeight="1">
+    <row r="86" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>86</v>
+        <f t="shared" si="1"/>
+        <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>84</v>
@@ -4082,7 +4241,7 @@
       <c r="H86" s="1">
         <v>1849</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="16">
         <v>7015</v>
       </c>
       <c r="L86" s="8" t="s">
@@ -4092,9 +4251,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="17.25" customHeight="1">
+    <row r="87" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>87</v>
+        <f t="shared" si="1"/>
+        <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>84</v>
@@ -4123,7 +4283,7 @@
       <c r="J87" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="16">
         <v>7015</v>
       </c>
       <c r="L87" s="8" t="s">
@@ -4133,9 +4293,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="17.25" customHeight="1">
+    <row r="88" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>88</v>
+        <f t="shared" si="1"/>
+        <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>84</v>
@@ -4164,7 +4325,7 @@
       <c r="J88" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K88">
+      <c r="K88" s="16">
         <v>7015</v>
       </c>
       <c r="L88" s="8" t="s">
@@ -4174,9 +4335,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="17.25" customHeight="1">
+    <row r="89" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>89</v>
+        <f t="shared" si="1"/>
+        <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>84</v>
@@ -4199,7 +4361,7 @@
       <c r="H89" s="1">
         <v>1849</v>
       </c>
-      <c r="K89">
+      <c r="K89" s="16">
         <v>7015</v>
       </c>
       <c r="L89" s="8" t="s">
@@ -4209,9 +4371,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="17.25" customHeight="1">
+    <row r="90" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>90</v>
+        <f t="shared" si="1"/>
+        <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>86</v>
@@ -4237,7 +4400,7 @@
       <c r="I90" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="16">
         <v>7015</v>
       </c>
       <c r="L90" s="8" t="s">
@@ -4247,9 +4410,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="17.25" customHeight="1">
+    <row r="91" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>91</v>
+        <f t="shared" si="1"/>
+        <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>86</v>
@@ -4272,7 +4436,7 @@
       <c r="H91" s="1">
         <v>1849</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="16">
         <v>7015</v>
       </c>
       <c r="L91" s="8" t="s">
@@ -4282,9 +4446,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="17.25" customHeight="1">
+    <row r="92" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>93</v>
+        <f t="shared" si="1"/>
+        <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>86</v>
@@ -4307,7 +4472,7 @@
       <c r="H92" s="1">
         <v>1940</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="16">
         <v>7015</v>
       </c>
       <c r="L92" s="8" t="s">
@@ -4317,9 +4482,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="17.25" customHeight="1">
+    <row r="93" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>94</v>
+        <f t="shared" si="1"/>
+        <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>86</v>
@@ -4342,7 +4508,7 @@
       <c r="H93" s="1">
         <v>1849</v>
       </c>
-      <c r="K93">
+      <c r="K93" s="16">
         <v>7015</v>
       </c>
       <c r="L93" s="8" t="s">
@@ -4352,9 +4518,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="17.25" customHeight="1">
+    <row r="94" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>95</v>
+        <f t="shared" si="1"/>
+        <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>86</v>
@@ -4378,7 +4545,7 @@
         <v>1849</v>
       </c>
       <c r="I94" s="13"/>
-      <c r="K94">
+      <c r="K94" s="16">
         <v>7015</v>
       </c>
       <c r="L94" s="8" t="s">
@@ -4388,9 +4555,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="17.25" customHeight="1">
+    <row r="95" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>96</v>
+        <f t="shared" si="1"/>
+        <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>86</v>
@@ -4413,7 +4581,7 @@
       <c r="H95" s="1">
         <v>1849</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="16">
         <v>7015</v>
       </c>
       <c r="L95" s="8" t="s">
@@ -4423,9 +4591,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="17.25" customHeight="1">
+    <row r="96" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>97</v>
+        <f t="shared" si="1"/>
+        <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>88</v>
@@ -4458,9 +4627,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="17.25" customHeight="1">
+    <row r="97" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>98</v>
+        <f t="shared" si="1"/>
+        <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>90</v>
@@ -4483,7 +4653,7 @@
       <c r="H97" s="1">
         <v>1757</v>
       </c>
-      <c r="K97" s="14" t="s">
+      <c r="K97" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L97" s="8" t="s">
@@ -4493,9 +4663,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="17.25" customHeight="1">
+    <row r="98" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>99</v>
+        <f t="shared" si="1"/>
+        <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>92</v>
@@ -4518,7 +4689,7 @@
       <c r="H98" s="1">
         <v>2332</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="16">
         <v>8990</v>
       </c>
       <c r="L98" s="8" t="s">
@@ -4528,9 +4699,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="17.25" customHeight="1">
+    <row r="99" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>94</v>
@@ -4553,7 +4725,7 @@
       <c r="H99" s="1">
         <v>1757</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="16">
         <v>9982</v>
       </c>
       <c r="L99" s="8" t="s">
@@ -4563,9 +4735,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="17.25" customHeight="1">
+    <row r="100" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>101</v>
+        <f t="shared" si="1"/>
+        <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>96</v>
@@ -4588,7 +4761,7 @@
       <c r="H100" s="1">
         <v>2565</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="16">
         <v>4040</v>
       </c>
       <c r="L100" s="8" t="s">
@@ -4598,9 +4771,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="17.25" customHeight="1">
+    <row r="101" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>102</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>96</v>
@@ -4623,7 +4797,7 @@
       <c r="H101" s="1">
         <v>2216</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="16">
         <v>4040</v>
       </c>
       <c r="L101" s="8" t="s">
@@ -4633,9 +4807,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="17.25" customHeight="1">
+    <row r="102" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>103</v>
+        <f t="shared" si="1"/>
+        <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>96</v>
@@ -4658,7 +4833,7 @@
       <c r="H102" s="1">
         <v>2032</v>
       </c>
-      <c r="K102">
+      <c r="K102" s="16">
         <v>4040</v>
       </c>
       <c r="L102" s="8" t="s">
@@ -4668,9 +4843,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="17.25" customHeight="1">
+    <row r="103" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>104</v>
+        <f t="shared" si="1"/>
+        <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>96</v>
@@ -4693,7 +4869,7 @@
       <c r="H103" s="1">
         <v>2216</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="16">
         <v>4040</v>
       </c>
       <c r="L103" s="8" t="s">
@@ -4703,9 +4879,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="17.25" customHeight="1">
+    <row r="104" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>105</v>
+        <f t="shared" si="1"/>
+        <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>96</v>
@@ -4728,7 +4905,7 @@
       <c r="H104" s="1">
         <v>2216</v>
       </c>
-      <c r="K104">
+      <c r="K104" s="16">
         <v>4040</v>
       </c>
       <c r="L104" s="8" t="s">
@@ -4738,9 +4915,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="17.25" customHeight="1">
+    <row r="105" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>106</v>
+        <f t="shared" si="1"/>
+        <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>75</v>
@@ -4763,7 +4941,7 @@
       <c r="H105" s="1">
         <v>2681</v>
       </c>
-      <c r="K105">
+      <c r="K105" s="16">
         <v>6262</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -4773,9 +4951,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="17.25" customHeight="1">
+    <row r="106" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>107</v>
+        <f t="shared" si="1"/>
+        <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>75</v>
@@ -4798,7 +4977,7 @@
       <c r="H106" s="1">
         <v>2449</v>
       </c>
-      <c r="K106">
+      <c r="K106" s="16">
         <v>6262</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -4808,9 +4987,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="17.25" customHeight="1">
+    <row r="107" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>108</v>
+        <f t="shared" si="1"/>
+        <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>75</v>
@@ -4833,7 +5013,7 @@
       <c r="H107" s="1">
         <v>2449</v>
       </c>
-      <c r="K107">
+      <c r="K107" s="16">
         <v>6262</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -4843,9 +5023,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="17.25" customHeight="1">
+    <row r="108" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>109</v>
+        <f t="shared" si="1"/>
+        <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>76</v>
@@ -4868,7 +5049,7 @@
       <c r="H108" s="1">
         <v>1849</v>
       </c>
-      <c r="K108">
+      <c r="K108" s="16">
         <v>6919</v>
       </c>
       <c r="L108" s="8" t="s">
@@ -4878,9 +5059,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="17.25" customHeight="1">
+    <row r="109" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>110</v>
+        <f t="shared" si="1"/>
+        <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>76</v>
@@ -4903,7 +5085,7 @@
       <c r="H109" s="1">
         <v>2216</v>
       </c>
-      <c r="K109">
+      <c r="K109" s="16">
         <v>6919</v>
       </c>
       <c r="L109" s="8" t="s">
@@ -4913,9 +5095,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="17.25" customHeight="1">
+    <row r="110" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>111</v>
+        <f t="shared" si="1"/>
+        <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>76</v>
@@ -4938,7 +5121,7 @@
       <c r="H110" s="1">
         <v>2032</v>
       </c>
-      <c r="K110">
+      <c r="K110" s="16">
         <v>6919</v>
       </c>
       <c r="L110" s="8" t="s">
@@ -4948,9 +5131,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="17.25" customHeight="1">
+    <row r="111" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>112</v>
+        <f t="shared" si="1"/>
+        <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>78</v>
@@ -4973,7 +5157,7 @@
       <c r="H111" s="1">
         <v>3233</v>
       </c>
-      <c r="K111">
+      <c r="K111" s="16">
         <v>6919</v>
       </c>
       <c r="L111" s="8" t="s">
@@ -4983,9 +5167,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="17.25" customHeight="1">
+    <row r="112" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>113</v>
+        <f t="shared" si="1"/>
+        <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>82</v>
@@ -5008,7 +5193,7 @@
       <c r="H112" s="1">
         <v>2032</v>
       </c>
-      <c r="K112">
+      <c r="K112" s="16">
         <v>3020</v>
       </c>
       <c r="L112" s="8" t="s">
@@ -5018,9 +5203,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="17.25" customHeight="1">
+    <row r="113" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>114</v>
+        <f t="shared" si="1"/>
+        <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>82</v>
@@ -5043,7 +5229,7 @@
       <c r="H113" s="1">
         <v>2032</v>
       </c>
-      <c r="K113">
+      <c r="K113" s="16">
         <v>3020</v>
       </c>
       <c r="L113" s="8" t="s">
@@ -5053,9 +5239,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="17.25" customHeight="1">
+    <row r="114" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>115</v>
+        <f t="shared" si="1"/>
+        <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>82</v>
@@ -5078,7 +5265,7 @@
       <c r="H114" s="1">
         <v>2032</v>
       </c>
-      <c r="K114">
+      <c r="K114" s="16">
         <v>3020</v>
       </c>
       <c r="L114" s="8" t="s">
@@ -5088,9 +5275,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="17.25" customHeight="1">
+    <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>116</v>
+        <f t="shared" si="1"/>
+        <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>84</v>
@@ -5113,7 +5301,7 @@
       <c r="H115" s="1">
         <v>1757</v>
       </c>
-      <c r="K115">
+      <c r="K115" s="16">
         <v>1615</v>
       </c>
       <c r="L115" s="8" t="s">
@@ -5123,9 +5311,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="17.25" customHeight="1">
+    <row r="116" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>117</v>
+        <f t="shared" si="1"/>
+        <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>84</v>
@@ -5148,7 +5337,7 @@
       <c r="H116" s="1">
         <v>1849</v>
       </c>
-      <c r="K116">
+      <c r="K116" s="16">
         <v>7015</v>
       </c>
       <c r="L116" s="8" t="s">
@@ -5158,9 +5347,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="17.25" customHeight="1">
+    <row r="117" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>118</v>
+        <f t="shared" si="1"/>
+        <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>84</v>
@@ -5189,7 +5379,7 @@
       <c r="J117" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K117">
+      <c r="K117" s="16">
         <v>7015</v>
       </c>
       <c r="L117" s="8" t="s">
@@ -5199,9 +5389,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="17.25" customHeight="1">
+    <row r="118" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>119</v>
+        <f t="shared" si="1"/>
+        <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>84</v>
@@ -5224,7 +5415,7 @@
       <c r="H118" s="1">
         <v>1849</v>
       </c>
-      <c r="K118">
+      <c r="K118" s="16">
         <v>7015</v>
       </c>
       <c r="L118" s="8" t="s">
@@ -5234,9 +5425,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="17.25" customHeight="1">
+    <row r="119" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>120</v>
+        <f t="shared" si="1"/>
+        <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>84</v>
@@ -5259,7 +5451,7 @@
       <c r="H119" s="1">
         <v>1849</v>
       </c>
-      <c r="K119">
+      <c r="K119" s="16">
         <v>7015</v>
       </c>
       <c r="L119" s="8" t="s">
@@ -5269,9 +5461,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="17.25" customHeight="1">
+    <row r="120" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>121</v>
+        <f t="shared" si="1"/>
+        <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>84</v>
@@ -5294,7 +5487,7 @@
       <c r="H120" s="1">
         <v>1849</v>
       </c>
-      <c r="K120">
+      <c r="K120" s="16">
         <v>7015</v>
       </c>
       <c r="L120" s="8" t="s">
@@ -5304,9 +5497,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="17.25" customHeight="1">
+    <row r="121" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>122</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>84</v>
@@ -5329,7 +5523,7 @@
       <c r="H121" s="1">
         <v>1849</v>
       </c>
-      <c r="K121">
+      <c r="K121" s="16">
         <v>7015</v>
       </c>
       <c r="L121" s="8" t="s">
@@ -5339,9 +5533,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="17.25" customHeight="1">
+    <row r="122" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>123</v>
+        <f t="shared" si="1"/>
+        <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>86</v>
@@ -5364,7 +5559,7 @@
       <c r="H122" s="1">
         <v>2449</v>
       </c>
-      <c r="K122">
+      <c r="K122" s="16">
         <v>7015</v>
       </c>
       <c r="L122" s="8" t="s">
@@ -5374,9 +5569,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="17.25" customHeight="1">
+    <row r="123" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>124</v>
+        <f t="shared" si="1"/>
+        <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>86</v>
@@ -5399,7 +5595,7 @@
       <c r="H123" s="1">
         <v>1849</v>
       </c>
-      <c r="K123">
+      <c r="K123" s="16">
         <v>7015</v>
       </c>
       <c r="L123" s="8" t="s">
@@ -5409,9 +5605,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="17.25" customHeight="1">
+    <row r="124" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>126</v>
+        <f t="shared" si="1"/>
+        <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>86</v>
@@ -5434,7 +5631,7 @@
       <c r="H124" s="1">
         <v>1940</v>
       </c>
-      <c r="K124">
+      <c r="K124" s="16">
         <v>7015</v>
       </c>
       <c r="L124" s="8" t="s">
@@ -5444,9 +5641,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="17.25" customHeight="1">
+    <row r="125" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>127</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>86</v>
@@ -5469,7 +5667,7 @@
       <c r="H125" s="1">
         <v>1849</v>
       </c>
-      <c r="K125">
+      <c r="K125" s="16">
         <v>7015</v>
       </c>
       <c r="L125" s="8" t="s">
@@ -5479,9 +5677,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="17.25" customHeight="1">
+    <row r="126" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>128</v>
+        <f t="shared" si="1"/>
+        <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>86</v>
@@ -5504,7 +5703,7 @@
       <c r="H126" s="1">
         <v>1849</v>
       </c>
-      <c r="K126">
+      <c r="K126" s="16">
         <v>7015</v>
       </c>
       <c r="L126" s="8" t="s">
@@ -5514,9 +5713,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="17.25" customHeight="1">
+    <row r="127" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>129</v>
+        <f t="shared" si="1"/>
+        <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>86</v>
@@ -5539,7 +5739,7 @@
       <c r="H127" s="1">
         <v>1849</v>
       </c>
-      <c r="K127">
+      <c r="K127" s="16">
         <v>7015</v>
       </c>
       <c r="L127" s="8" t="s">
@@ -5549,9 +5749,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="17.25" customHeight="1">
+    <row r="128" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>130</v>
+        <f t="shared" si="1"/>
+        <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>88</v>
@@ -5584,9 +5785,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="17.25" customHeight="1">
+    <row r="129" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>131</v>
+        <f t="shared" si="1"/>
+        <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>90</v>
@@ -5609,7 +5811,7 @@
       <c r="H129" s="1">
         <v>1757</v>
       </c>
-      <c r="K129" s="14" t="s">
+      <c r="K129" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L129" s="8" t="s">
@@ -5619,9 +5821,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="17.25" customHeight="1">
+    <row r="130" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>92</v>
@@ -5644,7 +5847,7 @@
       <c r="H130" s="1">
         <v>2332</v>
       </c>
-      <c r="K130">
+      <c r="K130" s="16">
         <v>8990</v>
       </c>
       <c r="L130" s="8" t="s">
@@ -5654,9 +5857,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="17.25" customHeight="1">
+    <row r="131" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>133</v>
+        <f t="shared" ref="A131:A194" si="2">ROW()-1</f>
+        <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>94</v>
@@ -5679,7 +5883,7 @@
       <c r="H131" s="1">
         <v>1757</v>
       </c>
-      <c r="K131">
+      <c r="K131" s="16">
         <v>9982</v>
       </c>
       <c r="L131" s="8" t="s">
@@ -5689,9 +5893,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="17.25" customHeight="1">
+    <row r="132" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>134</v>
+        <f t="shared" si="2"/>
+        <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>96</v>
@@ -5714,7 +5919,7 @@
       <c r="H132" s="1">
         <v>2565</v>
       </c>
-      <c r="K132">
+      <c r="K132" s="16">
         <v>4040</v>
       </c>
       <c r="L132" s="8" t="s">
@@ -5724,9 +5929,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="17.25" customHeight="1">
+    <row r="133" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>135</v>
+        <f t="shared" si="2"/>
+        <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>96</v>
@@ -5749,7 +5955,7 @@
       <c r="H133" s="1">
         <v>2216</v>
       </c>
-      <c r="K133">
+      <c r="K133" s="16">
         <v>4040</v>
       </c>
       <c r="L133" s="8" t="s">
@@ -5759,9 +5965,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="17.25" customHeight="1">
+    <row r="134" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>136</v>
+        <f t="shared" si="2"/>
+        <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>96</v>
@@ -5784,7 +5991,7 @@
       <c r="H134" s="1">
         <v>2032</v>
       </c>
-      <c r="K134">
+      <c r="K134" s="16">
         <v>4040</v>
       </c>
       <c r="L134" s="8" t="s">
@@ -5794,9 +6001,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="17.25" customHeight="1">
+    <row r="135" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>137</v>
+        <f t="shared" si="2"/>
+        <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>96</v>
@@ -5819,7 +6027,7 @@
       <c r="H135" s="1">
         <v>2216</v>
       </c>
-      <c r="K135">
+      <c r="K135" s="16">
         <v>4040</v>
       </c>
       <c r="L135" s="8" t="s">
@@ -5829,9 +6037,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="17.25" customHeight="1">
+    <row r="136" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>138</v>
+        <f t="shared" si="2"/>
+        <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>96</v>
@@ -5854,7 +6063,7 @@
       <c r="H136" s="1">
         <v>2216</v>
       </c>
-      <c r="K136">
+      <c r="K136" s="16">
         <v>4040</v>
       </c>
       <c r="L136" s="8" t="s">
@@ -5864,9 +6073,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="17.25" customHeight="1">
+    <row r="137" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>139</v>
+        <f t="shared" si="2"/>
+        <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>75</v>
@@ -5889,7 +6099,7 @@
       <c r="H137" s="1">
         <v>2681</v>
       </c>
-      <c r="K137">
+      <c r="K137" s="16">
         <v>6262</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -5899,9 +6109,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="17.25" customHeight="1">
+    <row r="138" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>140</v>
+        <f t="shared" si="2"/>
+        <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>75</v>
@@ -5930,7 +6141,7 @@
       <c r="J138" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K138">
+      <c r="K138" s="16">
         <v>6262</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -5940,9 +6151,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="17.25" customHeight="1">
+    <row r="139" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>141</v>
+        <f t="shared" si="2"/>
+        <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>75</v>
@@ -5971,7 +6183,7 @@
       <c r="J139" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K139">
+      <c r="K139" s="16">
         <v>6262</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -5981,9 +6193,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="17.25" customHeight="1">
+    <row r="140" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>142</v>
+        <f t="shared" si="2"/>
+        <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>75</v>
@@ -6006,7 +6219,7 @@
       <c r="H140" s="1">
         <v>2449</v>
       </c>
-      <c r="K140">
+      <c r="K140" s="16">
         <v>6262</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -6016,9 +6229,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="17.25" customHeight="1">
+    <row r="141" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>143</v>
+        <f t="shared" si="2"/>
+        <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>76</v>
@@ -6041,7 +6255,7 @@
       <c r="H141" s="1">
         <v>1849</v>
       </c>
-      <c r="K141">
+      <c r="K141" s="16">
         <v>6919</v>
       </c>
       <c r="L141" s="8" t="s">
@@ -6051,9 +6265,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="17.25" customHeight="1">
+    <row r="142" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>144</v>
+        <f t="shared" si="2"/>
+        <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>76</v>
@@ -6079,7 +6294,7 @@
       <c r="I142" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K142">
+      <c r="K142" s="16">
         <v>6919</v>
       </c>
       <c r="L142" s="8" t="s">
@@ -6089,9 +6304,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="17.25" customHeight="1">
+    <row r="143" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>145</v>
+        <f t="shared" si="2"/>
+        <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>76</v>
@@ -6114,7 +6330,7 @@
       <c r="H143" s="1">
         <v>2032</v>
       </c>
-      <c r="K143">
+      <c r="K143" s="16">
         <v>6919</v>
       </c>
       <c r="L143" s="8" t="s">
@@ -6124,9 +6340,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="17.25" customHeight="1">
+    <row r="144" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>146</v>
+        <f t="shared" si="2"/>
+        <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>78</v>
@@ -6149,7 +6366,7 @@
       <c r="H144" s="1">
         <v>3233</v>
       </c>
-      <c r="K144">
+      <c r="K144" s="16">
         <v>6919</v>
       </c>
       <c r="L144" s="8" t="s">
@@ -6159,9 +6376,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="17.25" customHeight="1">
+    <row r="145" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>147</v>
+        <f t="shared" si="2"/>
+        <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>82</v>
@@ -6184,7 +6402,7 @@
       <c r="H145" s="1">
         <v>2032</v>
       </c>
-      <c r="K145">
+      <c r="K145" s="16">
         <v>3020</v>
       </c>
       <c r="L145" s="8" t="s">
@@ -6194,9 +6412,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="17.25" customHeight="1">
+    <row r="146" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>148</v>
+        <f t="shared" si="2"/>
+        <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>82</v>
@@ -6219,7 +6438,7 @@
       <c r="H146" s="1">
         <v>2032</v>
       </c>
-      <c r="K146">
+      <c r="K146" s="16">
         <v>3020</v>
       </c>
       <c r="L146" s="8" t="s">
@@ -6229,9 +6448,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="17.25" customHeight="1">
+    <row r="147" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>149</v>
+        <f t="shared" si="2"/>
+        <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>82</v>
@@ -6254,7 +6474,7 @@
       <c r="H147" s="1">
         <v>2032</v>
       </c>
-      <c r="K147">
+      <c r="K147" s="16">
         <v>3020</v>
       </c>
       <c r="L147" s="8" t="s">
@@ -6264,9 +6484,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="17.25" customHeight="1">
+    <row r="148" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>150</v>
+        <f t="shared" si="2"/>
+        <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>84</v>
@@ -6289,7 +6510,7 @@
       <c r="H148" s="1">
         <v>1757</v>
       </c>
-      <c r="K148">
+      <c r="K148" s="16">
         <v>1615</v>
       </c>
       <c r="L148" s="8" t="s">
@@ -6299,9 +6520,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="17.25" customHeight="1">
+    <row r="149" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>151</v>
+        <f t="shared" si="2"/>
+        <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>84</v>
@@ -6324,7 +6546,7 @@
       <c r="H149" s="1">
         <v>1849</v>
       </c>
-      <c r="K149">
+      <c r="K149" s="16">
         <v>7015</v>
       </c>
       <c r="L149" s="8" t="s">
@@ -6334,9 +6556,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="17.25" customHeight="1">
+    <row r="150" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>152</v>
+        <f t="shared" si="2"/>
+        <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>84</v>
@@ -6365,7 +6588,7 @@
       <c r="J150" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K150">
+      <c r="K150" s="16">
         <v>7015</v>
       </c>
       <c r="L150" s="8" t="s">
@@ -6375,9 +6598,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="17.25" customHeight="1">
+    <row r="151" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>153</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>84</v>
@@ -6400,7 +6624,7 @@
       <c r="H151" s="1">
         <v>1849</v>
       </c>
-      <c r="K151">
+      <c r="K151" s="16">
         <v>7015</v>
       </c>
       <c r="L151" s="8" t="s">
@@ -6410,9 +6634,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="17.25" customHeight="1">
+    <row r="152" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>154</v>
+        <f t="shared" si="2"/>
+        <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>84</v>
@@ -6435,7 +6660,7 @@
       <c r="H152" s="1">
         <v>1849</v>
       </c>
-      <c r="K152">
+      <c r="K152" s="16">
         <v>7015</v>
       </c>
       <c r="L152" s="8" t="s">
@@ -6445,9 +6670,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="17.25" customHeight="1">
+    <row r="153" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>155</v>
+        <f t="shared" si="2"/>
+        <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>84</v>
@@ -6470,7 +6696,7 @@
       <c r="H153" s="1">
         <v>1849</v>
       </c>
-      <c r="K153">
+      <c r="K153" s="16">
         <v>7015</v>
       </c>
       <c r="L153" s="8" t="s">
@@ -6480,9 +6706,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="17.25" customHeight="1">
+    <row r="154" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>156</v>
+        <f t="shared" si="2"/>
+        <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>84</v>
@@ -6505,7 +6732,7 @@
       <c r="H154" s="1">
         <v>1849</v>
       </c>
-      <c r="K154">
+      <c r="K154" s="16">
         <v>7015</v>
       </c>
       <c r="L154" s="8" t="s">
@@ -6515,9 +6742,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="17.25" customHeight="1">
+    <row r="155" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>157</v>
+        <f t="shared" si="2"/>
+        <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>86</v>
@@ -6540,7 +6768,7 @@
       <c r="H155" s="1">
         <v>2449</v>
       </c>
-      <c r="K155">
+      <c r="K155" s="16">
         <v>7015</v>
       </c>
       <c r="L155" s="8" t="s">
@@ -6550,9 +6778,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="17.25" customHeight="1">
+    <row r="156" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>158</v>
+        <f t="shared" si="2"/>
+        <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>86</v>
@@ -6575,7 +6804,7 @@
       <c r="H156" s="1">
         <v>1849</v>
       </c>
-      <c r="K156">
+      <c r="K156" s="16">
         <v>7015</v>
       </c>
       <c r="L156" s="8" t="s">
@@ -6585,9 +6814,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="17.25" customHeight="1">
+    <row r="157" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>159</v>
+        <f t="shared" si="2"/>
+        <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>86</v>
@@ -6616,7 +6846,7 @@
       <c r="J157" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K157">
+      <c r="K157" s="16">
         <v>7015</v>
       </c>
       <c r="L157" s="8" t="s">
@@ -6626,9 +6856,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="17.25" customHeight="1">
+    <row r="158" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>160</v>
+        <f t="shared" si="2"/>
+        <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>86</v>
@@ -6651,7 +6882,7 @@
       <c r="H158" s="1">
         <v>1940</v>
       </c>
-      <c r="K158">
+      <c r="K158" s="16">
         <v>7015</v>
       </c>
       <c r="L158" s="8" t="s">
@@ -6661,9 +6892,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="17.25" customHeight="1">
+    <row r="159" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>161</v>
+        <f t="shared" si="2"/>
+        <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>86</v>
@@ -6686,7 +6918,7 @@
       <c r="H159" s="1">
         <v>1849</v>
       </c>
-      <c r="K159">
+      <c r="K159" s="16">
         <v>7015</v>
       </c>
       <c r="L159" s="8" t="s">
@@ -6696,9 +6928,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="17.25" customHeight="1">
+    <row r="160" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>162</v>
+        <f t="shared" si="2"/>
+        <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>86</v>
@@ -6721,7 +6954,7 @@
       <c r="H160" s="1">
         <v>1849</v>
       </c>
-      <c r="K160">
+      <c r="K160" s="16">
         <v>7015</v>
       </c>
       <c r="L160" s="8" t="s">
@@ -6731,9 +6964,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="17.25" customHeight="1">
+    <row r="161" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>163</v>
+        <f t="shared" si="2"/>
+        <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>86</v>
@@ -6756,7 +6990,7 @@
       <c r="H161" s="1">
         <v>1849</v>
       </c>
-      <c r="K161">
+      <c r="K161" s="16">
         <v>7015</v>
       </c>
       <c r="L161" s="8" t="s">
@@ -6766,9 +7000,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="17.25" customHeight="1">
+    <row r="162" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>164</v>
+        <f t="shared" si="2"/>
+        <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>88</v>
@@ -6801,9 +7036,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="17.25" customHeight="1">
+    <row r="163" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>165</v>
+        <f t="shared" si="2"/>
+        <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>90</v>
@@ -6826,7 +7062,7 @@
       <c r="H163" s="1">
         <v>1757</v>
       </c>
-      <c r="K163" s="14" t="s">
+      <c r="K163" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L163" s="8" t="s">
@@ -6836,9 +7072,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="17.25" customHeight="1">
+    <row r="164" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>166</v>
+        <f t="shared" si="2"/>
+        <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>92</v>
@@ -6861,7 +7098,7 @@
       <c r="H164" s="1">
         <v>2332</v>
       </c>
-      <c r="K164">
+      <c r="K164" s="16">
         <v>8990</v>
       </c>
       <c r="L164" s="8" t="s">
@@ -6871,9 +7108,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="17.25" customHeight="1">
+    <row r="165" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>167</v>
+        <f t="shared" si="2"/>
+        <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>94</v>
@@ -6896,7 +7134,7 @@
       <c r="H165" s="1">
         <v>1757</v>
       </c>
-      <c r="K165">
+      <c r="K165" s="16">
         <v>9982</v>
       </c>
       <c r="L165" s="8" t="s">
@@ -6906,9 +7144,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="17.25" customHeight="1">
+    <row r="166" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>168</v>
+        <f t="shared" si="2"/>
+        <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>96</v>
@@ -6931,7 +7170,7 @@
       <c r="H166" s="1">
         <v>2565</v>
       </c>
-      <c r="K166">
+      <c r="K166" s="16">
         <v>4040</v>
       </c>
       <c r="L166" s="8" t="s">
@@ -6941,9 +7180,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="17.25" customHeight="1">
+    <row r="167" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>169</v>
+        <f t="shared" si="2"/>
+        <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>96</v>
@@ -6966,7 +7206,7 @@
       <c r="H167" s="1">
         <v>2216</v>
       </c>
-      <c r="K167">
+      <c r="K167" s="16">
         <v>4040</v>
       </c>
       <c r="L167" s="8" t="s">
@@ -6976,9 +7216,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="17.25" customHeight="1">
+    <row r="168" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>170</v>
+        <f t="shared" si="2"/>
+        <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>96</v>
@@ -7001,7 +7242,7 @@
       <c r="H168" s="1">
         <v>2032</v>
       </c>
-      <c r="K168">
+      <c r="K168" s="16">
         <v>4040</v>
       </c>
       <c r="L168" s="8" t="s">
@@ -7011,9 +7252,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="17.25" customHeight="1">
+    <row r="169" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>171</v>
+        <f t="shared" si="2"/>
+        <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>96</v>
@@ -7036,7 +7278,7 @@
       <c r="H169" s="1">
         <v>2216</v>
       </c>
-      <c r="K169">
+      <c r="K169" s="16">
         <v>4040</v>
       </c>
       <c r="L169" s="8" t="s">
@@ -7046,9 +7288,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="17.25" customHeight="1">
+    <row r="170" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>172</v>
+        <f t="shared" si="2"/>
+        <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>96</v>
@@ -7071,7 +7314,7 @@
       <c r="H170" s="1">
         <v>2216</v>
       </c>
-      <c r="K170">
+      <c r="K170" s="16">
         <v>4040</v>
       </c>
       <c r="L170" s="8" t="s">
@@ -7081,9 +7324,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="17.25" customHeight="1">
+    <row r="171" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>173</v>
+        <f t="shared" si="2"/>
+        <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>75</v>
@@ -7106,7 +7350,7 @@
       <c r="H171" s="1">
         <v>2681</v>
       </c>
-      <c r="K171">
+      <c r="K171" s="16">
         <v>6262</v>
       </c>
       <c r="L171" s="1" t="s">
@@ -7116,9 +7360,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="17.25" customHeight="1">
+    <row r="172" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>174</v>
+        <f t="shared" si="2"/>
+        <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>75</v>
@@ -7141,7 +7386,7 @@
       <c r="H172" s="1">
         <v>2332</v>
       </c>
-      <c r="K172">
+      <c r="K172" s="16">
         <v>6262</v>
       </c>
       <c r="L172" s="1" t="s">
@@ -7151,9 +7396,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="17.25" customHeight="1">
+    <row r="173" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>175</v>
+        <f t="shared" si="2"/>
+        <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>75</v>
@@ -7176,7 +7422,7 @@
       <c r="H173" s="1">
         <v>2449</v>
       </c>
-      <c r="K173">
+      <c r="K173" s="16">
         <v>6262</v>
       </c>
       <c r="L173" s="1" t="s">
@@ -7186,9 +7432,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="17.25" customHeight="1">
+    <row r="174" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>176</v>
+        <f t="shared" si="2"/>
+        <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>76</v>
@@ -7211,7 +7458,7 @@
       <c r="H174" s="1">
         <v>1849</v>
       </c>
-      <c r="K174">
+      <c r="K174" s="16">
         <v>6919</v>
       </c>
       <c r="L174" s="8" t="s">
@@ -7221,9 +7468,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="17.25" customHeight="1">
+    <row r="175" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>177</v>
+        <f t="shared" si="2"/>
+        <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>76</v>
@@ -7246,7 +7494,7 @@
       <c r="H175" s="1">
         <v>2332</v>
       </c>
-      <c r="K175">
+      <c r="K175" s="16">
         <v>6919</v>
       </c>
       <c r="L175" s="8" t="s">
@@ -7256,9 +7504,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="17.25" customHeight="1">
+    <row r="176" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>178</v>
+        <f t="shared" si="2"/>
+        <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>76</v>
@@ -7281,7 +7530,7 @@
       <c r="H176" s="1">
         <v>2032</v>
       </c>
-      <c r="K176">
+      <c r="K176" s="16">
         <v>6919</v>
       </c>
       <c r="L176" s="8" t="s">
@@ -7291,9 +7540,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="17.25" customHeight="1">
+    <row r="177" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>179</v>
+        <f t="shared" si="2"/>
+        <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>78</v>
@@ -7316,7 +7566,7 @@
       <c r="H177" s="1">
         <v>3233</v>
       </c>
-      <c r="K177">
+      <c r="K177" s="16">
         <v>6919</v>
       </c>
       <c r="L177" s="8" t="s">
@@ -7326,9 +7576,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="17.25" customHeight="1">
+    <row r="178" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>180</v>
+        <f t="shared" si="2"/>
+        <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>82</v>
@@ -7351,7 +7602,7 @@
       <c r="H178" s="1">
         <v>2032</v>
       </c>
-      <c r="K178">
+      <c r="K178" s="16">
         <v>3020</v>
       </c>
       <c r="L178" s="8" t="s">
@@ -7361,9 +7612,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="17.25" customHeight="1">
+    <row r="179" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>181</v>
+        <f t="shared" si="2"/>
+        <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>82</v>
@@ -7386,7 +7638,7 @@
       <c r="H179" s="1">
         <v>2032</v>
       </c>
-      <c r="K179">
+      <c r="K179" s="16">
         <v>3020</v>
       </c>
       <c r="L179" s="8" t="s">
@@ -7396,9 +7648,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="17.25" customHeight="1">
+    <row r="180" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>182</v>
+        <f t="shared" si="2"/>
+        <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>82</v>
@@ -7421,7 +7674,7 @@
       <c r="H180" s="1">
         <v>2032</v>
       </c>
-      <c r="K180">
+      <c r="K180" s="16">
         <v>3020</v>
       </c>
       <c r="L180" s="8" t="s">
@@ -7431,9 +7684,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="17.25" customHeight="1">
+    <row r="181" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>183</v>
+        <f t="shared" si="2"/>
+        <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>84</v>
@@ -7456,7 +7710,7 @@
       <c r="H181" s="1">
         <v>1757</v>
       </c>
-      <c r="K181">
+      <c r="K181" s="16">
         <v>1615</v>
       </c>
       <c r="L181" s="8" t="s">
@@ -7466,9 +7720,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="17.25" customHeight="1">
+    <row r="182" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>184</v>
+        <f t="shared" si="2"/>
+        <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>84</v>
@@ -7491,7 +7746,7 @@
       <c r="H182" s="1">
         <v>1849</v>
       </c>
-      <c r="K182">
+      <c r="K182" s="16">
         <v>7015</v>
       </c>
       <c r="L182" s="8" t="s">
@@ -7501,9 +7756,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="17.25" customHeight="1">
+    <row r="183" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>185</v>
+        <f t="shared" si="2"/>
+        <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>84</v>
@@ -7526,7 +7782,7 @@
       <c r="H183" s="1">
         <v>1849</v>
       </c>
-      <c r="K183">
+      <c r="K183" s="16">
         <v>7015</v>
       </c>
       <c r="L183" s="8" t="s">
@@ -7536,9 +7792,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="17.25" customHeight="1">
+    <row r="184" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>186</v>
+        <f t="shared" si="2"/>
+        <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>84</v>
@@ -7561,7 +7818,7 @@
       <c r="H184" s="1">
         <v>1849</v>
       </c>
-      <c r="K184">
+      <c r="K184" s="16">
         <v>7015</v>
       </c>
       <c r="L184" s="8" t="s">
@@ -7571,9 +7828,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="17.25" customHeight="1">
+    <row r="185" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>187</v>
+        <f t="shared" si="2"/>
+        <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>84</v>
@@ -7596,7 +7854,7 @@
       <c r="H185" s="1">
         <v>1849</v>
       </c>
-      <c r="K185">
+      <c r="K185" s="16">
         <v>7015</v>
       </c>
       <c r="L185" s="8" t="s">
@@ -7606,9 +7864,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="17.25" customHeight="1">
+    <row r="186" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>84</v>
@@ -7631,7 +7890,7 @@
       <c r="H186" s="1">
         <v>1849</v>
       </c>
-      <c r="K186">
+      <c r="K186" s="16">
         <v>7015</v>
       </c>
       <c r="L186" s="8" t="s">
@@ -7641,9 +7900,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="17.25" customHeight="1">
+    <row r="187" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>189</v>
+        <f t="shared" si="2"/>
+        <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>84</v>
@@ -7666,7 +7926,7 @@
       <c r="H187" s="1">
         <v>1849</v>
       </c>
-      <c r="K187">
+      <c r="K187" s="16">
         <v>7015</v>
       </c>
       <c r="L187" s="8" t="s">
@@ -7676,9 +7936,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="17.25" customHeight="1">
+    <row r="188" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>190</v>
+        <f t="shared" si="2"/>
+        <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>86</v>
@@ -7701,7 +7962,7 @@
       <c r="H188" s="1">
         <v>2449</v>
       </c>
-      <c r="K188">
+      <c r="K188" s="16">
         <v>7015</v>
       </c>
       <c r="L188" s="8" t="s">
@@ -7711,9 +7972,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="17.25" customHeight="1">
+    <row r="189" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>191</v>
+        <f t="shared" si="2"/>
+        <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>86</v>
@@ -7736,7 +7998,7 @@
       <c r="H189" s="1">
         <v>1849</v>
       </c>
-      <c r="K189">
+      <c r="K189" s="16">
         <v>7015</v>
       </c>
       <c r="L189" s="8" t="s">
@@ -7746,9 +8008,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="190" spans="1:13" ht="17.25" customHeight="1">
+    <row r="190" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>192</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>86</v>
@@ -7771,7 +8034,7 @@
       <c r="H190" s="1">
         <v>1849</v>
       </c>
-      <c r="K190">
+      <c r="K190" s="16">
         <v>7015</v>
       </c>
       <c r="L190" s="8" t="s">
@@ -7781,9 +8044,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="17.25" customHeight="1">
+    <row r="191" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>193</v>
+        <f t="shared" si="2"/>
+        <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>86</v>
@@ -7806,7 +8070,7 @@
       <c r="H191" s="1">
         <v>1940</v>
       </c>
-      <c r="K191">
+      <c r="K191" s="16">
         <v>7015</v>
       </c>
       <c r="L191" s="8" t="s">
@@ -7816,9 +8080,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="17.25" customHeight="1">
+    <row r="192" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>194</v>
+        <f t="shared" si="2"/>
+        <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>86</v>
@@ -7841,7 +8106,7 @@
       <c r="H192" s="1">
         <v>1849</v>
       </c>
-      <c r="K192">
+      <c r="K192" s="16">
         <v>7015</v>
       </c>
       <c r="L192" s="8" t="s">
@@ -7851,9 +8116,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="17.25" customHeight="1">
+    <row r="193" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>195</v>
+        <f t="shared" si="2"/>
+        <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>86</v>
@@ -7876,7 +8142,7 @@
       <c r="H193" s="1">
         <v>1849</v>
       </c>
-      <c r="K193">
+      <c r="K193" s="16">
         <v>7015</v>
       </c>
       <c r="L193" s="8" t="s">
@@ -7886,9 +8152,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="17.25" customHeight="1">
+    <row r="194" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>196</v>
+        <f t="shared" si="2"/>
+        <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>86</v>
@@ -7911,7 +8178,7 @@
       <c r="H194" s="1">
         <v>1849</v>
       </c>
-      <c r="K194">
+      <c r="K194" s="16">
         <v>7015</v>
       </c>
       <c r="L194" s="8" t="s">
@@ -7921,9 +8188,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="17.25" customHeight="1">
+    <row r="195" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>197</v>
+        <f t="shared" ref="A195:A258" si="3">ROW()-1</f>
+        <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>88</v>
@@ -7962,9 +8230,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="17.25" customHeight="1">
+    <row r="196" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>198</v>
+        <f t="shared" si="3"/>
+        <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>90</v>
@@ -7987,7 +8256,7 @@
       <c r="H196" s="1">
         <v>1757</v>
       </c>
-      <c r="K196" s="14" t="s">
+      <c r="K196" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L196" s="8" t="s">
@@ -7997,9 +8266,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="17.25" customHeight="1">
+    <row r="197" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>199</v>
+        <f t="shared" si="3"/>
+        <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>92</v>
@@ -8022,7 +8292,7 @@
       <c r="H197" s="1">
         <v>2332</v>
       </c>
-      <c r="K197">
+      <c r="K197" s="16">
         <v>8990</v>
       </c>
       <c r="L197" s="8" t="s">
@@ -8032,9 +8302,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="17.25" customHeight="1">
+    <row r="198" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>200</v>
+        <f t="shared" si="3"/>
+        <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>94</v>
@@ -8057,7 +8328,7 @@
       <c r="H198" s="1">
         <v>1757</v>
       </c>
-      <c r="K198">
+      <c r="K198" s="16">
         <v>9982</v>
       </c>
       <c r="L198" s="8" t="s">
@@ -8067,9 +8338,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="17.25" customHeight="1">
+    <row r="199" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>201</v>
+        <f t="shared" si="3"/>
+        <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>96</v>
@@ -8092,7 +8364,7 @@
       <c r="H199" s="1">
         <v>2565</v>
       </c>
-      <c r="K199" s="15" t="s">
+      <c r="K199" s="18" t="s">
         <v>110</v>
       </c>
       <c r="L199" s="8" t="s">
@@ -8102,9 +8374,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="17.25" customHeight="1">
+    <row r="200" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>202</v>
+        <f t="shared" si="3"/>
+        <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>96</v>
@@ -8127,7 +8400,7 @@
       <c r="H200" s="1">
         <v>2216</v>
       </c>
-      <c r="K200" s="15" t="s">
+      <c r="K200" s="18" t="s">
         <v>110</v>
       </c>
       <c r="L200" s="8" t="s">
@@ -8137,9 +8410,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="17.25" customHeight="1">
+    <row r="201" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>203</v>
+        <f t="shared" si="3"/>
+        <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>96</v>
@@ -8162,7 +8436,7 @@
       <c r="H201" s="1">
         <v>2032</v>
       </c>
-      <c r="K201" s="15" t="s">
+      <c r="K201" s="18" t="s">
         <v>110</v>
       </c>
       <c r="L201" s="8" t="s">
@@ -8172,9 +8446,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="17.25" customHeight="1">
+    <row r="202" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>204</v>
+        <f t="shared" si="3"/>
+        <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>96</v>
@@ -8197,7 +8472,7 @@
       <c r="H202" s="1">
         <v>2216</v>
       </c>
-      <c r="K202" s="15" t="s">
+      <c r="K202" s="18" t="s">
         <v>110</v>
       </c>
       <c r="L202" s="8" t="s">
@@ -8207,9 +8482,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="17.25" customHeight="1">
+    <row r="203" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>96</v>
@@ -8232,7 +8508,7 @@
       <c r="H203" s="1">
         <v>2216</v>
       </c>
-      <c r="K203" s="15" t="s">
+      <c r="K203" s="18" t="s">
         <v>110</v>
       </c>
       <c r="L203" s="8" t="s">
@@ -8242,9 +8518,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="17.25" customHeight="1">
+    <row r="204" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>206</v>
+        <f t="shared" si="3"/>
+        <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>75</v>
@@ -8267,7 +8544,7 @@
       <c r="H204" s="1">
         <v>2681</v>
       </c>
-      <c r="K204">
+      <c r="K204" s="16">
         <v>6262</v>
       </c>
       <c r="L204" s="1" t="s">
@@ -8277,9 +8554,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="17.25" customHeight="1">
+    <row r="205" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>207</v>
+        <f t="shared" si="3"/>
+        <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>75</v>
@@ -8302,7 +8580,7 @@
       <c r="H205" s="1">
         <v>2332</v>
       </c>
-      <c r="K205">
+      <c r="K205" s="16">
         <v>6262</v>
       </c>
       <c r="L205" s="1" t="s">
@@ -8312,9 +8590,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="17.25" customHeight="1">
+    <row r="206" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>208</v>
+        <f t="shared" si="3"/>
+        <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>75</v>
@@ -8337,7 +8616,7 @@
       <c r="H206" s="1">
         <v>2449</v>
       </c>
-      <c r="K206">
+      <c r="K206" s="16">
         <v>6262</v>
       </c>
       <c r="L206" s="1" t="s">
@@ -8347,9 +8626,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="17.25" customHeight="1">
+    <row r="207" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>209</v>
+        <f t="shared" si="3"/>
+        <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>76</v>
@@ -8372,7 +8652,7 @@
       <c r="H207" s="1">
         <v>1849</v>
       </c>
-      <c r="K207">
+      <c r="K207" s="16">
         <v>6919</v>
       </c>
       <c r="L207" s="8" t="s">
@@ -8382,9 +8662,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="17.25" customHeight="1">
+    <row r="208" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>210</v>
+        <f t="shared" si="3"/>
+        <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>76</v>
@@ -8407,7 +8688,7 @@
       <c r="H208" s="1">
         <v>2332</v>
       </c>
-      <c r="K208">
+      <c r="K208" s="16">
         <v>6919</v>
       </c>
       <c r="L208" s="8" t="s">
@@ -8417,9 +8698,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="17.25" customHeight="1">
+    <row r="209" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>211</v>
+        <f t="shared" si="3"/>
+        <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>76</v>
@@ -8442,7 +8724,7 @@
       <c r="H209" s="1">
         <v>2032</v>
       </c>
-      <c r="K209">
+      <c r="K209" s="16">
         <v>6919</v>
       </c>
       <c r="L209" s="8" t="s">
@@ -8452,9 +8734,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="17.25" customHeight="1">
+    <row r="210" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>212</v>
+        <f t="shared" si="3"/>
+        <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>78</v>
@@ -8477,7 +8760,7 @@
       <c r="H210" s="1">
         <v>3233</v>
       </c>
-      <c r="K210">
+      <c r="K210" s="16">
         <v>6919</v>
       </c>
       <c r="L210" s="8" t="s">
@@ -8487,9 +8770,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="17.25" customHeight="1">
+    <row r="211" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>213</v>
+        <f t="shared" si="3"/>
+        <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>82</v>
@@ -8512,7 +8796,7 @@
       <c r="H211" s="1">
         <v>2032</v>
       </c>
-      <c r="K211">
+      <c r="K211" s="16">
         <v>3020</v>
       </c>
       <c r="L211" s="8" t="s">
@@ -8522,9 +8806,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="17.25" customHeight="1">
+    <row r="212" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>82</v>
@@ -8547,7 +8832,7 @@
       <c r="H212" s="1">
         <v>2032</v>
       </c>
-      <c r="K212">
+      <c r="K212" s="16">
         <v>3020</v>
       </c>
       <c r="L212" s="8" t="s">
@@ -8557,9 +8842,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="213" spans="1:13" ht="17.25" customHeight="1">
+    <row r="213" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>215</v>
+        <f t="shared" si="3"/>
+        <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>82</v>
@@ -8582,7 +8868,7 @@
       <c r="H213" s="1">
         <v>2032</v>
       </c>
-      <c r="K213">
+      <c r="K213" s="16">
         <v>3020</v>
       </c>
       <c r="L213" s="8" t="s">
@@ -8592,9 +8878,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="17.25" customHeight="1">
+    <row r="214" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>216</v>
+        <f t="shared" si="3"/>
+        <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>84</v>
@@ -8617,7 +8904,7 @@
       <c r="H214" s="1">
         <v>1757</v>
       </c>
-      <c r="K214">
+      <c r="K214" s="16">
         <v>1615</v>
       </c>
       <c r="L214" s="8" t="s">
@@ -8627,9 +8914,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="17.25" customHeight="1">
+    <row r="215" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>217</v>
+        <f t="shared" si="3"/>
+        <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>84</v>
@@ -8652,7 +8940,7 @@
       <c r="H215" s="1">
         <v>1849</v>
       </c>
-      <c r="K215">
+      <c r="K215" s="16">
         <v>7015</v>
       </c>
       <c r="L215" s="8" t="s">
@@ -8662,9 +8950,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="17.25" customHeight="1">
+    <row r="216" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>218</v>
+        <f t="shared" si="3"/>
+        <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>84</v>
@@ -8687,7 +8976,7 @@
       <c r="H216" s="1">
         <v>1849</v>
       </c>
-      <c r="K216">
+      <c r="K216" s="16">
         <v>7015</v>
       </c>
       <c r="L216" s="8" t="s">
@@ -8697,9 +8986,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="217" spans="1:13" ht="17.25" customHeight="1">
+    <row r="217" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>219</v>
+        <f t="shared" si="3"/>
+        <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>84</v>
@@ -8722,7 +9012,7 @@
       <c r="H217" s="1">
         <v>1849</v>
       </c>
-      <c r="K217">
+      <c r="K217" s="16">
         <v>7015</v>
       </c>
       <c r="L217" s="8" t="s">
@@ -8732,9 +9022,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="218" spans="1:13" ht="17.25" customHeight="1">
+    <row r="218" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>220</v>
+        <f t="shared" si="3"/>
+        <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>84</v>
@@ -8757,7 +9048,7 @@
       <c r="H218" s="1">
         <v>1849</v>
       </c>
-      <c r="K218">
+      <c r="K218" s="16">
         <v>7015</v>
       </c>
       <c r="L218" s="8" t="s">
@@ -8767,9 +9058,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="17.25" customHeight="1">
+    <row r="219" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>221</v>
+        <f t="shared" si="3"/>
+        <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>84</v>
@@ -8792,7 +9084,7 @@
       <c r="H219" s="1">
         <v>1849</v>
       </c>
-      <c r="K219">
+      <c r="K219" s="16">
         <v>7015</v>
       </c>
       <c r="L219" s="8" t="s">
@@ -8802,9 +9094,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="220" spans="1:13" ht="17.25" customHeight="1">
+    <row r="220" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>222</v>
+        <f t="shared" si="3"/>
+        <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>84</v>
@@ -8827,7 +9120,7 @@
       <c r="H220" s="1">
         <v>1849</v>
       </c>
-      <c r="K220">
+      <c r="K220" s="16">
         <v>7015</v>
       </c>
       <c r="L220" s="8" t="s">
@@ -8837,9 +9130,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="221" spans="1:13" ht="17.25" customHeight="1">
+    <row r="221" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>223</v>
+        <f t="shared" si="3"/>
+        <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>86</v>
@@ -8862,7 +9156,7 @@
       <c r="H221" s="1">
         <v>2449</v>
       </c>
-      <c r="K221">
+      <c r="K221" s="16">
         <v>7015</v>
       </c>
       <c r="L221" s="8" t="s">
@@ -8872,9 +9166,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="222" spans="1:13" ht="17.25" customHeight="1">
+    <row r="222" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>224</v>
+        <f t="shared" si="3"/>
+        <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>86</v>
@@ -8897,7 +9192,7 @@
       <c r="H222" s="1">
         <v>1849</v>
       </c>
-      <c r="K222">
+      <c r="K222" s="16">
         <v>7015</v>
       </c>
       <c r="L222" s="8" t="s">
@@ -8907,9 +9202,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="223" spans="1:13" ht="17.25" customHeight="1">
+    <row r="223" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>225</v>
+        <f t="shared" si="3"/>
+        <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>86</v>
@@ -8932,7 +9228,7 @@
       <c r="H223" s="1">
         <v>1849</v>
       </c>
-      <c r="K223">
+      <c r="K223" s="16">
         <v>7015</v>
       </c>
       <c r="L223" s="8" t="s">
@@ -8942,9 +9238,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="224" spans="1:13" ht="17.25" customHeight="1">
+    <row r="224" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>226</v>
+        <f t="shared" si="3"/>
+        <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>86</v>
@@ -8967,7 +9264,7 @@
       <c r="H224" s="1">
         <v>1940</v>
       </c>
-      <c r="K224">
+      <c r="K224" s="16">
         <v>7015</v>
       </c>
       <c r="L224" s="8" t="s">
@@ -8977,9 +9274,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="225" spans="1:13" ht="17.25" customHeight="1">
+    <row r="225" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>227</v>
+        <f t="shared" si="3"/>
+        <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>86</v>
@@ -9002,7 +9300,7 @@
       <c r="H225" s="1">
         <v>1849</v>
       </c>
-      <c r="K225">
+      <c r="K225" s="16">
         <v>7015</v>
       </c>
       <c r="L225" s="8" t="s">
@@ -9012,9 +9310,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="226" spans="1:13" ht="17.25" customHeight="1">
+    <row r="226" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>228</v>
+        <f t="shared" si="3"/>
+        <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>86</v>
@@ -9037,7 +9336,7 @@
       <c r="H226" s="1">
         <v>1849</v>
       </c>
-      <c r="K226">
+      <c r="K226" s="16">
         <v>7015</v>
       </c>
       <c r="L226" s="8" t="s">
@@ -9047,9 +9346,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="17.25" customHeight="1">
+    <row r="227" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>229</v>
+        <f t="shared" si="3"/>
+        <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>86</v>
@@ -9072,7 +9372,7 @@
       <c r="H227" s="1">
         <v>1849</v>
       </c>
-      <c r="K227">
+      <c r="K227" s="16">
         <v>7015</v>
       </c>
       <c r="L227" s="8" t="s">
@@ -9082,9 +9382,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="228" spans="1:13" ht="17.25" customHeight="1">
+    <row r="228" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>230</v>
+        <f t="shared" si="3"/>
+        <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>90</v>
@@ -9107,7 +9408,7 @@
       <c r="H228" s="1">
         <v>1757</v>
       </c>
-      <c r="K228" s="14" t="s">
+      <c r="K228" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L228" s="8" t="s">
@@ -9117,9 +9418,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="229" spans="1:13" ht="17.25" customHeight="1">
+    <row r="229" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>231</v>
+        <f t="shared" si="3"/>
+        <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>92</v>
@@ -9142,7 +9444,7 @@
       <c r="H229" s="1">
         <v>2332</v>
       </c>
-      <c r="K229">
+      <c r="K229" s="16">
         <v>8990</v>
       </c>
       <c r="L229" s="8" t="s">
@@ -9152,9 +9454,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="230" spans="1:13" ht="17.25" customHeight="1">
+    <row r="230" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>232</v>
+        <f t="shared" si="3"/>
+        <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>94</v>
@@ -9177,7 +9480,7 @@
       <c r="H230" s="1">
         <v>1757</v>
       </c>
-      <c r="K230">
+      <c r="K230" s="16">
         <v>9982</v>
       </c>
       <c r="L230" s="8" t="s">
@@ -9187,9 +9490,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="231" spans="1:13" ht="17.25" customHeight="1">
+    <row r="231" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>233</v>
+        <f t="shared" si="3"/>
+        <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>96</v>
@@ -9212,7 +9516,7 @@
       <c r="H231" s="1">
         <v>2565</v>
       </c>
-      <c r="K231">
+      <c r="K231" s="16">
         <v>4040</v>
       </c>
       <c r="L231" s="8" t="s">
@@ -9222,9 +9526,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:13" ht="17.25" customHeight="1">
+    <row r="232" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>234</v>
+        <f t="shared" si="3"/>
+        <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>96</v>
@@ -9247,7 +9552,7 @@
       <c r="H232" s="1">
         <v>2216</v>
       </c>
-      <c r="K232">
+      <c r="K232" s="16">
         <v>4040</v>
       </c>
       <c r="L232" s="8" t="s">
@@ -9257,9 +9562,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:13" ht="17.25" customHeight="1">
+    <row r="233" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>235</v>
+        <f t="shared" si="3"/>
+        <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>96</v>
@@ -9282,7 +9588,7 @@
       <c r="H233" s="1">
         <v>2032</v>
       </c>
-      <c r="K233">
+      <c r="K233" s="16">
         <v>4040</v>
       </c>
       <c r="L233" s="8" t="s">
@@ -9292,9 +9598,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="17.25" customHeight="1">
+    <row r="234" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>236</v>
+        <f t="shared" si="3"/>
+        <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>96</v>
@@ -9317,7 +9624,7 @@
       <c r="H234" s="1">
         <v>2216</v>
       </c>
-      <c r="K234">
+      <c r="K234" s="16">
         <v>4040</v>
       </c>
       <c r="L234" s="8" t="s">
@@ -9327,9 +9634,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="17.25" customHeight="1">
+    <row r="235" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>237</v>
+        <f t="shared" si="3"/>
+        <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>96</v>
@@ -9352,7 +9660,7 @@
       <c r="H235" s="1">
         <v>2216</v>
       </c>
-      <c r="K235">
+      <c r="K235" s="16">
         <v>4040</v>
       </c>
       <c r="L235" s="8" t="s">
@@ -9362,9 +9670,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:13" ht="17.25" customHeight="1">
+    <row r="236" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>75</v>
@@ -9387,7 +9696,7 @@
       <c r="H236" s="1">
         <v>2681</v>
       </c>
-      <c r="K236">
+      <c r="K236" s="16">
         <v>6262</v>
       </c>
       <c r="L236" s="1" t="s">
@@ -9397,9 +9706,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="17.25" customHeight="1">
+    <row r="237" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>239</v>
+        <f t="shared" si="3"/>
+        <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>75</v>
@@ -9422,7 +9732,7 @@
       <c r="H237" s="1">
         <v>2332</v>
       </c>
-      <c r="K237">
+      <c r="K237" s="16">
         <v>6262</v>
       </c>
       <c r="L237" s="1" t="s">
@@ -9432,9 +9742,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="17.25" customHeight="1">
+    <row r="238" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>240</v>
+        <f t="shared" si="3"/>
+        <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>75</v>
@@ -9457,7 +9768,7 @@
       <c r="H238" s="1">
         <v>2449</v>
       </c>
-      <c r="K238">
+      <c r="K238" s="16">
         <v>6262</v>
       </c>
       <c r="L238" s="1" t="s">
@@ -9467,9 +9778,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:13" ht="17.25" customHeight="1">
+    <row r="239" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>241</v>
+        <f t="shared" si="3"/>
+        <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>76</v>
@@ -9492,7 +9804,7 @@
       <c r="H239" s="1">
         <v>1849</v>
       </c>
-      <c r="K239">
+      <c r="K239" s="16">
         <v>6919</v>
       </c>
       <c r="L239" s="8" t="s">
@@ -9502,9 +9814,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240" spans="1:13" ht="17.25" customHeight="1">
+    <row r="240" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>242</v>
+        <f t="shared" si="3"/>
+        <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>76</v>
@@ -9527,7 +9840,7 @@
       <c r="H240" s="1">
         <v>2332</v>
       </c>
-      <c r="K240">
+      <c r="K240" s="16">
         <v>6919</v>
       </c>
       <c r="L240" s="8" t="s">
@@ -9537,9 +9850,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:13" ht="17.25" customHeight="1">
+    <row r="241" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>243</v>
+        <f t="shared" si="3"/>
+        <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>76</v>
@@ -9562,7 +9876,7 @@
       <c r="H241" s="1">
         <v>2032</v>
       </c>
-      <c r="K241">
+      <c r="K241" s="16">
         <v>6919</v>
       </c>
       <c r="L241" s="8" t="s">
@@ -9572,9 +9886,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:13" ht="17.25" customHeight="1">
+    <row r="242" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>244</v>
+        <f t="shared" si="3"/>
+        <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>78</v>
@@ -9597,7 +9912,7 @@
       <c r="H242" s="1">
         <v>3233</v>
       </c>
-      <c r="K242">
+      <c r="K242" s="16">
         <v>6919</v>
       </c>
       <c r="L242" s="8" t="s">
@@ -9607,9 +9922,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:13" ht="17.25" customHeight="1">
+    <row r="243" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>245</v>
+        <f t="shared" si="3"/>
+        <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>82</v>
@@ -9638,7 +9954,7 @@
       <c r="J243" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="K243">
+      <c r="K243" s="16">
         <v>3020</v>
       </c>
       <c r="L243" s="8" t="s">
@@ -9648,9 +9964,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="244" spans="1:13" ht="17.25" customHeight="1">
+    <row r="244" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>246</v>
+        <f t="shared" si="3"/>
+        <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>82</v>
@@ -9673,7 +9990,7 @@
       <c r="H244" s="1">
         <v>2032</v>
       </c>
-      <c r="K244">
+      <c r="K244" s="16">
         <v>3020</v>
       </c>
       <c r="L244" s="8" t="s">
@@ -9683,9 +10000,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="245" spans="1:13" ht="17.25" customHeight="1">
+    <row r="245" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>247</v>
+        <f t="shared" si="3"/>
+        <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>82</v>
@@ -9708,7 +10026,7 @@
       <c r="H245" s="1">
         <v>2032</v>
       </c>
-      <c r="K245">
+      <c r="K245" s="16">
         <v>3020</v>
       </c>
       <c r="L245" s="8" t="s">
@@ -9718,9 +10036,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="246" spans="1:13" ht="17.25" customHeight="1">
+    <row r="246" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>248</v>
+        <f t="shared" si="3"/>
+        <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>84</v>
@@ -9743,7 +10062,7 @@
       <c r="H246" s="1">
         <v>1757</v>
       </c>
-      <c r="K246">
+      <c r="K246" s="16">
         <v>1615</v>
       </c>
       <c r="L246" s="8" t="s">
@@ -9753,9 +10072,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="247" spans="1:13" ht="17.25" customHeight="1">
+    <row r="247" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>249</v>
+        <f t="shared" si="3"/>
+        <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>84</v>
@@ -9778,7 +10098,7 @@
       <c r="H247" s="1">
         <v>1849</v>
       </c>
-      <c r="K247">
+      <c r="K247" s="16">
         <v>7015</v>
       </c>
       <c r="L247" s="8" t="s">
@@ -9788,9 +10108,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="248" spans="1:13" ht="17.25" customHeight="1">
+    <row r="248" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>250</v>
+        <f t="shared" si="3"/>
+        <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>84</v>
@@ -9813,7 +10134,7 @@
       <c r="H248" s="1">
         <v>1849</v>
       </c>
-      <c r="K248">
+      <c r="K248" s="16">
         <v>7015</v>
       </c>
       <c r="L248" s="8" t="s">
@@ -9823,9 +10144,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="249" spans="1:13" ht="17.25" customHeight="1">
+    <row r="249" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>251</v>
+        <f t="shared" si="3"/>
+        <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>84</v>
@@ -9848,7 +10170,7 @@
       <c r="H249" s="1">
         <v>1849</v>
       </c>
-      <c r="K249">
+      <c r="K249" s="16">
         <v>7015</v>
       </c>
       <c r="L249" s="8" t="s">
@@ -9858,9 +10180,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="250" spans="1:13" ht="17.25" customHeight="1">
+    <row r="250" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>252</v>
+        <f t="shared" si="3"/>
+        <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>84</v>
@@ -9883,7 +10206,7 @@
       <c r="H250" s="1">
         <v>1849</v>
       </c>
-      <c r="K250">
+      <c r="K250" s="16">
         <v>7015</v>
       </c>
       <c r="L250" s="8" t="s">
@@ -9893,9 +10216,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="251" spans="1:13" ht="17.25" customHeight="1">
+    <row r="251" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>253</v>
+        <f t="shared" si="3"/>
+        <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>84</v>
@@ -9918,7 +10242,7 @@
       <c r="H251" s="1">
         <v>1849</v>
       </c>
-      <c r="K251">
+      <c r="K251" s="16">
         <v>7015</v>
       </c>
       <c r="L251" s="8" t="s">
@@ -9928,9 +10252,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="252" spans="1:13" ht="17.25" customHeight="1">
+    <row r="252" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>254</v>
+        <f t="shared" si="3"/>
+        <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>84</v>
@@ -9953,7 +10278,7 @@
       <c r="H252" s="1">
         <v>1849</v>
       </c>
-      <c r="K252">
+      <c r="K252" s="16">
         <v>7015</v>
       </c>
       <c r="L252" s="8" t="s">
@@ -9963,9 +10288,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="253" spans="1:13" ht="17.25" customHeight="1">
+    <row r="253" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>255</v>
+        <f t="shared" si="3"/>
+        <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>86</v>
@@ -9988,7 +10314,7 @@
       <c r="H253" s="1">
         <v>2449</v>
       </c>
-      <c r="K253">
+      <c r="K253" s="16">
         <v>7015</v>
       </c>
       <c r="L253" s="8" t="s">
@@ -9998,9 +10324,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="254" spans="1:13" ht="17.25" customHeight="1">
+    <row r="254" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>256</v>
+        <f t="shared" si="3"/>
+        <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>86</v>
@@ -10023,7 +10350,7 @@
       <c r="H254" s="1">
         <v>1849</v>
       </c>
-      <c r="K254">
+      <c r="K254" s="16">
         <v>7015</v>
       </c>
       <c r="L254" s="8" t="s">
@@ -10033,9 +10360,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="255" spans="1:13" ht="17.25" customHeight="1">
+    <row r="255" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>257</v>
+        <f t="shared" si="3"/>
+        <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>86</v>
@@ -10058,7 +10386,7 @@
       <c r="H255" s="1">
         <v>1849</v>
       </c>
-      <c r="K255">
+      <c r="K255" s="16">
         <v>7015</v>
       </c>
       <c r="L255" s="8" t="s">
@@ -10068,9 +10396,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="256" spans="1:13" ht="17.25" customHeight="1">
+    <row r="256" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>258</v>
+        <f t="shared" si="3"/>
+        <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>86</v>
@@ -10093,7 +10422,7 @@
       <c r="H256" s="1">
         <v>1940</v>
       </c>
-      <c r="K256">
+      <c r="K256" s="16">
         <v>7015</v>
       </c>
       <c r="L256" s="8" t="s">
@@ -10103,9 +10432,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="257" spans="1:13" ht="17.25" customHeight="1">
+    <row r="257" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>259</v>
+        <f t="shared" si="3"/>
+        <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>86</v>
@@ -10128,7 +10458,7 @@
       <c r="H257" s="1">
         <v>1849</v>
       </c>
-      <c r="K257">
+      <c r="K257" s="16">
         <v>7015</v>
       </c>
       <c r="L257" s="8" t="s">
@@ -10138,9 +10468,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="258" spans="1:13" ht="17.25" customHeight="1">
+    <row r="258" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>260</v>
+        <f t="shared" si="3"/>
+        <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>86</v>
@@ -10163,7 +10494,7 @@
       <c r="H258" s="1">
         <v>1849</v>
       </c>
-      <c r="K258">
+      <c r="K258" s="16">
         <v>7015</v>
       </c>
       <c r="L258" s="8" t="s">
@@ -10173,9 +10504,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="259" spans="1:13" ht="17.25" customHeight="1">
+    <row r="259" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>261</v>
+        <f t="shared" ref="A259:A296" si="4">ROW()-1</f>
+        <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>86</v>
@@ -10198,7 +10530,7 @@
       <c r="H259" s="1">
         <v>1849</v>
       </c>
-      <c r="K259">
+      <c r="K259" s="16">
         <v>7015</v>
       </c>
       <c r="L259" s="8" t="s">
@@ -10208,9 +10540,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="260" spans="1:13" ht="17.25" customHeight="1">
+    <row r="260" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>262</v>
+        <f t="shared" si="4"/>
+        <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>90</v>
@@ -10233,7 +10566,7 @@
       <c r="H260" s="1">
         <v>1757</v>
       </c>
-      <c r="K260" s="14" t="s">
+      <c r="K260" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L260" s="8" t="s">
@@ -10243,9 +10576,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="17.25" customHeight="1">
+    <row r="261" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>263</v>
+        <f t="shared" si="4"/>
+        <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>92</v>
@@ -10268,7 +10602,7 @@
       <c r="H261" s="1">
         <v>2332</v>
       </c>
-      <c r="K261">
+      <c r="K261" s="16">
         <v>8990</v>
       </c>
       <c r="L261" s="8" t="s">
@@ -10278,9 +10612,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="17.25" customHeight="1">
+    <row r="262" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>264</v>
+        <f t="shared" si="4"/>
+        <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>94</v>
@@ -10309,7 +10644,7 @@
       <c r="J262" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K262">
+      <c r="K262" s="16">
         <v>9982</v>
       </c>
       <c r="L262" s="8" t="s">
@@ -10319,67 +10654,75 @@
         <v>66</v>
       </c>
     </row>
-    <row r="263" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A263" s="1">
-        <v>265</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D263" s="8">
-        <v>11509</v>
-      </c>
-      <c r="E263" s="8">
-        <v>53000</v>
-      </c>
-      <c r="F263" s="8">
-        <v>4072</v>
-      </c>
-      <c r="G263" s="8">
-        <v>3180</v>
-      </c>
-      <c r="H263" s="1">
-        <v>2565</v>
-      </c>
-      <c r="K263">
-        <v>4040</v>
-      </c>
-      <c r="L263" s="8" t="s">
-        <v>13</v>
+    <row r="263" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="14">
+        <f t="shared" si="4"/>
+        <v>262</v>
+      </c>
+      <c r="B263" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C263" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D263" s="15">
+        <v>11508</v>
+      </c>
+      <c r="E263" s="15">
+        <v>36300</v>
+      </c>
+      <c r="F263" s="15">
+        <v>2040</v>
+      </c>
+      <c r="G263" s="15">
+        <v>1379</v>
+      </c>
+      <c r="H263" s="14">
+        <v>1757</v>
+      </c>
+      <c r="I263" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="J263" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K263" s="19">
+        <v>7040</v>
+      </c>
+      <c r="L263" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="264" spans="1:13" ht="17.25" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>266</v>
+        <f t="shared" si="4"/>
+        <v>263</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D264" s="8">
         <v>11509</v>
       </c>
       <c r="E264" s="8">
-        <v>45800</v>
+        <v>53000</v>
       </c>
       <c r="F264" s="8">
-        <v>4063</v>
+        <v>4072</v>
       </c>
       <c r="G264" s="8">
-        <v>2748</v>
+        <v>3180</v>
       </c>
       <c r="H264" s="1">
-        <v>2216</v>
-      </c>
-      <c r="K264">
+        <v>2565</v>
+      </c>
+      <c r="K264" s="16">
         <v>4040</v>
       </c>
       <c r="L264" s="8" t="s">
@@ -10389,35 +10732,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:13" ht="17.25" customHeight="1">
+    <row r="265" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>267</v>
+        <f t="shared" si="4"/>
+        <v>264</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D265" s="8">
         <v>11509</v>
       </c>
       <c r="E265" s="8">
-        <v>43900</v>
+        <v>45800</v>
       </c>
       <c r="F265" s="8">
-        <v>3894</v>
+        <v>4063</v>
       </c>
       <c r="G265" s="8">
-        <v>2634</v>
+        <v>2748</v>
       </c>
       <c r="H265" s="1">
-        <v>2124</v>
-      </c>
-      <c r="I265" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K265">
+        <v>2216</v>
+      </c>
+      <c r="K265" s="16">
         <v>4040</v>
       </c>
       <c r="L265" s="8" t="s">
@@ -10427,32 +10768,36 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:13" ht="17.25" customHeight="1">
+    <row r="266" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>268</v>
+        <f t="shared" si="4"/>
+        <v>265</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D266" s="8">
         <v>11509</v>
       </c>
       <c r="E266" s="8">
-        <v>45800</v>
+        <v>43900</v>
       </c>
       <c r="F266" s="8">
-        <v>4063</v>
+        <v>3894</v>
       </c>
       <c r="G266" s="8">
-        <v>2748</v>
+        <v>2634</v>
       </c>
       <c r="H266" s="1">
-        <v>2216</v>
-      </c>
-      <c r="K266">
+        <v>2124</v>
+      </c>
+      <c r="I266" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K266" s="16">
         <v>4040</v>
       </c>
       <c r="L266" s="8" t="s">
@@ -10462,15 +10807,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:13" ht="17.25" customHeight="1">
+    <row r="267" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>269</v>
+        <f t="shared" si="4"/>
+        <v>266</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D267" s="8">
         <v>11509</v>
@@ -10487,7 +10833,7 @@
       <c r="H267" s="1">
         <v>2216</v>
       </c>
-      <c r="K267">
+      <c r="K267" s="16">
         <v>4040</v>
       </c>
       <c r="L267" s="8" t="s">
@@ -10497,67 +10843,69 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:13" ht="17.25" customHeight="1">
+    <row r="268" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>270</v>
+        <f t="shared" si="4"/>
+        <v>267</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C268" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D268" s="8">
         <v>11509</v>
       </c>
       <c r="E268" s="8">
-        <v>55400</v>
+        <v>45800</v>
       </c>
       <c r="F268" s="8">
-        <v>4074</v>
+        <v>4063</v>
       </c>
       <c r="G268" s="8">
-        <v>3324</v>
+        <v>2748</v>
       </c>
       <c r="H268" s="1">
-        <v>2681</v>
-      </c>
-      <c r="K268">
-        <v>6262</v>
-      </c>
-      <c r="L268" s="1" t="s">
-        <v>25</v>
+        <v>2216</v>
+      </c>
+      <c r="K268" s="16">
+        <v>4040</v>
+      </c>
+      <c r="L268" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="M268" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="269" spans="1:13" ht="17.25" customHeight="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>271</v>
+        <f t="shared" si="4"/>
+        <v>268</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D269" s="8">
         <v>11509</v>
       </c>
       <c r="E269" s="8">
-        <v>48200</v>
+        <v>55400</v>
       </c>
       <c r="F269" s="8">
-        <v>4066</v>
+        <v>4074</v>
       </c>
       <c r="G269" s="8">
-        <v>2892</v>
+        <v>3324</v>
       </c>
       <c r="H269" s="1">
-        <v>2332</v>
-      </c>
-      <c r="K269">
+        <v>2681</v>
+      </c>
+      <c r="K269" s="16">
         <v>6262</v>
       </c>
       <c r="L269" s="1" t="s">
@@ -10567,32 +10915,33 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:13" ht="17.25" customHeight="1">
+    <row r="270" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>272</v>
+        <f t="shared" si="4"/>
+        <v>269</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C270" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D270" s="8">
         <v>11509</v>
       </c>
       <c r="E270" s="8">
-        <v>50600</v>
+        <v>48200</v>
       </c>
       <c r="F270" s="8">
-        <v>4069</v>
+        <v>4066</v>
       </c>
       <c r="G270" s="8">
-        <v>3036</v>
+        <v>2892</v>
       </c>
       <c r="H270" s="1">
-        <v>2449</v>
-      </c>
-      <c r="K270">
+        <v>2332</v>
+      </c>
+      <c r="K270" s="16">
         <v>6262</v>
       </c>
       <c r="L270" s="1" t="s">
@@ -10602,67 +10951,69 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="17.25" customHeight="1">
+    <row r="271" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>273</v>
+        <f t="shared" si="4"/>
+        <v>270</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C271" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D271" s="8">
         <v>11509</v>
       </c>
       <c r="E271" s="8">
-        <v>38200</v>
+        <v>50600</v>
       </c>
       <c r="F271" s="8">
-        <v>3388</v>
+        <v>4069</v>
       </c>
       <c r="G271" s="8">
-        <v>2292</v>
+        <v>3036</v>
       </c>
       <c r="H271" s="1">
-        <v>1849</v>
-      </c>
-      <c r="K271">
-        <v>6919</v>
-      </c>
-      <c r="L271" s="8" t="s">
-        <v>20</v>
+        <v>2449</v>
+      </c>
+      <c r="K271" s="16">
+        <v>6262</v>
+      </c>
+      <c r="L271" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="M271" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="272" spans="1:13" ht="17.25" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>274</v>
+        <f t="shared" si="4"/>
+        <v>271</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C272" s="8" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D272" s="8">
         <v>11509</v>
       </c>
       <c r="E272" s="8">
-        <v>45800</v>
+        <v>38200</v>
       </c>
       <c r="F272" s="8">
-        <v>4066</v>
+        <v>3388</v>
       </c>
       <c r="G272" s="8">
-        <v>2892</v>
+        <v>2292</v>
       </c>
       <c r="H272" s="1">
-        <v>2332</v>
-      </c>
-      <c r="K272">
+        <v>1849</v>
+      </c>
+      <c r="K272" s="16">
         <v>6919</v>
       </c>
       <c r="L272" s="8" t="s">
@@ -10672,32 +11023,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="17.25" customHeight="1">
+    <row r="273" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>275</v>
+        <f t="shared" si="4"/>
+        <v>272</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D273" s="8">
         <v>11509</v>
       </c>
       <c r="E273" s="8">
-        <v>42000</v>
+        <v>45800</v>
       </c>
       <c r="F273" s="8">
-        <v>3725</v>
+        <v>4066</v>
       </c>
       <c r="G273" s="8">
-        <v>2520</v>
+        <v>2892</v>
       </c>
       <c r="H273" s="1">
-        <v>2032</v>
-      </c>
-      <c r="K273">
+        <v>2332</v>
+      </c>
+      <c r="K273" s="16">
         <v>6919</v>
       </c>
       <c r="L273" s="8" t="s">
@@ -10707,32 +11059,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="17.25" customHeight="1">
+    <row r="274" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>276</v>
+        <f t="shared" si="4"/>
+        <v>273</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D274" s="8">
         <v>11509</v>
       </c>
       <c r="E274" s="8">
-        <v>66800</v>
+        <v>42000</v>
       </c>
       <c r="F274" s="8">
-        <v>4088</v>
+        <v>3725</v>
       </c>
       <c r="G274" s="8">
-        <v>4008</v>
+        <v>2520</v>
       </c>
       <c r="H274" s="1">
-        <v>3233</v>
-      </c>
-      <c r="K274">
+        <v>2032</v>
+      </c>
+      <c r="K274" s="16">
         <v>6919</v>
       </c>
       <c r="L274" s="8" t="s">
@@ -10742,73 +11095,75 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="17.25" customHeight="1">
+    <row r="275" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>277</v>
+        <f t="shared" si="4"/>
+        <v>274</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D275" s="8">
         <v>11509</v>
       </c>
       <c r="E275" s="8">
-        <v>36300</v>
+        <v>66800</v>
       </c>
       <c r="F275" s="8">
-        <v>3220</v>
+        <v>4088</v>
       </c>
       <c r="G275" s="8">
-        <v>2520</v>
+        <v>4008</v>
       </c>
       <c r="H275" s="1">
-        <v>1757</v>
-      </c>
-      <c r="I275" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J275" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K275">
-        <v>3020</v>
+        <v>3233</v>
+      </c>
+      <c r="K275" s="16">
+        <v>6919</v>
       </c>
       <c r="L275" s="8" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="M275" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="276" spans="1:13" ht="17.25" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>278</v>
+        <f t="shared" si="4"/>
+        <v>275</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D276" s="8">
         <v>11509</v>
       </c>
       <c r="E276" s="8">
-        <v>42000</v>
+        <v>36300</v>
       </c>
       <c r="F276" s="8">
-        <v>3725</v>
+        <v>3220</v>
       </c>
       <c r="G276" s="8">
         <v>2520</v>
       </c>
       <c r="H276" s="1">
-        <v>2032</v>
-      </c>
-      <c r="K276">
+        <v>1757</v>
+      </c>
+      <c r="I276" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J276" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K276" s="16">
         <v>3020</v>
       </c>
       <c r="L276" s="8" t="s">
@@ -10818,15 +11173,16 @@
         <v>61</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="17.25" customHeight="1">
+    <row r="277" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>279</v>
+        <f t="shared" si="4"/>
+        <v>276</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D277" s="8">
         <v>11509</v>
@@ -10843,7 +11199,7 @@
       <c r="H277" s="1">
         <v>2032</v>
       </c>
-      <c r="K277">
+      <c r="K277" s="16">
         <v>3020</v>
       </c>
       <c r="L277" s="8" t="s">
@@ -10853,85 +11209,88 @@
         <v>61</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="17.25" customHeight="1">
+    <row r="278" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>280</v>
+        <f t="shared" si="4"/>
+        <v>277</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D278" s="8">
         <v>11509</v>
       </c>
       <c r="E278" s="8">
-        <v>36300</v>
+        <v>42000</v>
       </c>
       <c r="F278" s="8">
-        <v>3220</v>
+        <v>3725</v>
       </c>
       <c r="G278" s="8">
-        <v>2178</v>
+        <v>2520</v>
       </c>
       <c r="H278" s="1">
-        <v>1757</v>
-      </c>
-      <c r="K278">
-        <v>1615</v>
+        <v>2032</v>
+      </c>
+      <c r="K278" s="16">
+        <v>3020</v>
       </c>
       <c r="L278" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M278" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="279" spans="1:13" ht="17.25" customHeight="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>281</v>
+        <f t="shared" si="4"/>
+        <v>278</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D279" s="8">
         <v>11509</v>
       </c>
       <c r="E279" s="8">
-        <v>38200</v>
+        <v>36300</v>
       </c>
       <c r="F279" s="8">
-        <v>3388</v>
+        <v>3220</v>
       </c>
       <c r="G279" s="8">
-        <v>2292</v>
+        <v>2178</v>
       </c>
       <c r="H279" s="1">
-        <v>1849</v>
-      </c>
-      <c r="K279">
-        <v>7015</v>
+        <v>1757</v>
+      </c>
+      <c r="K279" s="16">
+        <v>1615</v>
       </c>
       <c r="L279" s="8" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M279" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="280" spans="1:13" ht="17.25" customHeight="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>282</v>
+        <f t="shared" si="4"/>
+        <v>279</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D280" s="8">
         <v>11509</v>
@@ -10948,7 +11307,7 @@
       <c r="H280" s="1">
         <v>1849</v>
       </c>
-      <c r="K280">
+      <c r="K280" s="16">
         <v>7015</v>
       </c>
       <c r="L280" s="8" t="s">
@@ -10958,15 +11317,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="17.25" customHeight="1">
+    <row r="281" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>283</v>
+        <f t="shared" si="4"/>
+        <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D281" s="8">
         <v>11509</v>
@@ -10983,13 +11343,7 @@
       <c r="H281" s="1">
         <v>1849</v>
       </c>
-      <c r="I281" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J281" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K281">
+      <c r="K281" s="16">
         <v>7015</v>
       </c>
       <c r="L281" s="8" t="s">
@@ -10999,15 +11353,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="17.25" customHeight="1">
+    <row r="282" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>284</v>
+        <f t="shared" si="4"/>
+        <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D282" s="8">
         <v>11509</v>
@@ -11024,7 +11379,13 @@
       <c r="H282" s="1">
         <v>1849</v>
       </c>
-      <c r="K282">
+      <c r="I282" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K282" s="16">
         <v>7015</v>
       </c>
       <c r="L282" s="8" t="s">
@@ -11034,15 +11395,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="17.25" customHeight="1">
+    <row r="283" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>285</v>
+        <f t="shared" si="4"/>
+        <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D283" s="8">
         <v>11509</v>
@@ -11059,7 +11421,7 @@
       <c r="H283" s="1">
         <v>1849</v>
       </c>
-      <c r="K283">
+      <c r="K283" s="16">
         <v>7015</v>
       </c>
       <c r="L283" s="8" t="s">
@@ -11069,15 +11431,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="17.25" customHeight="1">
+    <row r="284" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>286</v>
+        <f t="shared" si="4"/>
+        <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D284" s="8">
         <v>11509</v>
@@ -11094,7 +11457,7 @@
       <c r="H284" s="1">
         <v>1849</v>
       </c>
-      <c r="K284">
+      <c r="K284" s="16">
         <v>7015</v>
       </c>
       <c r="L284" s="8" t="s">
@@ -11104,15 +11467,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="17.25" customHeight="1">
+    <row r="285" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>287</v>
+        <f t="shared" si="4"/>
+        <v>284</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D285" s="8">
         <v>11509</v>
@@ -11129,7 +11493,7 @@
       <c r="H285" s="1">
         <v>1849</v>
       </c>
-      <c r="K285">
+      <c r="K285" s="16">
         <v>7015</v>
       </c>
       <c r="L285" s="8" t="s">
@@ -11139,38 +11503,33 @@
         <v>63</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="17.25" customHeight="1">
+    <row r="286" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>288</v>
+        <f t="shared" si="4"/>
+        <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D286" s="8">
         <v>11509</v>
       </c>
       <c r="E286" s="8">
-        <v>48200</v>
+        <v>38200</v>
       </c>
       <c r="F286" s="8">
-        <v>0</v>
+        <v>3388</v>
       </c>
       <c r="G286" s="8">
-        <v>0</v>
+        <v>2292</v>
       </c>
       <c r="H286" s="1">
-        <v>0</v>
-      </c>
-      <c r="I286" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J286" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K286">
+        <v>1849</v>
+      </c>
+      <c r="K286" s="16">
         <v>7015</v>
       </c>
       <c r="L286" s="8" t="s">
@@ -11180,32 +11539,39 @@
         <v>63</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="17.25" customHeight="1">
+    <row r="287" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>289</v>
+        <f t="shared" si="4"/>
+        <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D287" s="8">
         <v>11509</v>
       </c>
       <c r="E287" s="8">
-        <v>38200</v>
+        <v>48200</v>
       </c>
       <c r="F287" s="8">
-        <v>3388</v>
+        <v>0</v>
       </c>
       <c r="G287" s="8">
-        <v>2292</v>
+        <v>0</v>
       </c>
       <c r="H287" s="1">
-        <v>1849</v>
-      </c>
-      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="I287" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K287" s="16">
         <v>7015</v>
       </c>
       <c r="L287" s="8" t="s">
@@ -11215,15 +11581,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="17.25" customHeight="1">
+    <row r="288" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>290</v>
+        <f t="shared" si="4"/>
+        <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D288" s="8">
         <v>11509</v>
@@ -11240,7 +11607,7 @@
       <c r="H288" s="1">
         <v>1849</v>
       </c>
-      <c r="K288">
+      <c r="K288" s="16">
         <v>7015</v>
       </c>
       <c r="L288" s="8" t="s">
@@ -11250,32 +11617,33 @@
         <v>63</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="17.25" customHeight="1">
+    <row r="289" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>291</v>
+        <f t="shared" si="4"/>
+        <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D289" s="8">
         <v>11509</v>
       </c>
       <c r="E289" s="8">
-        <v>40100</v>
+        <v>38200</v>
       </c>
       <c r="F289" s="8">
-        <v>3557</v>
+        <v>3388</v>
       </c>
       <c r="G289" s="8">
-        <v>2406</v>
+        <v>2292</v>
       </c>
       <c r="H289" s="1">
-        <v>1940</v>
-      </c>
-      <c r="K289">
+        <v>1849</v>
+      </c>
+      <c r="K289" s="16">
         <v>7015</v>
       </c>
       <c r="L289" s="8" t="s">
@@ -11285,32 +11653,33 @@
         <v>63</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="17.25" customHeight="1">
+    <row r="290" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>292</v>
+        <f t="shared" si="4"/>
+        <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C290" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D290" s="8">
         <v>11509</v>
       </c>
       <c r="E290" s="8">
-        <v>38200</v>
+        <v>40100</v>
       </c>
       <c r="F290" s="8">
-        <v>3388</v>
+        <v>3557</v>
       </c>
       <c r="G290" s="8">
-        <v>2292</v>
+        <v>2406</v>
       </c>
       <c r="H290" s="1">
-        <v>1849</v>
-      </c>
-      <c r="K290">
+        <v>1940</v>
+      </c>
+      <c r="K290" s="16">
         <v>7015</v>
       </c>
       <c r="L290" s="8" t="s">
@@ -11320,15 +11689,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="17.25" customHeight="1">
+    <row r="291" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>293</v>
+        <f t="shared" si="4"/>
+        <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D291" s="8">
         <v>11509</v>
@@ -11345,7 +11715,7 @@
       <c r="H291" s="1">
         <v>1849</v>
       </c>
-      <c r="K291">
+      <c r="K291" s="16">
         <v>7015</v>
       </c>
       <c r="L291" s="8" t="s">
@@ -11355,15 +11725,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="17.25" customHeight="1">
+    <row r="292" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>294</v>
+        <f t="shared" si="4"/>
+        <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D292" s="8">
         <v>11509</v>
@@ -11380,7 +11751,7 @@
       <c r="H292" s="1">
         <v>1849</v>
       </c>
-      <c r="K292">
+      <c r="K292" s="16">
         <v>7015</v>
       </c>
       <c r="L292" s="8" t="s">
@@ -11390,81 +11761,153 @@
         <v>63</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="17.25" customHeight="1">
+    <row r="293" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>295</v>
+        <f t="shared" si="4"/>
+        <v>292</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D293" s="8">
         <v>11509</v>
       </c>
       <c r="E293" s="8">
-        <v>36300</v>
+        <v>38200</v>
       </c>
       <c r="F293" s="8">
-        <v>44</v>
+        <v>3388</v>
       </c>
       <c r="G293" s="8">
-        <v>2178</v>
+        <v>2292</v>
       </c>
       <c r="H293" s="1">
-        <v>1757</v>
-      </c>
-      <c r="K293" s="14" t="s">
-        <v>106</v>
+        <v>1849</v>
+      </c>
+      <c r="K293" s="16">
+        <v>7015</v>
       </c>
       <c r="L293" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M293" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <f t="shared" si="4"/>
+        <v>293</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C294" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="M293" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="294" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A294" s="1">
-        <v>296</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C294" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="D294" s="8">
         <v>11509</v>
       </c>
       <c r="E294" s="8">
+        <v>36300</v>
+      </c>
+      <c r="F294" s="8">
+        <v>44</v>
+      </c>
+      <c r="G294" s="8">
+        <v>2178</v>
+      </c>
+      <c r="H294" s="1">
+        <v>1757</v>
+      </c>
+      <c r="K294" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="L294" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M294" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <f t="shared" si="4"/>
+        <v>294</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C295" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D295" s="8">
+        <v>11509</v>
+      </c>
+      <c r="E295" s="8">
         <v>50600</v>
       </c>
-      <c r="F294" s="8">
+      <c r="F295" s="8">
         <v>4069</v>
       </c>
-      <c r="G294" s="8">
+      <c r="G295" s="8">
         <v>3036</v>
       </c>
-      <c r="H294" s="1">
+      <c r="H295" s="1">
         <v>2449</v>
       </c>
-      <c r="I294" s="8" t="s">
+      <c r="I295" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K294">
+      <c r="K295" s="16">
         <v>8990</v>
       </c>
-      <c r="L294" s="8" t="s">
+      <c r="L295" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="M294" s="1" t="s">
+      <c r="M295" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="17.25" customHeight="1">
-      <c r="K295"/>
+    <row r="296" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="14">
+        <f t="shared" si="4"/>
+        <v>295</v>
+      </c>
+      <c r="B296" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C296" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D296" s="8">
+        <v>11509</v>
+      </c>
+      <c r="E296" s="15">
+        <v>36300</v>
+      </c>
+      <c r="F296" s="8">
+        <v>3220</v>
+      </c>
+      <c r="G296" s="8">
+        <v>2178</v>
+      </c>
+      <c r="H296" s="14">
+        <v>1757</v>
+      </c>
+      <c r="I296" s="15"/>
+      <c r="K296" s="19">
+        <v>7040</v>
+      </c>
+      <c r="L296" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="M296" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B881BE1-D9E3-4318-8084-219D4449C9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1ACDA6-6B76-422C-B52B-01203C972180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="117">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -998,7 +998,7 @@
   <sheetPr codeName="工作表2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M296"/>
+  <dimension ref="A1:M295"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1" bestFit="1" customWidth="1"/>
@@ -1292,10 +1292,10 @@
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>5</v>
@@ -1330,10 +1330,10 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>5</v>
@@ -1367,10 +1367,10 @@
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>5</v>
@@ -2451,10 +2451,10 @@
         <v>2565</v>
       </c>
       <c r="K38" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>5</v>
@@ -2487,10 +2487,10 @@
         <v>2449</v>
       </c>
       <c r="K39" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>5</v>
@@ -2523,10 +2523,10 @@
         <v>2332</v>
       </c>
       <c r="K40" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>5</v>
@@ -3675,10 +3675,10 @@
         <v>57</v>
       </c>
       <c r="K71" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>5</v>
@@ -3711,10 +3711,10 @@
         <v>2449</v>
       </c>
       <c r="K72" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>5</v>
@@ -3750,10 +3750,10 @@
         <v>57</v>
       </c>
       <c r="K73" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>5</v>
@@ -4942,10 +4942,10 @@
         <v>2681</v>
       </c>
       <c r="K105" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>5</v>
@@ -4978,10 +4978,10 @@
         <v>2449</v>
       </c>
       <c r="K106" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>5</v>
@@ -5014,10 +5014,10 @@
         <v>2449</v>
       </c>
       <c r="K107" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>5</v>
@@ -5548,7 +5548,7 @@
         <v>11504</v>
       </c>
       <c r="E122" s="8">
-        <v>48200</v>
+        <v>50600</v>
       </c>
       <c r="F122" s="8">
         <v>4069</v>
@@ -5558,6 +5558,9 @@
       </c>
       <c r="H122" s="1">
         <v>2449</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="K122" s="16">
         <v>7015</v>
@@ -6100,10 +6103,10 @@
         <v>2681</v>
       </c>
       <c r="K137" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>5</v>
@@ -6142,10 +6145,10 @@
         <v>68</v>
       </c>
       <c r="K138" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>5</v>
@@ -6184,10 +6187,10 @@
         <v>69</v>
       </c>
       <c r="K139" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>5</v>
@@ -6220,10 +6223,10 @@
         <v>2449</v>
       </c>
       <c r="K140" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>5</v>
@@ -6757,7 +6760,7 @@
         <v>11505</v>
       </c>
       <c r="E155" s="8">
-        <v>48200</v>
+        <v>50600</v>
       </c>
       <c r="F155" s="8">
         <v>4069</v>
@@ -7351,10 +7354,10 @@
         <v>2681</v>
       </c>
       <c r="K171" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M171" s="1" t="s">
         <v>5</v>
@@ -7387,10 +7390,10 @@
         <v>2332</v>
       </c>
       <c r="K172" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>5</v>
@@ -7423,10 +7426,10 @@
         <v>2449</v>
       </c>
       <c r="K173" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M173" s="1" t="s">
         <v>5</v>
@@ -7951,7 +7954,7 @@
         <v>11506</v>
       </c>
       <c r="E188" s="8">
-        <v>48200</v>
+        <v>50600</v>
       </c>
       <c r="F188" s="8">
         <v>4069</v>
@@ -8545,10 +8548,10 @@
         <v>2681</v>
       </c>
       <c r="K204" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M204" s="1" t="s">
         <v>5</v>
@@ -8581,10 +8584,10 @@
         <v>2332</v>
       </c>
       <c r="K205" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M205" s="1" t="s">
         <v>5</v>
@@ -8617,10 +8620,10 @@
         <v>2449</v>
       </c>
       <c r="K206" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M206" s="1" t="s">
         <v>5</v>
@@ -9145,7 +9148,7 @@
         <v>11507</v>
       </c>
       <c r="E221" s="8">
-        <v>48200</v>
+        <v>50600</v>
       </c>
       <c r="F221" s="8">
         <v>4069</v>
@@ -9697,10 +9700,10 @@
         <v>2681</v>
       </c>
       <c r="K236" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M236" s="1" t="s">
         <v>5</v>
@@ -9733,10 +9736,10 @@
         <v>2332</v>
       </c>
       <c r="K237" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M237" s="1" t="s">
         <v>5</v>
@@ -9769,10 +9772,10 @@
         <v>2449</v>
       </c>
       <c r="K238" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M238" s="1" t="s">
         <v>5</v>
@@ -10303,7 +10306,7 @@
         <v>11508</v>
       </c>
       <c r="E253" s="8">
-        <v>48200</v>
+        <v>50600</v>
       </c>
       <c r="F253" s="8">
         <v>4069</v>
@@ -10313,6 +10316,12 @@
       </c>
       <c r="H253" s="1">
         <v>2449</v>
+      </c>
+      <c r="I253" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="K253" s="16">
         <v>7015</v>
@@ -10506,7 +10515,7 @@
     </row>
     <row r="259" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <f t="shared" ref="A259:A296" si="4">ROW()-1</f>
+        <f t="shared" ref="A259:A295" si="4">ROW()-1</f>
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
@@ -10906,10 +10915,10 @@
         <v>2681</v>
       </c>
       <c r="K269" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>5</v>
@@ -10942,10 +10951,10 @@
         <v>2332</v>
       </c>
       <c r="K270" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>5</v>
@@ -10978,10 +10987,10 @@
         <v>2449</v>
       </c>
       <c r="K271" s="16">
-        <v>6262</v>
+        <v>6588</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>5</v>
@@ -11548,28 +11557,22 @@
         <v>86</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D287" s="8">
         <v>11509</v>
       </c>
       <c r="E287" s="8">
-        <v>48200</v>
+        <v>38200</v>
       </c>
       <c r="F287" s="8">
-        <v>0</v>
+        <v>3388</v>
       </c>
       <c r="G287" s="8">
-        <v>0</v>
+        <v>2292</v>
       </c>
       <c r="H287" s="1">
-        <v>0</v>
-      </c>
-      <c r="I287" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J287" s="1" t="s">
-        <v>74</v>
+        <v>1849</v>
       </c>
       <c r="K287" s="16">
         <v>7015</v>
@@ -11590,7 +11593,7 @@
         <v>86</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D288" s="8">
         <v>11509</v>
@@ -11626,22 +11629,22 @@
         <v>86</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D289" s="8">
         <v>11509</v>
       </c>
       <c r="E289" s="8">
-        <v>38200</v>
+        <v>40100</v>
       </c>
       <c r="F289" s="8">
-        <v>3388</v>
+        <v>3557</v>
       </c>
       <c r="G289" s="8">
-        <v>2292</v>
+        <v>2406</v>
       </c>
       <c r="H289" s="1">
-        <v>1849</v>
+        <v>1940</v>
       </c>
       <c r="K289" s="16">
         <v>7015</v>
@@ -11662,22 +11665,22 @@
         <v>86</v>
       </c>
       <c r="C290" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D290" s="8">
         <v>11509</v>
       </c>
       <c r="E290" s="8">
-        <v>40100</v>
+        <v>38200</v>
       </c>
       <c r="F290" s="8">
-        <v>3557</v>
+        <v>3388</v>
       </c>
       <c r="G290" s="8">
-        <v>2406</v>
+        <v>2292</v>
       </c>
       <c r="H290" s="1">
-        <v>1940</v>
+        <v>1849</v>
       </c>
       <c r="K290" s="16">
         <v>7015</v>
@@ -11698,7 +11701,7 @@
         <v>86</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D291" s="8">
         <v>11509</v>
@@ -11734,7 +11737,7 @@
         <v>86</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D292" s="8">
         <v>11509</v>
@@ -11767,34 +11770,34 @@
         <v>292</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D293" s="8">
         <v>11509</v>
       </c>
       <c r="E293" s="8">
-        <v>38200</v>
+        <v>36300</v>
       </c>
       <c r="F293" s="8">
-        <v>3388</v>
+        <v>44</v>
       </c>
       <c r="G293" s="8">
-        <v>2292</v>
+        <v>2178</v>
       </c>
       <c r="H293" s="1">
-        <v>1849</v>
-      </c>
-      <c r="K293" s="16">
-        <v>7015</v>
+        <v>1757</v>
+      </c>
+      <c r="K293" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="L293" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M293" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="294" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11803,109 +11806,73 @@
         <v>293</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D294" s="8">
         <v>11509</v>
       </c>
       <c r="E294" s="8">
-        <v>36300</v>
+        <v>50600</v>
       </c>
       <c r="F294" s="8">
-        <v>44</v>
+        <v>4069</v>
       </c>
       <c r="G294" s="8">
-        <v>2178</v>
+        <v>3036</v>
       </c>
       <c r="H294" s="1">
-        <v>1757</v>
-      </c>
-      <c r="K294" s="17" t="s">
-        <v>106</v>
+        <v>2449</v>
+      </c>
+      <c r="I294" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K294" s="16">
+        <v>8990</v>
       </c>
       <c r="L294" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M294" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="295" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="14">
         <f t="shared" si="4"/>
         <v>294</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C295" s="8" t="s">
-        <v>47</v>
+      <c r="B295" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C295" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="D295" s="8">
         <v>11509</v>
       </c>
-      <c r="E295" s="8">
-        <v>50600</v>
+      <c r="E295" s="15">
+        <v>36300</v>
       </c>
       <c r="F295" s="8">
-        <v>4069</v>
+        <v>3220</v>
       </c>
       <c r="G295" s="8">
-        <v>3036</v>
-      </c>
-      <c r="H295" s="1">
-        <v>2449</v>
-      </c>
-      <c r="I295" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K295" s="16">
-        <v>8990</v>
-      </c>
-      <c r="L295" s="8" t="s">
-        <v>47</v>
+        <v>2178</v>
+      </c>
+      <c r="H295" s="14">
+        <v>1757</v>
+      </c>
+      <c r="I295" s="15"/>
+      <c r="K295" s="19">
+        <v>7040</v>
+      </c>
+      <c r="L295" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="M295" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="296" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="14">
-        <f t="shared" si="4"/>
-        <v>295</v>
-      </c>
-      <c r="B296" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C296" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="D296" s="8">
-        <v>11509</v>
-      </c>
-      <c r="E296" s="15">
-        <v>36300</v>
-      </c>
-      <c r="F296" s="8">
-        <v>3220</v>
-      </c>
-      <c r="G296" s="8">
-        <v>2178</v>
-      </c>
-      <c r="H296" s="14">
-        <v>1757</v>
-      </c>
-      <c r="I296" s="15"/>
-      <c r="K296" s="19">
-        <v>7040</v>
-      </c>
-      <c r="L296" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="M296" s="1" t="s">
         <v>116</v>
       </c>
     </row>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1ACDA6-6B76-422C-B52B-01203C972180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE384AD-EF5F-4E47-91A9-BCCF7D4A8375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -577,7 +577,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -639,6 +639,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4058,8 +4061,8 @@
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>84</v>
+      <c r="B82" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>37</v>
@@ -5280,8 +5283,8 @@
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>84</v>
+      <c r="B115" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>37</v>
@@ -6492,8 +6495,8 @@
         <f t="shared" si="2"/>
         <v>147</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>84</v>
+      <c r="B148" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>37</v>
@@ -7692,8 +7695,8 @@
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>84</v>
+      <c r="B181" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>37</v>
@@ -8886,8 +8889,8 @@
         <f t="shared" si="3"/>
         <v>213</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>84</v>
+      <c r="B214" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="C214" s="8" t="s">
         <v>37</v>
@@ -10044,8 +10047,8 @@
         <f t="shared" si="3"/>
         <v>245</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>84</v>
+      <c r="B246" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="C246" s="8" t="s">
         <v>37</v>
@@ -11259,8 +11262,8 @@
         <f t="shared" si="4"/>
         <v>278</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>84</v>
+      <c r="B279" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="C279" s="8" t="s">
         <v>37</v>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE384AD-EF5F-4E47-91A9-BCCF7D4A8375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DF5E3C-D061-4C6F-887D-B8D459937AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="業務承辦人" localSheetId="0">資料頁!$K$2:$K$10</definedName>
     <definedName name="資料" localSheetId="0">資料頁!$A$1:$K$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="116">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -216,9 +216,6 @@
   </si>
   <si>
     <t>郭珮翎</t>
-  </si>
-  <si>
-    <t>盧瑞卿</t>
   </si>
   <si>
     <t>施瀚晶</t>
@@ -1073,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
@@ -1094,7 +1091,7 @@
         <v>2565</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="16">
@@ -1113,7 +1110,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -1134,7 +1131,7 @@
         <v>2216</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="16">
@@ -1153,7 +1150,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
@@ -1190,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -1211,7 +1208,7 @@
         <v>2216</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="16">
@@ -1230,7 +1227,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
@@ -1251,7 +1248,7 @@
         <v>2124</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="16">
@@ -1270,7 +1267,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>25</v>
@@ -1291,14 +1288,14 @@
         <v>2565</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>5</v>
@@ -1310,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>26</v>
@@ -1333,10 +1330,10 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>5</v>
@@ -1348,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
@@ -1370,10 +1367,10 @@
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>5</v>
@@ -1385,7 +1382,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -1406,7 +1403,7 @@
         <v>1849</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="16">
@@ -1425,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>27</v>
@@ -1446,7 +1443,7 @@
         <v>2216</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="16">
         <v>6919</v>
@@ -1464,7 +1461,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>28</v>
@@ -1485,7 +1482,7 @@
         <v>2032</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K12" s="16">
         <v>6919</v>
@@ -1503,7 +1500,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>29</v>
@@ -1539,7 +1536,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>30</v>
@@ -1566,7 +1563,7 @@
         <v>32</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1575,7 +1572,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>31</v>
@@ -1596,7 +1593,7 @@
         <v>2032</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K15" s="16">
         <v>3020</v>
@@ -1605,7 +1602,7 @@
         <v>32</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1614,7 +1611,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>32</v>
@@ -1641,7 +1638,7 @@
         <v>32</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1650,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>33</v>
@@ -1677,7 +1674,7 @@
         <v>33</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1686,7 +1683,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>34</v>
@@ -1707,7 +1704,7 @@
         <v>2449</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K18" s="16">
         <v>7015</v>
@@ -1716,7 +1713,7 @@
         <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1725,7 +1722,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>35</v>
@@ -1746,7 +1743,7 @@
         <v>1849</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K19" s="16">
         <v>7015</v>
@@ -1755,7 +1752,7 @@
         <v>50</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1764,7 +1761,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>36</v>
@@ -1785,7 +1782,7 @@
         <v>1849</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K20" s="16">
         <v>7015</v>
@@ -1794,7 +1791,7 @@
         <v>50</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1803,7 +1800,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>37</v>
@@ -1824,7 +1821,7 @@
         <v>1849</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K21" s="16">
         <v>7015</v>
@@ -1833,7 +1830,7 @@
         <v>50</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1842,7 +1839,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>38</v>
@@ -1863,7 +1860,7 @@
         <v>1849</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K22" s="16">
         <v>7015</v>
@@ -1872,7 +1869,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1881,7 +1878,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>39</v>
@@ -1908,7 +1905,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1917,7 +1914,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>40</v>
@@ -1944,7 +1941,7 @@
         <v>50</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1953,7 +1950,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>41</v>
@@ -1980,7 +1977,7 @@
         <v>50</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1989,7 +1986,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>42</v>
@@ -2010,7 +2007,7 @@
         <v>1940</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K26" s="16">
         <v>7015</v>
@@ -2019,7 +2016,7 @@
         <v>50</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2028,7 +2025,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>43</v>
@@ -2055,7 +2052,7 @@
         <v>50</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2064,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>44</v>
@@ -2085,10 +2082,10 @@
         <v>1849</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K28" s="16">
         <v>7015</v>
@@ -2097,7 +2094,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2106,7 +2103,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>45</v>
@@ -2133,7 +2130,7 @@
         <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2142,7 +2139,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>46</v>
@@ -2163,13 +2160,13 @@
         <v>1757</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2178,7 +2175,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>47</v>
@@ -2199,7 +2196,7 @@
         <v>2332</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K31" s="16">
         <v>8990</v>
@@ -2208,7 +2205,7 @@
         <v>47</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2217,7 +2214,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>48</v>
@@ -2244,7 +2241,7 @@
         <v>48</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2253,7 +2250,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>13</v>
@@ -2289,7 +2286,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>14</v>
@@ -2325,7 +2322,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>15</v>
@@ -2361,7 +2358,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>16</v>
@@ -2397,7 +2394,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>17</v>
@@ -2433,7 +2430,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>25</v>
@@ -2454,10 +2451,10 @@
         <v>2565</v>
       </c>
       <c r="K38" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>5</v>
@@ -2469,7 +2466,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>26</v>
@@ -2490,10 +2487,10 @@
         <v>2449</v>
       </c>
       <c r="K39" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>5</v>
@@ -2505,7 +2502,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>19</v>
@@ -2526,10 +2523,10 @@
         <v>2332</v>
       </c>
       <c r="K40" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>5</v>
@@ -2541,7 +2538,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>20</v>
@@ -2577,7 +2574,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>27</v>
@@ -2613,7 +2610,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>28</v>
@@ -2649,7 +2646,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>29</v>
@@ -2685,7 +2682,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>30</v>
@@ -2712,7 +2709,7 @@
         <v>32</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2721,7 +2718,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>31</v>
@@ -2748,7 +2745,7 @@
         <v>32</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2757,7 +2754,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>32</v>
@@ -2784,7 +2781,7 @@
         <v>32</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2793,7 +2790,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>33</v>
@@ -2820,7 +2817,7 @@
         <v>33</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2829,7 +2826,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>34</v>
@@ -2856,7 +2853,7 @@
         <v>50</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2865,7 +2862,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>35</v>
@@ -2886,10 +2883,10 @@
         <v>0</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K50" s="16">
         <v>7015</v>
@@ -2898,7 +2895,7 @@
         <v>50</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2907,7 +2904,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>36</v>
@@ -2934,7 +2931,7 @@
         <v>50</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2943,7 +2940,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>37</v>
@@ -2964,10 +2961,10 @@
         <v>1849</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K52" s="16">
         <v>7015</v>
@@ -2976,7 +2973,7 @@
         <v>50</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2985,7 +2982,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>49</v>
@@ -3006,10 +3003,10 @@
         <v>1849</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K53" s="16">
         <v>7015</v>
@@ -3018,7 +3015,7 @@
         <v>50</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3027,7 +3024,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>38</v>
@@ -3054,7 +3051,7 @@
         <v>50</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3063,7 +3060,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>39</v>
@@ -3090,7 +3087,7 @@
         <v>50</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3099,7 +3096,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>40</v>
@@ -3126,7 +3123,7 @@
         <v>50</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3135,7 +3132,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>41</v>
@@ -3156,10 +3153,10 @@
         <v>1849</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K57" s="16">
         <v>7015</v>
@@ -3168,7 +3165,7 @@
         <v>50</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3177,7 +3174,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>42</v>
@@ -3204,7 +3201,7 @@
         <v>50</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3213,7 +3210,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>43</v>
@@ -3240,7 +3237,7 @@
         <v>50</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>44</v>
@@ -3276,7 +3273,7 @@
         <v>50</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3285,7 +3282,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>50</v>
@@ -3306,10 +3303,10 @@
         <v>1849</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K61" s="16">
         <v>7015</v>
@@ -3318,7 +3315,7 @@
         <v>50</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3327,7 +3324,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>45</v>
@@ -3354,7 +3351,7 @@
         <v>45</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3363,7 +3360,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>46</v>
@@ -3384,13 +3381,13 @@
         <v>1757</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3399,7 +3396,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>47</v>
@@ -3426,7 +3423,7 @@
         <v>47</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3435,7 +3432,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>48</v>
@@ -3462,7 +3459,7 @@
         <v>48</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3471,7 +3468,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>13</v>
@@ -3507,7 +3504,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>14</v>
@@ -3543,7 +3540,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>15</v>
@@ -3579,7 +3576,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>16</v>
@@ -3615,7 +3612,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>17</v>
@@ -3636,7 +3633,7 @@
         <v>2216</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K70" s="16">
         <v>4040</v>
@@ -3654,7 +3651,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>25</v>
@@ -3675,13 +3672,13 @@
         <v>2681</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K71" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>5</v>
@@ -3693,7 +3690,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>26</v>
@@ -3714,10 +3711,10 @@
         <v>2449</v>
       </c>
       <c r="K72" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>5</v>
@@ -3729,7 +3726,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>19</v>
@@ -3750,13 +3747,13 @@
         <v>2449</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K73" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>5</v>
@@ -3768,7 +3765,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>20</v>
@@ -3804,7 +3801,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>27</v>
@@ -3840,7 +3837,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>28</v>
@@ -3876,7 +3873,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>29</v>
@@ -3912,7 +3909,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>30</v>
@@ -3939,7 +3936,7 @@
         <v>32</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3948,7 +3945,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>31</v>
@@ -3975,7 +3972,7 @@
         <v>32</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3984,7 +3981,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>32</v>
@@ -4011,7 +4008,7 @@
         <v>32</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4020,7 +4017,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>33</v>
@@ -4041,10 +4038,10 @@
         <v>0</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
@@ -4053,7 +4050,7 @@
         <v>33</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4062,7 +4059,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>37</v>
@@ -4083,10 +4080,10 @@
         <v>1757</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K82" s="16">
         <v>1615</v>
@@ -4095,7 +4092,7 @@
         <v>37</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4104,10 +4101,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D83" s="8">
         <v>11503</v>
@@ -4125,10 +4122,10 @@
         <v>1849</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K83" s="16">
         <v>7015</v>
@@ -4137,7 +4134,7 @@
         <v>50</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4146,7 +4143,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>34</v>
@@ -4173,7 +4170,7 @@
         <v>50</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4182,10 +4179,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D85" s="8">
         <v>11503</v>
@@ -4203,10 +4200,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K85" s="16">
         <v>7015</v>
@@ -4215,7 +4212,7 @@
         <v>50</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4224,7 +4221,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>36</v>
@@ -4251,7 +4248,7 @@
         <v>50</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4260,10 +4257,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D87" s="8">
         <v>11503</v>
@@ -4281,10 +4278,10 @@
         <v>1849</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K87" s="16">
         <v>7015</v>
@@ -4293,7 +4290,7 @@
         <v>50</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4302,10 +4299,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D88" s="8">
         <v>11503</v>
@@ -4323,10 +4320,10 @@
         <v>1849</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K88" s="16">
         <v>7015</v>
@@ -4335,7 +4332,7 @@
         <v>50</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4344,7 +4341,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>38</v>
@@ -4371,7 +4368,7 @@
         <v>50</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4380,7 +4377,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>39</v>
@@ -4401,7 +4398,7 @@
         <v>2332</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K90" s="16">
         <v>7015</v>
@@ -4410,7 +4407,7 @@
         <v>50</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4419,7 +4416,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>40</v>
@@ -4446,7 +4443,7 @@
         <v>50</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4455,7 +4452,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>42</v>
@@ -4482,7 +4479,7 @@
         <v>50</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4491,7 +4488,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>43</v>
@@ -4518,7 +4515,7 @@
         <v>50</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4527,7 +4524,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>44</v>
@@ -4555,7 +4552,7 @@
         <v>50</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4564,7 +4561,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>50</v>
@@ -4591,7 +4588,7 @@
         <v>50</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4600,7 +4597,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>45</v>
@@ -4627,7 +4624,7 @@
         <v>45</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4636,7 +4633,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>46</v>
@@ -4657,13 +4654,13 @@
         <v>1757</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4672,7 +4669,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>47</v>
@@ -4699,7 +4696,7 @@
         <v>47</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4708,7 +4705,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>48</v>
@@ -4735,7 +4732,7 @@
         <v>48</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4744,7 +4741,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>13</v>
@@ -4780,7 +4777,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>14</v>
@@ -4816,7 +4813,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>15</v>
@@ -4852,7 +4849,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>16</v>
@@ -4888,7 +4885,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>17</v>
@@ -4924,7 +4921,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>25</v>
@@ -4945,10 +4942,10 @@
         <v>2681</v>
       </c>
       <c r="K105" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>5</v>
@@ -4960,7 +4957,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>26</v>
@@ -4981,10 +4978,10 @@
         <v>2449</v>
       </c>
       <c r="K106" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>5</v>
@@ -4996,7 +4993,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>19</v>
@@ -5017,10 +5014,10 @@
         <v>2449</v>
       </c>
       <c r="K107" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>5</v>
@@ -5032,7 +5029,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>20</v>
@@ -5068,7 +5065,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>27</v>
@@ -5104,7 +5101,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>28</v>
@@ -5140,7 +5137,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>29</v>
@@ -5176,7 +5173,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>30</v>
@@ -5203,7 +5200,7 @@
         <v>32</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5212,7 +5209,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>31</v>
@@ -5239,7 +5236,7 @@
         <v>32</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5248,7 +5245,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>32</v>
@@ -5275,7 +5272,7 @@
         <v>32</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5284,7 +5281,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>37</v>
@@ -5311,7 +5308,7 @@
         <v>37</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5320,10 +5317,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D116" s="8">
         <v>11504</v>
@@ -5347,7 +5344,7 @@
         <v>50</v>
       </c>
       <c r="M116" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5356,7 +5353,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>34</v>
@@ -5377,10 +5374,10 @@
         <v>1940</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K117" s="16">
         <v>7015</v>
@@ -5389,7 +5386,7 @@
         <v>50</v>
       </c>
       <c r="M117" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5398,7 +5395,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>36</v>
@@ -5425,7 +5422,7 @@
         <v>50</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5434,10 +5431,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D119" s="8">
         <v>11504</v>
@@ -5461,7 +5458,7 @@
         <v>50</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5470,10 +5467,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D120" s="8">
         <v>11504</v>
@@ -5497,7 +5494,7 @@
         <v>50</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5506,7 +5503,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>38</v>
@@ -5533,7 +5530,7 @@
         <v>50</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5542,7 +5539,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>39</v>
@@ -5563,7 +5560,7 @@
         <v>2449</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K122" s="16">
         <v>7015</v>
@@ -5572,7 +5569,7 @@
         <v>50</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5581,7 +5578,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>40</v>
@@ -5608,7 +5605,7 @@
         <v>50</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5617,7 +5614,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>42</v>
@@ -5644,7 +5641,7 @@
         <v>50</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5653,7 +5650,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>43</v>
@@ -5680,7 +5677,7 @@
         <v>50</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5689,7 +5686,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>44</v>
@@ -5716,7 +5713,7 @@
         <v>50</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5725,7 +5722,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>50</v>
@@ -5752,7 +5749,7 @@
         <v>50</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5761,7 +5758,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>45</v>
@@ -5788,7 +5785,7 @@
         <v>45</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5797,7 +5794,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>46</v>
@@ -5818,13 +5815,13 @@
         <v>1757</v>
       </c>
       <c r="K129" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5833,7 +5830,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>47</v>
@@ -5860,7 +5857,7 @@
         <v>47</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5869,7 +5866,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>48</v>
@@ -5896,7 +5893,7 @@
         <v>48</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5905,7 +5902,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>13</v>
@@ -5941,7 +5938,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>14</v>
@@ -5977,7 +5974,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>15</v>
@@ -6013,7 +6010,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>16</v>
@@ -6049,7 +6046,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>17</v>
@@ -6085,7 +6082,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>25</v>
@@ -6106,10 +6103,10 @@
         <v>2681</v>
       </c>
       <c r="K137" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>5</v>
@@ -6121,7 +6118,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>26</v>
@@ -6142,16 +6139,16 @@
         <v>0</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K138" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>5</v>
@@ -6163,7 +6160,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>18</v>
@@ -6184,16 +6181,16 @@
         <v>2332</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K139" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>5</v>
@@ -6205,7 +6202,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>19</v>
@@ -6226,10 +6223,10 @@
         <v>2449</v>
       </c>
       <c r="K140" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>5</v>
@@ -6241,7 +6238,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>20</v>
@@ -6277,7 +6274,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>27</v>
@@ -6316,7 +6313,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>28</v>
@@ -6352,7 +6349,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>29</v>
@@ -6388,7 +6385,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>30</v>
@@ -6415,7 +6412,7 @@
         <v>32</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6424,7 +6421,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>31</v>
@@ -6451,7 +6448,7 @@
         <v>32</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6460,7 +6457,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>32</v>
@@ -6487,7 +6484,7 @@
         <v>32</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6496,7 +6493,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>37</v>
@@ -6523,7 +6520,7 @@
         <v>37</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6532,10 +6529,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D149" s="8">
         <v>11505</v>
@@ -6559,7 +6556,7 @@
         <v>50</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6568,10 +6565,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D150" s="8">
         <v>11505</v>
@@ -6589,10 +6586,10 @@
         <v>1849</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K150" s="16">
         <v>7015</v>
@@ -6601,7 +6598,7 @@
         <v>50</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6610,7 +6607,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>36</v>
@@ -6637,7 +6634,7 @@
         <v>50</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6646,10 +6643,10 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D152" s="8">
         <v>11505</v>
@@ -6673,7 +6670,7 @@
         <v>50</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6682,10 +6679,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D153" s="8">
         <v>11505</v>
@@ -6709,7 +6706,7 @@
         <v>50</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6718,7 +6715,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>38</v>
@@ -6745,7 +6742,7 @@
         <v>50</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6754,7 +6751,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>39</v>
@@ -6781,7 +6778,7 @@
         <v>50</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6790,7 +6787,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>40</v>
@@ -6817,7 +6814,7 @@
         <v>50</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6826,10 +6823,10 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D157" s="8">
         <v>11505</v>
@@ -6847,10 +6844,10 @@
         <v>1849</v>
       </c>
       <c r="I157" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K157" s="16">
         <v>7015</v>
@@ -6859,7 +6856,7 @@
         <v>50</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6868,7 +6865,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>42</v>
@@ -6895,7 +6892,7 @@
         <v>50</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6904,7 +6901,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>43</v>
@@ -6931,7 +6928,7 @@
         <v>50</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6940,7 +6937,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>44</v>
@@ -6967,7 +6964,7 @@
         <v>50</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6976,7 +6973,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>50</v>
@@ -7003,7 +7000,7 @@
         <v>50</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7012,7 +7009,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>45</v>
@@ -7039,7 +7036,7 @@
         <v>45</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7048,7 +7045,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>46</v>
@@ -7069,13 +7066,13 @@
         <v>1757</v>
       </c>
       <c r="K163" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L163" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7084,7 +7081,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>47</v>
@@ -7111,7 +7108,7 @@
         <v>47</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7120,7 +7117,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>48</v>
@@ -7147,7 +7144,7 @@
         <v>48</v>
       </c>
       <c r="M165" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7156,7 +7153,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>13</v>
@@ -7192,7 +7189,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>14</v>
@@ -7228,7 +7225,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>15</v>
@@ -7264,7 +7261,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>16</v>
@@ -7300,7 +7297,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>17</v>
@@ -7336,7 +7333,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>25</v>
@@ -7357,10 +7354,10 @@
         <v>2681</v>
       </c>
       <c r="K171" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M171" s="1" t="s">
         <v>5</v>
@@ -7372,7 +7369,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>18</v>
@@ -7393,10 +7390,10 @@
         <v>2332</v>
       </c>
       <c r="K172" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>5</v>
@@ -7408,7 +7405,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>19</v>
@@ -7429,10 +7426,10 @@
         <v>2449</v>
       </c>
       <c r="K173" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M173" s="1" t="s">
         <v>5</v>
@@ -7444,7 +7441,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>20</v>
@@ -7480,7 +7477,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>27</v>
@@ -7516,7 +7513,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>28</v>
@@ -7552,7 +7549,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>29</v>
@@ -7588,7 +7585,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>30</v>
@@ -7615,7 +7612,7 @@
         <v>32</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7624,7 +7621,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>31</v>
@@ -7651,7 +7648,7 @@
         <v>32</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7660,7 +7657,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>32</v>
@@ -7687,7 +7684,7 @@
         <v>32</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7696,7 +7693,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>37</v>
@@ -7723,7 +7720,7 @@
         <v>37</v>
       </c>
       <c r="M181" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7732,10 +7729,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D182" s="8">
         <v>11506</v>
@@ -7759,7 +7756,7 @@
         <v>50</v>
       </c>
       <c r="M182" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7768,10 +7765,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D183" s="8">
         <v>11506</v>
@@ -7795,7 +7792,7 @@
         <v>50</v>
       </c>
       <c r="M183" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7804,7 +7801,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>36</v>
@@ -7831,7 +7828,7 @@
         <v>50</v>
       </c>
       <c r="M184" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7840,10 +7837,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D185" s="8">
         <v>11506</v>
@@ -7867,7 +7864,7 @@
         <v>50</v>
       </c>
       <c r="M185" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7876,10 +7873,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D186" s="8">
         <v>11506</v>
@@ -7903,7 +7900,7 @@
         <v>50</v>
       </c>
       <c r="M186" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7912,7 +7909,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>38</v>
@@ -7939,7 +7936,7 @@
         <v>50</v>
       </c>
       <c r="M187" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7948,7 +7945,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>39</v>
@@ -7975,7 +7972,7 @@
         <v>50</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7984,7 +7981,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>40</v>
@@ -8011,7 +8008,7 @@
         <v>50</v>
       </c>
       <c r="M189" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8020,10 +8017,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D190" s="8">
         <v>11506</v>
@@ -8047,7 +8044,7 @@
         <v>50</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8056,7 +8053,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>42</v>
@@ -8083,7 +8080,7 @@
         <v>50</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8092,7 +8089,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>43</v>
@@ -8119,7 +8116,7 @@
         <v>50</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8128,7 +8125,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>44</v>
@@ -8155,7 +8152,7 @@
         <v>50</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8164,7 +8161,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>50</v>
@@ -8191,7 +8188,7 @@
         <v>50</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8200,7 +8197,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>45</v>
@@ -8221,10 +8218,10 @@
         <v>1757</v>
       </c>
       <c r="I195" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J195" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K195" s="1">
         <v>0</v>
@@ -8233,7 +8230,7 @@
         <v>45</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8242,7 +8239,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>46</v>
@@ -8263,13 +8260,13 @@
         <v>1757</v>
       </c>
       <c r="K196" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L196" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8278,7 +8275,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C197" s="8" t="s">
         <v>47</v>
@@ -8305,7 +8302,7 @@
         <v>47</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="198" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8314,7 +8311,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C198" s="8" t="s">
         <v>48</v>
@@ -8341,7 +8338,7 @@
         <v>48</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="199" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8350,7 +8347,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C199" s="8" t="s">
         <v>13</v>
@@ -8371,10 +8368,10 @@
         <v>2565</v>
       </c>
       <c r="K199" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L199" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="L199" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="M199" s="1" t="s">
         <v>4</v>
@@ -8386,7 +8383,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C200" s="8" t="s">
         <v>14</v>
@@ -8407,10 +8404,10 @@
         <v>2216</v>
       </c>
       <c r="K200" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L200" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="L200" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>4</v>
@@ -8422,7 +8419,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>15</v>
@@ -8443,10 +8440,10 @@
         <v>2032</v>
       </c>
       <c r="K201" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L201" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="L201" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="M201" s="1" t="s">
         <v>4</v>
@@ -8458,7 +8455,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C202" s="8" t="s">
         <v>16</v>
@@ -8479,10 +8476,10 @@
         <v>2216</v>
       </c>
       <c r="K202" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L202" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="L202" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="M202" s="1" t="s">
         <v>4</v>
@@ -8494,7 +8491,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C203" s="8" t="s">
         <v>17</v>
@@ -8515,10 +8512,10 @@
         <v>2216</v>
       </c>
       <c r="K203" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L203" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="L203" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="M203" s="1" t="s">
         <v>4</v>
@@ -8530,7 +8527,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C204" s="8" t="s">
         <v>25</v>
@@ -8551,10 +8548,10 @@
         <v>2681</v>
       </c>
       <c r="K204" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M204" s="1" t="s">
         <v>5</v>
@@ -8566,7 +8563,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C205" s="8" t="s">
         <v>18</v>
@@ -8587,10 +8584,10 @@
         <v>2332</v>
       </c>
       <c r="K205" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M205" s="1" t="s">
         <v>5</v>
@@ -8602,7 +8599,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C206" s="8" t="s">
         <v>19</v>
@@ -8623,10 +8620,10 @@
         <v>2449</v>
       </c>
       <c r="K206" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M206" s="1" t="s">
         <v>5</v>
@@ -8638,7 +8635,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>20</v>
@@ -8674,7 +8671,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C208" s="8" t="s">
         <v>27</v>
@@ -8710,7 +8707,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C209" s="8" t="s">
         <v>28</v>
@@ -8746,7 +8743,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C210" s="8" t="s">
         <v>29</v>
@@ -8782,7 +8779,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C211" s="8" t="s">
         <v>30</v>
@@ -8809,7 +8806,7 @@
         <v>32</v>
       </c>
       <c r="M211" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="212" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8818,7 +8815,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C212" s="8" t="s">
         <v>31</v>
@@ -8845,7 +8842,7 @@
         <v>32</v>
       </c>
       <c r="M212" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8854,7 +8851,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C213" s="8" t="s">
         <v>32</v>
@@ -8881,7 +8878,7 @@
         <v>32</v>
       </c>
       <c r="M213" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8890,7 +8887,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C214" s="8" t="s">
         <v>37</v>
@@ -8917,7 +8914,7 @@
         <v>37</v>
       </c>
       <c r="M214" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8926,10 +8923,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D215" s="8">
         <v>11507</v>
@@ -8953,7 +8950,7 @@
         <v>50</v>
       </c>
       <c r="M215" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8962,10 +8959,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D216" s="8">
         <v>11507</v>
@@ -8989,7 +8986,7 @@
         <v>50</v>
       </c>
       <c r="M216" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8998,7 +8995,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C217" s="8" t="s">
         <v>36</v>
@@ -9025,7 +9022,7 @@
         <v>50</v>
       </c>
       <c r="M217" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9034,10 +9031,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D218" s="8">
         <v>11507</v>
@@ -9061,7 +9058,7 @@
         <v>50</v>
       </c>
       <c r="M218" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9070,10 +9067,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D219" s="8">
         <v>11507</v>
@@ -9097,7 +9094,7 @@
         <v>50</v>
       </c>
       <c r="M219" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="220" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9106,7 +9103,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C220" s="8" t="s">
         <v>38</v>
@@ -9133,7 +9130,7 @@
         <v>50</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="221" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9142,7 +9139,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C221" s="8" t="s">
         <v>39</v>
@@ -9169,7 +9166,7 @@
         <v>50</v>
       </c>
       <c r="M221" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="222" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9178,7 +9175,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C222" s="8" t="s">
         <v>40</v>
@@ -9205,7 +9202,7 @@
         <v>50</v>
       </c>
       <c r="M222" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9214,10 +9211,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D223" s="8">
         <v>11507</v>
@@ -9241,7 +9238,7 @@
         <v>50</v>
       </c>
       <c r="M223" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9250,7 +9247,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C224" s="8" t="s">
         <v>42</v>
@@ -9277,7 +9274,7 @@
         <v>50</v>
       </c>
       <c r="M224" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="225" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9286,7 +9283,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C225" s="8" t="s">
         <v>43</v>
@@ -9313,7 +9310,7 @@
         <v>50</v>
       </c>
       <c r="M225" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="226" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9322,7 +9319,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C226" s="8" t="s">
         <v>44</v>
@@ -9349,7 +9346,7 @@
         <v>50</v>
       </c>
       <c r="M226" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="227" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9358,7 +9355,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C227" s="8" t="s">
         <v>50</v>
@@ -9385,7 +9382,7 @@
         <v>50</v>
       </c>
       <c r="M227" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="228" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9394,7 +9391,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C228" s="8" t="s">
         <v>46</v>
@@ -9415,13 +9412,13 @@
         <v>1757</v>
       </c>
       <c r="K228" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L228" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M228" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="229" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9430,7 +9427,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>47</v>
@@ -9457,7 +9454,7 @@
         <v>47</v>
       </c>
       <c r="M229" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9466,7 +9463,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C230" s="8" t="s">
         <v>48</v>
@@ -9493,7 +9490,7 @@
         <v>48</v>
       </c>
       <c r="M230" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="231" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9502,7 +9499,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>13</v>
@@ -9538,7 +9535,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C232" s="8" t="s">
         <v>14</v>
@@ -9574,7 +9571,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>15</v>
@@ -9610,7 +9607,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C234" s="8" t="s">
         <v>16</v>
@@ -9646,7 +9643,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C235" s="8" t="s">
         <v>17</v>
@@ -9682,7 +9679,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C236" s="8" t="s">
         <v>25</v>
@@ -9703,10 +9700,10 @@
         <v>2681</v>
       </c>
       <c r="K236" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M236" s="1" t="s">
         <v>5</v>
@@ -9718,7 +9715,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>18</v>
@@ -9739,10 +9736,10 @@
         <v>2332</v>
       </c>
       <c r="K237" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M237" s="1" t="s">
         <v>5</v>
@@ -9754,7 +9751,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C238" s="8" t="s">
         <v>19</v>
@@ -9775,10 +9772,10 @@
         <v>2449</v>
       </c>
       <c r="K238" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M238" s="1" t="s">
         <v>5</v>
@@ -9790,7 +9787,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C239" s="8" t="s">
         <v>20</v>
@@ -9826,7 +9823,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C240" s="8" t="s">
         <v>27</v>
@@ -9862,7 +9859,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C241" s="8" t="s">
         <v>28</v>
@@ -9898,7 +9895,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C242" s="8" t="s">
         <v>29</v>
@@ -9934,7 +9931,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C243" s="8" t="s">
         <v>30</v>
@@ -9955,10 +9952,10 @@
         <v>2032</v>
       </c>
       <c r="I243" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K243" s="16">
         <v>3020</v>
@@ -9967,7 +9964,7 @@
         <v>32</v>
       </c>
       <c r="M243" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9976,7 +9973,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C244" s="8" t="s">
         <v>31</v>
@@ -10003,7 +10000,7 @@
         <v>32</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10012,7 +10009,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C245" s="8" t="s">
         <v>32</v>
@@ -10039,7 +10036,7 @@
         <v>32</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10048,7 +10045,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C246" s="8" t="s">
         <v>37</v>
@@ -10075,7 +10072,7 @@
         <v>37</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10084,10 +10081,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C247" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D247" s="8">
         <v>11508</v>
@@ -10111,7 +10108,7 @@
         <v>50</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="248" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10120,10 +10117,10 @@
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D248" s="8">
         <v>11508</v>
@@ -10147,7 +10144,7 @@
         <v>50</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="249" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10156,7 +10153,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C249" s="8" t="s">
         <v>36</v>
@@ -10183,7 +10180,7 @@
         <v>50</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10192,10 +10189,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D250" s="8">
         <v>11508</v>
@@ -10219,7 +10216,7 @@
         <v>50</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10228,10 +10225,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D251" s="8">
         <v>11508</v>
@@ -10255,7 +10252,7 @@
         <v>50</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10264,7 +10261,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C252" s="8" t="s">
         <v>38</v>
@@ -10291,7 +10288,7 @@
         <v>50</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10300,7 +10297,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C253" s="8" t="s">
         <v>39</v>
@@ -10321,10 +10318,10 @@
         <v>2449</v>
       </c>
       <c r="I253" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K253" s="16">
         <v>7015</v>
@@ -10333,7 +10330,7 @@
         <v>50</v>
       </c>
       <c r="M253" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="254" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10342,7 +10339,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C254" s="8" t="s">
         <v>40</v>
@@ -10369,7 +10366,7 @@
         <v>50</v>
       </c>
       <c r="M254" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10378,10 +10375,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D255" s="8">
         <v>11508</v>
@@ -10405,7 +10402,7 @@
         <v>50</v>
       </c>
       <c r="M255" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10414,7 +10411,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C256" s="8" t="s">
         <v>42</v>
@@ -10441,7 +10438,7 @@
         <v>50</v>
       </c>
       <c r="M256" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10450,7 +10447,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C257" s="8" t="s">
         <v>43</v>
@@ -10477,7 +10474,7 @@
         <v>50</v>
       </c>
       <c r="M257" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10486,7 +10483,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C258" s="8" t="s">
         <v>44</v>
@@ -10513,7 +10510,7 @@
         <v>50</v>
       </c>
       <c r="M258" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10522,7 +10519,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C259" s="8" t="s">
         <v>50</v>
@@ -10549,7 +10546,7 @@
         <v>50</v>
       </c>
       <c r="M259" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10558,7 +10555,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C260" s="8" t="s">
         <v>46</v>
@@ -10579,13 +10576,13 @@
         <v>1757</v>
       </c>
       <c r="K260" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L260" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M260" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10594,7 +10591,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C261" s="8" t="s">
         <v>47</v>
@@ -10621,7 +10618,7 @@
         <v>47</v>
       </c>
       <c r="M261" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10630,7 +10627,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C262" s="8" t="s">
         <v>48</v>
@@ -10651,10 +10648,10 @@
         <v>1757</v>
       </c>
       <c r="I262" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K262" s="16">
         <v>9982</v>
@@ -10663,7 +10660,7 @@
         <v>48</v>
       </c>
       <c r="M262" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="263" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10672,10 +10669,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C263" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D263" s="15">
         <v>11508</v>
@@ -10693,19 +10690,19 @@
         <v>1757</v>
       </c>
       <c r="I263" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J263" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K263" s="19">
         <v>7040</v>
       </c>
       <c r="L263" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10714,7 +10711,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C264" s="8" t="s">
         <v>13</v>
@@ -10750,7 +10747,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C265" s="8" t="s">
         <v>14</v>
@@ -10786,7 +10783,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C266" s="8" t="s">
         <v>15</v>
@@ -10807,7 +10804,7 @@
         <v>2124</v>
       </c>
       <c r="I266" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K266" s="16">
         <v>4040</v>
@@ -10825,7 +10822,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>16</v>
@@ -10861,7 +10858,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C268" s="8" t="s">
         <v>17</v>
@@ -10897,7 +10894,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C269" s="8" t="s">
         <v>25</v>
@@ -10918,10 +10915,10 @@
         <v>2681</v>
       </c>
       <c r="K269" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>5</v>
@@ -10933,7 +10930,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C270" s="8" t="s">
         <v>18</v>
@@ -10954,10 +10951,10 @@
         <v>2332</v>
       </c>
       <c r="K270" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>5</v>
@@ -10969,7 +10966,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C271" s="8" t="s">
         <v>19</v>
@@ -10990,10 +10987,10 @@
         <v>2449</v>
       </c>
       <c r="K271" s="16">
-        <v>6588</v>
+        <v>6262</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>5</v>
@@ -11005,7 +11002,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C272" s="8" t="s">
         <v>20</v>
@@ -11041,7 +11038,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C273" s="8" t="s">
         <v>27</v>
@@ -11077,7 +11074,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C274" s="8" t="s">
         <v>28</v>
@@ -11113,7 +11110,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C275" s="8" t="s">
         <v>29</v>
@@ -11149,10 +11146,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D276" s="8">
         <v>11509</v>
@@ -11170,10 +11167,10 @@
         <v>1757</v>
       </c>
       <c r="I276" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K276" s="16">
         <v>3020</v>
@@ -11182,7 +11179,7 @@
         <v>32</v>
       </c>
       <c r="M276" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11191,7 +11188,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C277" s="8" t="s">
         <v>31</v>
@@ -11218,7 +11215,7 @@
         <v>32</v>
       </c>
       <c r="M277" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11227,7 +11224,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C278" s="8" t="s">
         <v>32</v>
@@ -11254,7 +11251,7 @@
         <v>32</v>
       </c>
       <c r="M278" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="279" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11263,7 +11260,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C279" s="8" t="s">
         <v>37</v>
@@ -11290,7 +11287,7 @@
         <v>37</v>
       </c>
       <c r="M279" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="280" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11299,10 +11296,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D280" s="8">
         <v>11509</v>
@@ -11326,7 +11323,7 @@
         <v>50</v>
       </c>
       <c r="M280" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="281" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11335,10 +11332,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D281" s="8">
         <v>11509</v>
@@ -11362,7 +11359,7 @@
         <v>50</v>
       </c>
       <c r="M281" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="282" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11371,7 +11368,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C282" s="8" t="s">
         <v>34</v>
@@ -11392,10 +11389,10 @@
         <v>1849</v>
       </c>
       <c r="I282" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K282" s="16">
         <v>7015</v>
@@ -11404,7 +11401,7 @@
         <v>50</v>
       </c>
       <c r="M282" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="283" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11413,7 +11410,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C283" s="8" t="s">
         <v>36</v>
@@ -11440,7 +11437,7 @@
         <v>50</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11449,10 +11446,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D284" s="8">
         <v>11509</v>
@@ -11476,7 +11473,7 @@
         <v>50</v>
       </c>
       <c r="M284" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11485,10 +11482,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D285" s="8">
         <v>11509</v>
@@ -11512,7 +11509,7 @@
         <v>50</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11521,7 +11518,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C286" s="8" t="s">
         <v>38</v>
@@ -11548,7 +11545,7 @@
         <v>50</v>
       </c>
       <c r="M286" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="287" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11557,7 +11554,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C287" s="8" t="s">
         <v>40</v>
@@ -11584,7 +11581,7 @@
         <v>50</v>
       </c>
       <c r="M287" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="288" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11593,10 +11590,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D288" s="8">
         <v>11509</v>
@@ -11620,7 +11617,7 @@
         <v>50</v>
       </c>
       <c r="M288" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="289" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11629,7 +11626,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C289" s="8" t="s">
         <v>42</v>
@@ -11656,7 +11653,7 @@
         <v>50</v>
       </c>
       <c r="M289" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11665,7 +11662,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C290" s="8" t="s">
         <v>43</v>
@@ -11692,7 +11689,7 @@
         <v>50</v>
       </c>
       <c r="M290" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="291" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11701,7 +11698,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C291" s="8" t="s">
         <v>44</v>
@@ -11728,7 +11725,7 @@
         <v>50</v>
       </c>
       <c r="M291" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="292" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11737,7 +11734,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C292" s="8" t="s">
         <v>50</v>
@@ -11764,7 +11761,7 @@
         <v>50</v>
       </c>
       <c r="M292" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11773,7 +11770,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C293" s="8" t="s">
         <v>46</v>
@@ -11794,13 +11791,13 @@
         <v>1757</v>
       </c>
       <c r="K293" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L293" s="8" t="s">
         <v>46</v>
       </c>
       <c r="M293" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="294" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11809,7 +11806,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C294" s="8" t="s">
         <v>47</v>
@@ -11830,7 +11827,7 @@
         <v>2449</v>
       </c>
       <c r="I294" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K294" s="16">
         <v>8990</v>
@@ -11839,7 +11836,7 @@
         <v>47</v>
       </c>
       <c r="M294" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="295" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11848,10 +11845,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C295" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D295" s="8">
         <v>11509</v>
@@ -11873,10 +11870,10 @@
         <v>7040</v>
       </c>
       <c r="L295" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M295" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DF5E3C-D061-4C6F-887D-B8D459937AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1B4D99-E888-4B44-B752-EF2CF0F75731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="115">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>郭憶如</t>
-  </si>
-  <si>
-    <t>王大中</t>
   </si>
   <si>
     <t>曾莉媛</t>
@@ -1070,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
@@ -1091,7 +1088,7 @@
         <v>2565</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="16">
@@ -1110,7 +1107,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -1131,7 +1128,7 @@
         <v>2216</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="16">
@@ -1150,7 +1147,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
@@ -1187,7 +1184,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -1208,7 +1205,7 @@
         <v>2216</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="16">
@@ -1227,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
@@ -1248,7 +1245,7 @@
         <v>2124</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="16">
@@ -1267,7 +1264,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>25</v>
@@ -1288,7 +1285,7 @@
         <v>2565</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="16">
@@ -1307,7 +1304,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>26</v>
@@ -1345,7 +1342,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
@@ -1382,7 +1379,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -1403,7 +1400,7 @@
         <v>1849</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="16">
@@ -1422,7 +1419,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>27</v>
@@ -1443,7 +1440,7 @@
         <v>2216</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K11" s="16">
         <v>6919</v>
@@ -1461,7 +1458,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>28</v>
@@ -1482,7 +1479,7 @@
         <v>2032</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K12" s="16">
         <v>6919</v>
@@ -1500,7 +1497,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>29</v>
@@ -1536,7 +1533,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>30</v>
@@ -1557,13 +1554,13 @@
         <v>2032</v>
       </c>
       <c r="K14" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1572,7 +1569,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>31</v>
@@ -1593,16 +1590,16 @@
         <v>2032</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K15" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1611,10 +1608,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="3">
         <v>11501</v>
@@ -1632,13 +1629,13 @@
         <v>2032</v>
       </c>
       <c r="K16" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1647,10 +1644,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="3">
         <v>11501</v>
@@ -1671,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1683,10 +1680,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="3">
         <v>11501</v>
@@ -1704,16 +1701,16 @@
         <v>2449</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K18" s="16">
         <v>7015</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1722,10 +1719,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="8">
         <v>11501</v>
@@ -1743,16 +1740,16 @@
         <v>1849</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K19" s="16">
         <v>7015</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1761,10 +1758,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="8">
         <v>11501</v>
@@ -1782,16 +1779,16 @@
         <v>1849</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K20" s="16">
         <v>7015</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1800,10 +1797,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="8">
         <v>11501</v>
@@ -1821,16 +1818,16 @@
         <v>1849</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K21" s="16">
         <v>7015</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1839,10 +1836,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" s="8">
         <v>11501</v>
@@ -1860,16 +1857,16 @@
         <v>1849</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K22" s="16">
         <v>7015</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1878,10 +1875,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" s="8">
         <v>11501</v>
@@ -1902,10 +1899,10 @@
         <v>7015</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1914,10 +1911,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="8">
         <v>11501</v>
@@ -1938,10 +1935,10 @@
         <v>7015</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1950,10 +1947,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D25" s="8">
         <v>11501</v>
@@ -1974,10 +1971,10 @@
         <v>7015</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1986,10 +1983,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" s="8">
         <v>11501</v>
@@ -2007,16 +2004,16 @@
         <v>1940</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K26" s="16">
         <v>7015</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2025,10 +2022,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="8">
         <v>11501</v>
@@ -2049,10 +2046,10 @@
         <v>7015</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2061,10 +2058,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" s="8">
         <v>11501</v>
@@ -2082,19 +2079,19 @@
         <v>1849</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K28" s="16">
         <v>7015</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2103,10 +2100,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D29" s="8">
         <v>11501</v>
@@ -2127,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2139,10 +2136,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" s="8">
         <v>11501</v>
@@ -2160,13 +2157,13 @@
         <v>1757</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2175,10 +2172,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" s="8">
         <v>11501</v>
@@ -2196,16 +2193,16 @@
         <v>2332</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K31" s="16">
         <v>8990</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2214,10 +2211,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D32" s="8">
         <v>11501</v>
@@ -2238,10 +2235,10 @@
         <v>9982</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2250,7 +2247,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>13</v>
@@ -2286,7 +2283,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>14</v>
@@ -2322,7 +2319,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>15</v>
@@ -2358,7 +2355,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>16</v>
@@ -2394,7 +2391,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>17</v>
@@ -2430,7 +2427,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>25</v>
@@ -2466,7 +2463,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>26</v>
@@ -2502,7 +2499,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>19</v>
@@ -2538,7 +2535,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>20</v>
@@ -2574,7 +2571,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>27</v>
@@ -2610,7 +2607,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>28</v>
@@ -2646,7 +2643,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>29</v>
@@ -2682,7 +2679,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>30</v>
@@ -2703,13 +2700,13 @@
         <v>2032</v>
       </c>
       <c r="K45" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2718,7 +2715,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>31</v>
@@ -2739,13 +2736,13 @@
         <v>2032</v>
       </c>
       <c r="K46" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2754,10 +2751,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" s="8">
         <v>11502</v>
@@ -2775,13 +2772,13 @@
         <v>2032</v>
       </c>
       <c r="K47" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2790,10 +2787,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D48" s="8">
         <v>11502</v>
@@ -2814,10 +2811,10 @@
         <v>0</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2826,10 +2823,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" s="8">
         <v>11502</v>
@@ -2850,10 +2847,10 @@
         <v>7015</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2862,10 +2859,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D50" s="8">
         <v>11502</v>
@@ -2883,19 +2880,19 @@
         <v>0</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K50" s="16">
         <v>7015</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2904,10 +2901,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D51" s="8">
         <v>11502</v>
@@ -2928,10 +2925,10 @@
         <v>7015</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2940,10 +2937,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D52" s="8">
         <v>11502</v>
@@ -2961,19 +2958,19 @@
         <v>1849</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K52" s="16">
         <v>7015</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2982,10 +2979,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D53" s="8">
         <v>11502</v>
@@ -3003,19 +3000,19 @@
         <v>1849</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K53" s="16">
         <v>7015</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3024,10 +3021,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D54" s="8">
         <v>11502</v>
@@ -3048,10 +3045,10 @@
         <v>7015</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3060,10 +3057,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D55" s="8">
         <v>11502</v>
@@ -3084,10 +3081,10 @@
         <v>7015</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3096,10 +3093,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D56" s="8">
         <v>11502</v>
@@ -3120,10 +3117,10 @@
         <v>7015</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3132,10 +3129,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D57" s="8">
         <v>11502</v>
@@ -3153,19 +3150,19 @@
         <v>1849</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K57" s="16">
         <v>7015</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3174,10 +3171,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D58" s="8">
         <v>11502</v>
@@ -3198,10 +3195,10 @@
         <v>7015</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3210,10 +3207,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D59" s="8">
         <v>11502</v>
@@ -3234,10 +3231,10 @@
         <v>7015</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3246,10 +3243,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D60" s="8">
         <v>11502</v>
@@ -3270,10 +3267,10 @@
         <v>7015</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3282,10 +3279,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" s="8">
         <v>11502</v>
@@ -3303,19 +3300,19 @@
         <v>1849</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K61" s="16">
         <v>7015</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3324,10 +3321,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D62" s="8">
         <v>11502</v>
@@ -3348,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3360,10 +3357,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D63" s="8">
         <v>11502</v>
@@ -3381,13 +3378,13 @@
         <v>1757</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3396,10 +3393,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D64" s="8">
         <v>11502</v>
@@ -3420,10 +3417,10 @@
         <v>8990</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3432,10 +3429,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D65" s="8">
         <v>11502</v>
@@ -3456,10 +3453,10 @@
         <v>9982</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3468,7 +3465,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>13</v>
@@ -3504,7 +3501,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>14</v>
@@ -3540,7 +3537,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>15</v>
@@ -3576,7 +3573,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>16</v>
@@ -3612,7 +3609,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>17</v>
@@ -3633,7 +3630,7 @@
         <v>2216</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K70" s="16">
         <v>4040</v>
@@ -3651,7 +3648,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>25</v>
@@ -3672,7 +3669,7 @@
         <v>2681</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K71" s="16">
         <v>6262</v>
@@ -3690,7 +3687,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>26</v>
@@ -3726,7 +3723,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>19</v>
@@ -3747,7 +3744,7 @@
         <v>2449</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K73" s="16">
         <v>6262</v>
@@ -3765,7 +3762,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>20</v>
@@ -3801,7 +3798,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>27</v>
@@ -3837,7 +3834,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>28</v>
@@ -3873,7 +3870,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>29</v>
@@ -3909,7 +3906,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>30</v>
@@ -3930,13 +3927,13 @@
         <v>2032</v>
       </c>
       <c r="K78" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L78" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3945,7 +3942,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>31</v>
@@ -3966,13 +3963,13 @@
         <v>2032</v>
       </c>
       <c r="K79" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3981,10 +3978,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D80" s="8">
         <v>11503</v>
@@ -4002,13 +3999,13 @@
         <v>2032</v>
       </c>
       <c r="K80" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4017,10 +4014,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D81" s="8">
         <v>11503</v>
@@ -4038,19 +4035,19 @@
         <v>0</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4059,10 +4056,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D82" s="8">
         <v>11503</v>
@@ -4080,19 +4077,19 @@
         <v>1757</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K82" s="16">
         <v>1615</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4101,7 +4098,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>25</v>
@@ -4122,19 +4119,19 @@
         <v>1849</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K83" s="16">
         <v>7015</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4143,10 +4140,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D84" s="8">
         <v>11503</v>
@@ -4167,10 +4164,10 @@
         <v>7015</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4179,10 +4176,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D85" s="8">
         <v>11503</v>
@@ -4200,19 +4197,19 @@
         <v>0</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K85" s="16">
         <v>7015</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4221,10 +4218,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D86" s="8">
         <v>11503</v>
@@ -4245,10 +4242,10 @@
         <v>7015</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4257,10 +4254,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D87" s="8">
         <v>11503</v>
@@ -4278,19 +4275,19 @@
         <v>1849</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K87" s="16">
         <v>7015</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4299,10 +4296,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D88" s="8">
         <v>11503</v>
@@ -4320,19 +4317,19 @@
         <v>1849</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K88" s="16">
         <v>7015</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4341,10 +4338,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D89" s="8">
         <v>11503</v>
@@ -4365,10 +4362,10 @@
         <v>7015</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4377,10 +4374,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D90" s="8">
         <v>11503</v>
@@ -4398,16 +4395,16 @@
         <v>2332</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K90" s="16">
         <v>7015</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4416,10 +4413,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D91" s="8">
         <v>11503</v>
@@ -4440,10 +4437,10 @@
         <v>7015</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4452,10 +4449,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D92" s="8">
         <v>11503</v>
@@ -4476,10 +4473,10 @@
         <v>7015</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,10 +4485,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D93" s="8">
         <v>11503</v>
@@ -4512,10 +4509,10 @@
         <v>7015</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4524,10 +4521,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D94" s="8">
         <v>11503</v>
@@ -4549,10 +4546,10 @@
         <v>7015</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4561,10 +4558,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D95" s="8">
         <v>11503</v>
@@ -4585,10 +4582,10 @@
         <v>7015</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4597,10 +4594,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D96" s="8">
         <v>11503</v>
@@ -4621,10 +4618,10 @@
         <v>0</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4633,10 +4630,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D97" s="8">
         <v>11503</v>
@@ -4654,13 +4651,13 @@
         <v>1757</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4669,10 +4666,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D98" s="8">
         <v>11503</v>
@@ -4693,10 +4690,10 @@
         <v>8990</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4705,10 +4702,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D99" s="8">
         <v>11503</v>
@@ -4729,10 +4726,10 @@
         <v>9982</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4741,7 +4738,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>13</v>
@@ -4777,7 +4774,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>14</v>
@@ -4813,7 +4810,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>15</v>
@@ -4849,7 +4846,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>16</v>
@@ -4885,7 +4882,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>17</v>
@@ -4921,7 +4918,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>25</v>
@@ -4957,7 +4954,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>26</v>
@@ -4993,7 +4990,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>19</v>
@@ -5029,7 +5026,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>20</v>
@@ -5065,7 +5062,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>27</v>
@@ -5101,7 +5098,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>28</v>
@@ -5137,7 +5134,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>29</v>
@@ -5173,7 +5170,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>30</v>
@@ -5194,13 +5191,13 @@
         <v>2032</v>
       </c>
       <c r="K112" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5209,7 +5206,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>31</v>
@@ -5230,13 +5227,13 @@
         <v>2032</v>
       </c>
       <c r="K113" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5245,10 +5242,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D114" s="8">
         <v>11504</v>
@@ -5266,13 +5263,13 @@
         <v>2032</v>
       </c>
       <c r="K114" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L114" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5281,10 +5278,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D115" s="8">
         <v>11504</v>
@@ -5305,10 +5302,10 @@
         <v>1615</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5317,7 +5314,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>25</v>
@@ -5341,10 +5338,10 @@
         <v>7015</v>
       </c>
       <c r="L116" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M116" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5353,10 +5350,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D117" s="8">
         <v>11504</v>
@@ -5374,19 +5371,19 @@
         <v>1940</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K117" s="16">
         <v>7015</v>
       </c>
       <c r="L117" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M117" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5395,10 +5392,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D118" s="8">
         <v>11504</v>
@@ -5419,10 +5416,10 @@
         <v>7015</v>
       </c>
       <c r="L118" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5431,10 +5428,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D119" s="8">
         <v>11504</v>
@@ -5455,10 +5452,10 @@
         <v>7015</v>
       </c>
       <c r="L119" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5467,10 +5464,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D120" s="8">
         <v>11504</v>
@@ -5491,10 +5488,10 @@
         <v>7015</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5503,10 +5500,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D121" s="8">
         <v>11504</v>
@@ -5527,10 +5524,10 @@
         <v>7015</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5539,10 +5536,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D122" s="8">
         <v>11504</v>
@@ -5560,16 +5557,16 @@
         <v>2449</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K122" s="16">
         <v>7015</v>
       </c>
       <c r="L122" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5578,10 +5575,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D123" s="8">
         <v>11504</v>
@@ -5602,10 +5599,10 @@
         <v>7015</v>
       </c>
       <c r="L123" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5614,10 +5611,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D124" s="8">
         <v>11504</v>
@@ -5638,10 +5635,10 @@
         <v>7015</v>
       </c>
       <c r="L124" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5650,10 +5647,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D125" s="8">
         <v>11504</v>
@@ -5674,10 +5671,10 @@
         <v>7015</v>
       </c>
       <c r="L125" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5686,10 +5683,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D126" s="8">
         <v>11504</v>
@@ -5710,10 +5707,10 @@
         <v>7015</v>
       </c>
       <c r="L126" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5722,10 +5719,10 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D127" s="8">
         <v>11504</v>
@@ -5746,10 +5743,10 @@
         <v>7015</v>
       </c>
       <c r="L127" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5758,10 +5755,10 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D128" s="8">
         <v>11504</v>
@@ -5782,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="L128" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5794,10 +5791,10 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D129" s="8">
         <v>11504</v>
@@ -5815,13 +5812,13 @@
         <v>1757</v>
       </c>
       <c r="K129" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L129" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5830,10 +5827,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D130" s="8">
         <v>11504</v>
@@ -5854,10 +5851,10 @@
         <v>8990</v>
       </c>
       <c r="L130" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5866,10 +5863,10 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D131" s="8">
         <v>11504</v>
@@ -5890,10 +5887,10 @@
         <v>9982</v>
       </c>
       <c r="L131" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5902,7 +5899,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>13</v>
@@ -5938,7 +5935,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>14</v>
@@ -5974,7 +5971,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>15</v>
@@ -6010,7 +6007,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>16</v>
@@ -6046,7 +6043,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>17</v>
@@ -6082,7 +6079,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>25</v>
@@ -6118,7 +6115,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>26</v>
@@ -6139,10 +6136,10 @@
         <v>0</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K138" s="16">
         <v>6262</v>
@@ -6160,7 +6157,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>18</v>
@@ -6181,10 +6178,10 @@
         <v>2332</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K139" s="16">
         <v>6262</v>
@@ -6202,7 +6199,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>19</v>
@@ -6238,7 +6235,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>20</v>
@@ -6274,7 +6271,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>27</v>
@@ -6313,7 +6310,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>28</v>
@@ -6349,7 +6346,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>29</v>
@@ -6385,7 +6382,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>30</v>
@@ -6406,13 +6403,13 @@
         <v>2032</v>
       </c>
       <c r="K145" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L145" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6421,7 +6418,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>31</v>
@@ -6442,13 +6439,13 @@
         <v>2032</v>
       </c>
       <c r="K146" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L146" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6457,10 +6454,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D147" s="8">
         <v>11505</v>
@@ -6478,13 +6475,13 @@
         <v>2032</v>
       </c>
       <c r="K147" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L147" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6493,10 +6490,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D148" s="8">
         <v>11505</v>
@@ -6517,10 +6514,10 @@
         <v>1615</v>
       </c>
       <c r="L148" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6529,7 +6526,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>25</v>
@@ -6553,10 +6550,10 @@
         <v>7015</v>
       </c>
       <c r="L149" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6565,10 +6562,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D150" s="8">
         <v>11505</v>
@@ -6586,19 +6583,19 @@
         <v>1849</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K150" s="16">
         <v>7015</v>
       </c>
       <c r="L150" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6607,10 +6604,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D151" s="8">
         <v>11505</v>
@@ -6631,10 +6628,10 @@
         <v>7015</v>
       </c>
       <c r="L151" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6643,10 +6640,10 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D152" s="8">
         <v>11505</v>
@@ -6667,10 +6664,10 @@
         <v>7015</v>
       </c>
       <c r="L152" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6679,10 +6676,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D153" s="8">
         <v>11505</v>
@@ -6703,10 +6700,10 @@
         <v>7015</v>
       </c>
       <c r="L153" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6715,10 +6712,10 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D154" s="8">
         <v>11505</v>
@@ -6739,10 +6736,10 @@
         <v>7015</v>
       </c>
       <c r="L154" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6751,10 +6748,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D155" s="8">
         <v>11505</v>
@@ -6775,10 +6772,10 @@
         <v>7015</v>
       </c>
       <c r="L155" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6787,10 +6784,10 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D156" s="8">
         <v>11505</v>
@@ -6811,10 +6808,10 @@
         <v>7015</v>
       </c>
       <c r="L156" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6823,10 +6820,10 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D157" s="8">
         <v>11505</v>
@@ -6844,19 +6841,19 @@
         <v>1849</v>
       </c>
       <c r="I157" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K157" s="16">
         <v>7015</v>
       </c>
       <c r="L157" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6865,10 +6862,10 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D158" s="8">
         <v>11505</v>
@@ -6889,10 +6886,10 @@
         <v>7015</v>
       </c>
       <c r="L158" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6901,10 +6898,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D159" s="8">
         <v>11505</v>
@@ -6925,10 +6922,10 @@
         <v>7015</v>
       </c>
       <c r="L159" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6937,10 +6934,10 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D160" s="8">
         <v>11505</v>
@@ -6961,10 +6958,10 @@
         <v>7015</v>
       </c>
       <c r="L160" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6973,10 +6970,10 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D161" s="8">
         <v>11505</v>
@@ -6997,10 +6994,10 @@
         <v>7015</v>
       </c>
       <c r="L161" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7009,10 +7006,10 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D162" s="8">
         <v>11505</v>
@@ -7033,10 +7030,10 @@
         <v>0</v>
       </c>
       <c r="L162" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7045,10 +7042,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D163" s="8">
         <v>11505</v>
@@ -7066,13 +7063,13 @@
         <v>1757</v>
       </c>
       <c r="K163" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L163" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7081,10 +7078,10 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D164" s="8">
         <v>11505</v>
@@ -7105,10 +7102,10 @@
         <v>8990</v>
       </c>
       <c r="L164" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7117,10 +7114,10 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D165" s="8">
         <v>11505</v>
@@ -7141,10 +7138,10 @@
         <v>9982</v>
       </c>
       <c r="L165" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M165" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7153,7 +7150,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>13</v>
@@ -7189,7 +7186,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>14</v>
@@ -7225,7 +7222,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>15</v>
@@ -7261,7 +7258,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>16</v>
@@ -7297,7 +7294,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>17</v>
@@ -7333,7 +7330,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>25</v>
@@ -7369,7 +7366,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>18</v>
@@ -7405,7 +7402,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>19</v>
@@ -7441,7 +7438,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>20</v>
@@ -7477,7 +7474,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>27</v>
@@ -7513,7 +7510,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>28</v>
@@ -7549,7 +7546,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>29</v>
@@ -7585,7 +7582,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>30</v>
@@ -7606,13 +7603,13 @@
         <v>2032</v>
       </c>
       <c r="K178" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L178" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7621,7 +7618,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>31</v>
@@ -7642,13 +7639,13 @@
         <v>2032</v>
       </c>
       <c r="K179" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L179" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7657,10 +7654,10 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D180" s="8">
         <v>11506</v>
@@ -7678,13 +7675,13 @@
         <v>2032</v>
       </c>
       <c r="K180" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L180" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7693,10 +7690,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D181" s="8">
         <v>11506</v>
@@ -7717,10 +7714,10 @@
         <v>1615</v>
       </c>
       <c r="L181" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M181" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7729,7 +7726,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>25</v>
@@ -7753,10 +7750,10 @@
         <v>7015</v>
       </c>
       <c r="L182" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M182" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7765,10 +7762,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D183" s="8">
         <v>11506</v>
@@ -7789,10 +7786,10 @@
         <v>7015</v>
       </c>
       <c r="L183" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M183" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7801,10 +7798,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D184" s="8">
         <v>11506</v>
@@ -7825,10 +7822,10 @@
         <v>7015</v>
       </c>
       <c r="L184" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M184" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7837,10 +7834,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D185" s="8">
         <v>11506</v>
@@ -7861,10 +7858,10 @@
         <v>7015</v>
       </c>
       <c r="L185" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M185" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7873,10 +7870,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D186" s="8">
         <v>11506</v>
@@ -7897,10 +7894,10 @@
         <v>7015</v>
       </c>
       <c r="L186" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M186" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7909,10 +7906,10 @@
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D187" s="8">
         <v>11506</v>
@@ -7933,10 +7930,10 @@
         <v>7015</v>
       </c>
       <c r="L187" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M187" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7945,10 +7942,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D188" s="8">
         <v>11506</v>
@@ -7969,10 +7966,10 @@
         <v>7015</v>
       </c>
       <c r="L188" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7981,10 +7978,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D189" s="8">
         <v>11506</v>
@@ -8005,10 +8002,10 @@
         <v>7015</v>
       </c>
       <c r="L189" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M189" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8017,10 +8014,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D190" s="8">
         <v>11506</v>
@@ -8041,10 +8038,10 @@
         <v>7015</v>
       </c>
       <c r="L190" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8053,10 +8050,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D191" s="8">
         <v>11506</v>
@@ -8077,10 +8074,10 @@
         <v>7015</v>
       </c>
       <c r="L191" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8089,10 +8086,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D192" s="8">
         <v>11506</v>
@@ -8113,10 +8110,10 @@
         <v>7015</v>
       </c>
       <c r="L192" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8125,10 +8122,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D193" s="8">
         <v>11506</v>
@@ -8149,10 +8146,10 @@
         <v>7015</v>
       </c>
       <c r="L193" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8161,10 +8158,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D194" s="8">
         <v>11506</v>
@@ -8185,10 +8182,10 @@
         <v>7015</v>
       </c>
       <c r="L194" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8197,10 +8194,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D195" s="8">
         <v>11506</v>
@@ -8218,19 +8215,19 @@
         <v>1757</v>
       </c>
       <c r="I195" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J195" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K195" s="1">
         <v>0</v>
       </c>
       <c r="L195" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8239,10 +8236,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D196" s="8">
         <v>11506</v>
@@ -8260,13 +8257,13 @@
         <v>1757</v>
       </c>
       <c r="K196" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L196" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8275,10 +8272,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D197" s="8">
         <v>11506</v>
@@ -8299,10 +8296,10 @@
         <v>8990</v>
       </c>
       <c r="L197" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="198" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8311,10 +8308,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D198" s="8">
         <v>11506</v>
@@ -8335,10 +8332,10 @@
         <v>9982</v>
       </c>
       <c r="L198" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="199" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8347,7 +8344,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C199" s="8" t="s">
         <v>13</v>
@@ -8368,10 +8365,10 @@
         <v>2565</v>
       </c>
       <c r="K199" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L199" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="L199" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="M199" s="1" t="s">
         <v>4</v>
@@ -8383,7 +8380,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C200" s="8" t="s">
         <v>14</v>
@@ -8404,10 +8401,10 @@
         <v>2216</v>
       </c>
       <c r="K200" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L200" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="L200" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>4</v>
@@ -8419,7 +8416,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>15</v>
@@ -8440,10 +8437,10 @@
         <v>2032</v>
       </c>
       <c r="K201" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L201" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="L201" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="M201" s="1" t="s">
         <v>4</v>
@@ -8455,7 +8452,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C202" s="8" t="s">
         <v>16</v>
@@ -8476,10 +8473,10 @@
         <v>2216</v>
       </c>
       <c r="K202" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L202" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="L202" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="M202" s="1" t="s">
         <v>4</v>
@@ -8491,7 +8488,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C203" s="8" t="s">
         <v>17</v>
@@ -8512,10 +8509,10 @@
         <v>2216</v>
       </c>
       <c r="K203" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L203" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="L203" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="M203" s="1" t="s">
         <v>4</v>
@@ -8527,7 +8524,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C204" s="8" t="s">
         <v>25</v>
@@ -8563,7 +8560,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C205" s="8" t="s">
         <v>18</v>
@@ -8599,7 +8596,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C206" s="8" t="s">
         <v>19</v>
@@ -8635,7 +8632,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>20</v>
@@ -8671,7 +8668,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C208" s="8" t="s">
         <v>27</v>
@@ -8707,7 +8704,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C209" s="8" t="s">
         <v>28</v>
@@ -8743,7 +8740,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C210" s="8" t="s">
         <v>29</v>
@@ -8779,7 +8776,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C211" s="8" t="s">
         <v>30</v>
@@ -8800,13 +8797,13 @@
         <v>2032</v>
       </c>
       <c r="K211" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L211" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M211" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="212" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8815,7 +8812,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C212" s="8" t="s">
         <v>31</v>
@@ -8836,13 +8833,13 @@
         <v>2032</v>
       </c>
       <c r="K212" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L212" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M212" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8851,10 +8848,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D213" s="8">
         <v>11507</v>
@@ -8872,13 +8869,13 @@
         <v>2032</v>
       </c>
       <c r="K213" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L213" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M213" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8887,10 +8884,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D214" s="8">
         <v>11507</v>
@@ -8911,10 +8908,10 @@
         <v>1615</v>
       </c>
       <c r="L214" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M214" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8923,7 +8920,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C215" s="8" t="s">
         <v>25</v>
@@ -8947,10 +8944,10 @@
         <v>7015</v>
       </c>
       <c r="L215" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M215" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8959,10 +8956,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D216" s="8">
         <v>11507</v>
@@ -8983,10 +8980,10 @@
         <v>7015</v>
       </c>
       <c r="L216" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M216" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8995,10 +8992,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D217" s="8">
         <v>11507</v>
@@ -9019,10 +9016,10 @@
         <v>7015</v>
       </c>
       <c r="L217" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M217" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9031,10 +9028,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D218" s="8">
         <v>11507</v>
@@ -9055,10 +9052,10 @@
         <v>7015</v>
       </c>
       <c r="L218" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M218" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9067,10 +9064,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D219" s="8">
         <v>11507</v>
@@ -9091,10 +9088,10 @@
         <v>7015</v>
       </c>
       <c r="L219" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M219" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="220" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9103,10 +9100,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D220" s="8">
         <v>11507</v>
@@ -9127,10 +9124,10 @@
         <v>7015</v>
       </c>
       <c r="L220" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="221" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9139,10 +9136,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D221" s="8">
         <v>11507</v>
@@ -9163,10 +9160,10 @@
         <v>7015</v>
       </c>
       <c r="L221" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M221" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="222" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9175,10 +9172,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D222" s="8">
         <v>11507</v>
@@ -9199,10 +9196,10 @@
         <v>7015</v>
       </c>
       <c r="L222" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M222" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9211,10 +9208,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D223" s="8">
         <v>11507</v>
@@ -9235,10 +9232,10 @@
         <v>7015</v>
       </c>
       <c r="L223" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M223" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9247,10 +9244,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D224" s="8">
         <v>11507</v>
@@ -9271,10 +9268,10 @@
         <v>7015</v>
       </c>
       <c r="L224" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M224" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="225" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9283,10 +9280,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D225" s="8">
         <v>11507</v>
@@ -9307,10 +9304,10 @@
         <v>7015</v>
       </c>
       <c r="L225" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M225" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="226" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9319,10 +9316,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D226" s="8">
         <v>11507</v>
@@ -9343,10 +9340,10 @@
         <v>7015</v>
       </c>
       <c r="L226" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M226" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="227" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9355,10 +9352,10 @@
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D227" s="8">
         <v>11507</v>
@@ -9379,10 +9376,10 @@
         <v>7015</v>
       </c>
       <c r="L227" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M227" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="228" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9391,10 +9388,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D228" s="8">
         <v>11507</v>
@@ -9412,13 +9409,13 @@
         <v>1757</v>
       </c>
       <c r="K228" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L228" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M228" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="229" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9427,10 +9424,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D229" s="8">
         <v>11507</v>
@@ -9451,10 +9448,10 @@
         <v>8990</v>
       </c>
       <c r="L229" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M229" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9463,10 +9460,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D230" s="8">
         <v>11507</v>
@@ -9487,10 +9484,10 @@
         <v>9982</v>
       </c>
       <c r="L230" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M230" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="231" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9499,7 +9496,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>13</v>
@@ -9535,7 +9532,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C232" s="8" t="s">
         <v>14</v>
@@ -9571,7 +9568,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>15</v>
@@ -9607,7 +9604,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C234" s="8" t="s">
         <v>16</v>
@@ -9643,7 +9640,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C235" s="8" t="s">
         <v>17</v>
@@ -9679,7 +9676,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C236" s="8" t="s">
         <v>25</v>
@@ -9715,7 +9712,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>18</v>
@@ -9751,7 +9748,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C238" s="8" t="s">
         <v>19</v>
@@ -9787,7 +9784,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C239" s="8" t="s">
         <v>20</v>
@@ -9823,7 +9820,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C240" s="8" t="s">
         <v>27</v>
@@ -9859,7 +9856,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C241" s="8" t="s">
         <v>28</v>
@@ -9895,7 +9892,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C242" s="8" t="s">
         <v>29</v>
@@ -9931,7 +9928,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C243" s="8" t="s">
         <v>30</v>
@@ -9952,19 +9949,19 @@
         <v>2032</v>
       </c>
       <c r="I243" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K243" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L243" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M243" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9973,7 +9970,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C244" s="8" t="s">
         <v>31</v>
@@ -9994,13 +9991,13 @@
         <v>2032</v>
       </c>
       <c r="K244" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L244" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10009,10 +10006,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D245" s="8">
         <v>11508</v>
@@ -10030,13 +10027,13 @@
         <v>2032</v>
       </c>
       <c r="K245" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L245" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10045,10 +10042,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C246" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D246" s="8">
         <v>11508</v>
@@ -10069,10 +10066,10 @@
         <v>1615</v>
       </c>
       <c r="L246" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10081,7 +10078,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C247" s="8" t="s">
         <v>25</v>
@@ -10105,10 +10102,10 @@
         <v>7015</v>
       </c>
       <c r="L247" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="248" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10117,10 +10114,10 @@
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D248" s="8">
         <v>11508</v>
@@ -10141,10 +10138,10 @@
         <v>7015</v>
       </c>
       <c r="L248" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="249" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10153,10 +10150,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D249" s="8">
         <v>11508</v>
@@ -10177,10 +10174,10 @@
         <v>7015</v>
       </c>
       <c r="L249" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10189,10 +10186,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D250" s="8">
         <v>11508</v>
@@ -10213,10 +10210,10 @@
         <v>7015</v>
       </c>
       <c r="L250" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10225,10 +10222,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D251" s="8">
         <v>11508</v>
@@ -10249,10 +10246,10 @@
         <v>7015</v>
       </c>
       <c r="L251" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10261,10 +10258,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D252" s="8">
         <v>11508</v>
@@ -10285,10 +10282,10 @@
         <v>7015</v>
       </c>
       <c r="L252" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10297,10 +10294,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D253" s="8">
         <v>11508</v>
@@ -10318,19 +10315,19 @@
         <v>2449</v>
       </c>
       <c r="I253" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K253" s="16">
         <v>7015</v>
       </c>
       <c r="L253" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M253" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="254" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10339,10 +10336,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D254" s="8">
         <v>11508</v>
@@ -10363,10 +10360,10 @@
         <v>7015</v>
       </c>
       <c r="L254" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M254" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10375,10 +10372,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D255" s="8">
         <v>11508</v>
@@ -10399,10 +10396,10 @@
         <v>7015</v>
       </c>
       <c r="L255" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M255" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10411,10 +10408,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D256" s="8">
         <v>11508</v>
@@ -10435,10 +10432,10 @@
         <v>7015</v>
       </c>
       <c r="L256" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M256" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10447,10 +10444,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C257" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D257" s="8">
         <v>11508</v>
@@ -10471,10 +10468,10 @@
         <v>7015</v>
       </c>
       <c r="L257" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M257" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10483,10 +10480,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D258" s="8">
         <v>11508</v>
@@ -10507,10 +10504,10 @@
         <v>7015</v>
       </c>
       <c r="L258" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M258" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10519,10 +10516,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D259" s="8">
         <v>11508</v>
@@ -10543,10 +10540,10 @@
         <v>7015</v>
       </c>
       <c r="L259" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M259" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10555,10 +10552,10 @@
         <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D260" s="8">
         <v>11508</v>
@@ -10576,13 +10573,13 @@
         <v>1757</v>
       </c>
       <c r="K260" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L260" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M260" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10591,10 +10588,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D261" s="8">
         <v>11508</v>
@@ -10615,10 +10612,10 @@
         <v>8990</v>
       </c>
       <c r="L261" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M261" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10627,10 +10624,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D262" s="8">
         <v>11508</v>
@@ -10648,19 +10645,19 @@
         <v>1757</v>
       </c>
       <c r="I262" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K262" s="16">
         <v>9982</v>
       </c>
       <c r="L262" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M262" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="263" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10669,10 +10666,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C263" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D263" s="15">
         <v>11508</v>
@@ -10690,19 +10687,19 @@
         <v>1757</v>
       </c>
       <c r="I263" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J263" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K263" s="19">
         <v>7040</v>
       </c>
       <c r="L263" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10711,7 +10708,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C264" s="8" t="s">
         <v>13</v>
@@ -10747,7 +10744,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C265" s="8" t="s">
         <v>14</v>
@@ -10783,7 +10780,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C266" s="8" t="s">
         <v>15</v>
@@ -10804,7 +10801,7 @@
         <v>2124</v>
       </c>
       <c r="I266" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K266" s="16">
         <v>4040</v>
@@ -10822,7 +10819,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>16</v>
@@ -10858,7 +10855,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C268" s="8" t="s">
         <v>17</v>
@@ -10894,7 +10891,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C269" s="8" t="s">
         <v>25</v>
@@ -10930,7 +10927,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C270" s="8" t="s">
         <v>18</v>
@@ -10966,7 +10963,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C271" s="8" t="s">
         <v>19</v>
@@ -11002,7 +10999,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C272" s="8" t="s">
         <v>20</v>
@@ -11038,7 +11035,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C273" s="8" t="s">
         <v>27</v>
@@ -11074,7 +11071,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C274" s="8" t="s">
         <v>28</v>
@@ -11110,7 +11107,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C275" s="8" t="s">
         <v>29</v>
@@ -11146,10 +11143,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D276" s="8">
         <v>11509</v>
@@ -11167,19 +11164,19 @@
         <v>1757</v>
       </c>
       <c r="I276" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K276" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L276" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M276" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11188,7 +11185,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C277" s="8" t="s">
         <v>31</v>
@@ -11209,13 +11206,13 @@
         <v>2032</v>
       </c>
       <c r="K277" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L277" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M277" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11224,10 +11221,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D278" s="8">
         <v>11509</v>
@@ -11245,13 +11242,13 @@
         <v>2032</v>
       </c>
       <c r="K278" s="16">
-        <v>3020</v>
+        <v>8791</v>
       </c>
       <c r="L278" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M278" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="279" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11260,10 +11257,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D279" s="8">
         <v>11509</v>
@@ -11284,10 +11281,10 @@
         <v>1615</v>
       </c>
       <c r="L279" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M279" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="280" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11296,7 +11293,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C280" s="8" t="s">
         <v>25</v>
@@ -11320,10 +11317,10 @@
         <v>7015</v>
       </c>
       <c r="L280" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M280" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="281" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11332,10 +11329,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D281" s="8">
         <v>11509</v>
@@ -11356,10 +11353,10 @@
         <v>7015</v>
       </c>
       <c r="L281" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M281" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="282" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11368,10 +11365,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D282" s="8">
         <v>11509</v>
@@ -11389,19 +11386,19 @@
         <v>1849</v>
       </c>
       <c r="I282" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K282" s="16">
         <v>7015</v>
       </c>
       <c r="L282" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M282" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="283" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11410,10 +11407,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D283" s="8">
         <v>11509</v>
@@ -11434,10 +11431,10 @@
         <v>7015</v>
       </c>
       <c r="L283" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11446,10 +11443,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D284" s="8">
         <v>11509</v>
@@ -11470,10 +11467,10 @@
         <v>7015</v>
       </c>
       <c r="L284" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M284" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11482,10 +11479,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D285" s="8">
         <v>11509</v>
@@ -11506,10 +11503,10 @@
         <v>7015</v>
       </c>
       <c r="L285" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11518,10 +11515,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D286" s="8">
         <v>11509</v>
@@ -11542,10 +11539,10 @@
         <v>7015</v>
       </c>
       <c r="L286" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M286" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="287" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11554,10 +11551,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D287" s="8">
         <v>11509</v>
@@ -11578,10 +11575,10 @@
         <v>7015</v>
       </c>
       <c r="L287" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M287" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="288" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11590,10 +11587,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D288" s="8">
         <v>11509</v>
@@ -11614,10 +11611,10 @@
         <v>7015</v>
       </c>
       <c r="L288" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M288" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="289" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11626,10 +11623,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D289" s="8">
         <v>11509</v>
@@ -11650,10 +11647,10 @@
         <v>7015</v>
       </c>
       <c r="L289" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M289" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11662,10 +11659,10 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C290" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D290" s="8">
         <v>11509</v>
@@ -11686,10 +11683,10 @@
         <v>7015</v>
       </c>
       <c r="L290" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M290" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="291" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11698,10 +11695,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D291" s="8">
         <v>11509</v>
@@ -11722,10 +11719,10 @@
         <v>7015</v>
       </c>
       <c r="L291" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M291" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="292" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11734,10 +11731,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D292" s="8">
         <v>11509</v>
@@ -11758,10 +11755,10 @@
         <v>7015</v>
       </c>
       <c r="L292" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M292" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11770,10 +11767,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D293" s="8">
         <v>11509</v>
@@ -11791,13 +11788,13 @@
         <v>1757</v>
       </c>
       <c r="K293" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L293" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M293" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="294" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11806,10 +11803,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D294" s="8">
         <v>11509</v>
@@ -11827,16 +11824,16 @@
         <v>2449</v>
       </c>
       <c r="I294" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K294" s="16">
         <v>8990</v>
       </c>
       <c r="L294" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M294" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="295" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11845,10 +11842,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C295" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D295" s="8">
         <v>11509</v>
@@ -11870,10 +11867,10 @@
         <v>7040</v>
       </c>
       <c r="L295" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M295" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1B4D99-E888-4B44-B752-EF2CF0F75731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17E24EE-62AD-4C8E-A128-C429F822A45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="116">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -435,6 +435,10 @@
   </si>
   <si>
     <t>教育部_補助大專校院精進校務經營計畫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>王大中</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1610,8 +1614,8 @@
       <c r="B16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>31</v>
+      <c r="C16" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D16" s="3">
         <v>11501</v>
@@ -2753,8 +2757,8 @@
       <c r="B47" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>31</v>
+      <c r="C47" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D47" s="8">
         <v>11502</v>
@@ -3980,8 +3984,8 @@
       <c r="B80" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>31</v>
+      <c r="C80" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D80" s="8">
         <v>11503</v>
@@ -5244,8 +5248,8 @@
       <c r="B114" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>31</v>
+      <c r="C114" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D114" s="8">
         <v>11504</v>
@@ -6456,8 +6460,8 @@
       <c r="B147" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C147" s="8" t="s">
-        <v>31</v>
+      <c r="C147" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D147" s="8">
         <v>11505</v>
@@ -7656,8 +7660,8 @@
       <c r="B180" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C180" s="8" t="s">
-        <v>31</v>
+      <c r="C180" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D180" s="8">
         <v>11506</v>
@@ -8850,8 +8854,8 @@
       <c r="B213" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C213" s="8" t="s">
-        <v>31</v>
+      <c r="C213" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D213" s="8">
         <v>11507</v>
@@ -10008,8 +10012,8 @@
       <c r="B245" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C245" s="8" t="s">
-        <v>31</v>
+      <c r="C245" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D245" s="8">
         <v>11508</v>
@@ -11223,8 +11227,8 @@
       <c r="B278" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C278" s="8" t="s">
-        <v>31</v>
+      <c r="C278" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="D278" s="8">
         <v>11509</v>
@@ -11875,6 +11879,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <autoFilter ref="A1:M295" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17E24EE-62AD-4C8E-A128-C429F822A45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2E1602-4568-4514-BBD6-AD4D17EC2E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9944,13 +9944,13 @@
         <v>42000</v>
       </c>
       <c r="F243" s="8">
-        <v>3725</v>
+        <v>0</v>
       </c>
       <c r="G243" s="8">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="H243" s="1">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I243" s="8" t="s">
         <v>57</v>
@@ -11879,7 +11879,6 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <autoFilter ref="A1:M295" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -5,18 +5,18 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v9_匯入資料格式修正版\專案計畫人員保費查詢系統_v6_修正doc錯誤與多承辦人\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v10.2_修正版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7815B72-6E2D-4187-89AE-0CC8E47DB22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5FC40B-DB6E-4F94-B602-7F46DF8E3B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料頁" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$L$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$M$883</definedName>
     <definedName name="全健康保險費" localSheetId="0">資料頁!#REF!</definedName>
     <definedName name="序號" localSheetId="0">資料頁!$A$2:$A$10</definedName>
     <definedName name="投保薪額">資料頁!$F$2:$F$10</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4681" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4687" uniqueCount="122">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -448,6 +448,18 @@
   </si>
   <si>
     <t>雇主負擔保費</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-115L01-02,(補)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-115L01-04,(補)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-115L01-03,(補)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9698,7 +9710,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -9731,7 +9743,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -9764,7 +9776,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <f t="shared" ref="A259:A295" si="4">ROW()-1</f>
         <v>258</v>
@@ -9797,7 +9809,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <f t="shared" si="4"/>
         <v>259</v>
@@ -9829,8 +9841,11 @@
       <c r="L260" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="261" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M260" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <f t="shared" si="4"/>
         <v>260</v>
@@ -9863,7 +9878,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <f t="shared" si="4"/>
         <v>261</v>
@@ -9902,7 +9917,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="263" spans="1:12" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="14">
         <f t="shared" si="4"/>
         <v>262</v>
@@ -9941,7 +9956,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -9974,7 +9989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -10007,7 +10022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -10043,7 +10058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -10076,7 +10091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -10109,7 +10124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -10142,7 +10157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -10175,7 +10190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -10208,7 +10223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -10781,7 +10796,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <f t="shared" si="4"/>
         <v>288</v>
@@ -10814,7 +10829,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -10847,7 +10862,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -10880,7 +10895,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -10913,7 +10928,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -10945,8 +10960,11 @@
       <c r="L293" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="294" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M293" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <f t="shared" si="4"/>
         <v>293</v>
@@ -10982,7 +11000,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="295" spans="1:12" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="14">
         <f t="shared" si="4"/>
         <v>294</v>
@@ -11016,7 +11034,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <f>ROW()-1</f>
         <v>295</v>
@@ -11053,7 +11071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <f t="shared" ref="A297:A360" si="5">ROW()-1</f>
         <v>296</v>
@@ -11090,7 +11108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <f t="shared" si="5"/>
         <v>297</v>
@@ -11124,7 +11142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <f t="shared" si="5"/>
         <v>298</v>
@@ -11161,7 +11179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <f t="shared" si="5"/>
         <v>299</v>
@@ -11198,7 +11216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <f t="shared" si="5"/>
         <v>300</v>
@@ -11235,7 +11253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <f t="shared" si="5"/>
         <v>301</v>
@@ -11270,7 +11288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <f t="shared" si="5"/>
         <v>302</v>
@@ -11304,7 +11322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <f t="shared" si="5"/>
         <v>303</v>
@@ -19424,7 +19442,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
         <f t="shared" si="8"/>
         <v>544</v>
@@ -19457,7 +19475,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -19490,7 +19508,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="547" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -19529,7 +19547,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -19562,7 +19580,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="549" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -19595,7 +19613,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -19628,7 +19646,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
         <f t="shared" si="8"/>
         <v>550</v>
@@ -19661,7 +19679,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
         <f t="shared" si="8"/>
         <v>551</v>
@@ -19694,7 +19712,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="553" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
         <f t="shared" ref="A553:A589" si="9">ROW()-1</f>
         <v>552</v>
@@ -19727,7 +19745,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="554" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
         <f t="shared" si="9"/>
         <v>553</v>
@@ -19759,8 +19777,11 @@
       <c r="L554" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="555" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M554" s="20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
         <f t="shared" si="9"/>
         <v>554</v>
@@ -19793,7 +19814,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="556" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
         <f t="shared" si="9"/>
         <v>555</v>
@@ -19832,7 +19853,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="557" spans="1:12" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="14">
         <f t="shared" si="9"/>
         <v>556</v>
@@ -19871,7 +19892,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="558" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
         <f t="shared" si="9"/>
         <v>557</v>
@@ -19904,7 +19925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="559" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
         <f t="shared" si="9"/>
         <v>558</v>
@@ -19937,7 +19958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
         <f t="shared" si="9"/>
         <v>559</v>
@@ -20513,7 +20534,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="577" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
         <f t="shared" si="9"/>
         <v>576</v>
@@ -20546,7 +20567,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="578" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
         <f t="shared" si="9"/>
         <v>577</v>
@@ -20579,7 +20600,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="579" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
         <f t="shared" si="9"/>
         <v>578</v>
@@ -20612,7 +20633,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="580" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
         <f t="shared" si="9"/>
         <v>579</v>
@@ -20645,7 +20666,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="581" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
         <f t="shared" si="9"/>
         <v>580</v>
@@ -20678,7 +20699,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="582" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
         <f t="shared" si="9"/>
         <v>581</v>
@@ -20711,7 +20732,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="583" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
         <f t="shared" si="9"/>
         <v>582</v>
@@ -20744,7 +20765,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="584" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1">
         <f t="shared" si="9"/>
         <v>583</v>
@@ -20777,7 +20798,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="585" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1">
         <f t="shared" si="9"/>
         <v>584</v>
@@ -20810,7 +20831,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="586" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
         <f t="shared" si="9"/>
         <v>585</v>
@@ -20843,7 +20864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="587" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
         <f t="shared" si="9"/>
         <v>586</v>
@@ -20875,8 +20896,11 @@
       <c r="L587" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="588" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M587" s="20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
         <f t="shared" si="9"/>
         <v>587</v>
@@ -20912,7 +20936,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="589" spans="1:12" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="14">
         <f t="shared" si="9"/>
         <v>588</v>
@@ -20946,7 +20970,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="590" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1">
         <f>ROW()-1</f>
         <v>589</v>
@@ -20983,7 +21007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="591" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1">
         <f t="shared" ref="A591:A654" si="10">ROW()-1</f>
         <v>590</v>
@@ -21020,7 +21044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="592" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1">
         <f t="shared" si="10"/>
         <v>591</v>
@@ -29156,7 +29180,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="833" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="1">
         <f t="shared" si="13"/>
         <v>832</v>
@@ -29189,7 +29213,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="834" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="1">
         <f t="shared" si="13"/>
         <v>833</v>
@@ -29222,7 +29246,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="835" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="1">
         <f t="shared" si="13"/>
         <v>834</v>
@@ -29255,7 +29279,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="836" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="1">
         <f t="shared" si="13"/>
         <v>835</v>
@@ -29288,7 +29312,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="837" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="1">
         <f t="shared" si="13"/>
         <v>836</v>
@@ -29321,7 +29345,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="838" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="1">
         <f t="shared" si="13"/>
         <v>837</v>
@@ -29354,7 +29378,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="839" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="1">
         <f t="shared" si="13"/>
         <v>838</v>
@@ -29387,7 +29411,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="840" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="1">
         <f t="shared" si="13"/>
         <v>839</v>
@@ -29420,7 +29444,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="841" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="1">
         <f t="shared" si="13"/>
         <v>840</v>
@@ -29459,7 +29483,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="842" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="1">
         <f t="shared" si="13"/>
         <v>841</v>
@@ -29492,7 +29516,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="843" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="1">
         <f t="shared" si="13"/>
         <v>842</v>
@@ -29525,7 +29549,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="844" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="1">
         <f t="shared" si="13"/>
         <v>843</v>
@@ -29558,7 +29582,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="845" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="1">
         <f t="shared" si="13"/>
         <v>844</v>
@@ -29591,7 +29615,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="846" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="1">
         <f t="shared" si="13"/>
         <v>845</v>
@@ -29624,7 +29648,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="847" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="1">
         <f t="shared" ref="A847:A883" si="14">ROW()-1</f>
         <v>846</v>
@@ -29657,7 +29681,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="848" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="1">
         <f t="shared" si="14"/>
         <v>847</v>
@@ -29688,6 +29712,9 @@
       </c>
       <c r="L848" s="1" t="s">
         <v>59</v>
+      </c>
+      <c r="M848" s="20" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="849" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -30773,7 +30800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="881" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="1">
         <f t="shared" si="14"/>
         <v>880</v>
@@ -30805,8 +30832,11 @@
       <c r="L881" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="882" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M881" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="882" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="1">
         <f t="shared" si="14"/>
         <v>881</v>
@@ -30842,7 +30872,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="883" spans="1:12" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="14">
         <f t="shared" si="14"/>
         <v>882</v>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v10.2_修正版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5FC40B-DB6E-4F94-B602-7F46DF8E3B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C264428-EB34-4947-AA1C-DE8A9B6A8A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4687" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="128">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -462,6 +462,90 @@
     <t>210-115L01-03,(補)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>152-115L01-02,(補)</t>
+  </si>
+  <si>
+    <t>152-115L01-03,(補)</t>
+  </si>
+  <si>
+    <t>152-115L01-04,(補)</t>
+  </si>
+  <si>
+    <r>
+      <t>134-115L01-03(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>補</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>134-115L01-04(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>補</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>134-115L01-02(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>補</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -470,7 +554,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -562,6 +646,25 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -604,7 +707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -673,6 +776,12 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1422,6 +1531,9 @@
       <c r="L10" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="M10" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1458,6 +1570,9 @@
       <c r="L11" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M11" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1494,6 +1609,9 @@
       <c r="L12" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M12" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2185,7 +2303,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2218,7 +2336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2251,7 +2369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2284,7 +2402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2317,7 +2435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2350,7 +2468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2383,7 +2501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2416,7 +2534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2449,7 +2567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2481,8 +2599,11 @@
       <c r="L41" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M41" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2514,8 +2635,11 @@
       <c r="L42" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2547,8 +2671,11 @@
       <c r="L43" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2581,7 +2708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -2614,7 +2741,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -2647,7 +2774,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -2680,7 +2807,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3271,7 +3398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3304,7 +3431,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3337,7 +3464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <f t="shared" ref="A67:A130" si="1">ROW()-1</f>
         <v>66</v>
@@ -3370,7 +3497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -3403,7 +3530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -3436,7 +3563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -3472,7 +3599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -3508,7 +3635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -3541,7 +3668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -3577,7 +3704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -3609,8 +3736,11 @@
       <c r="L74" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M74" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -3642,8 +3772,11 @@
       <c r="L75" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M75" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -3675,8 +3808,11 @@
       <c r="L76" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M76" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -3709,7 +3845,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -3742,7 +3878,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -3775,7 +3911,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -4376,7 +4512,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -4409,7 +4545,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -4442,7 +4578,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -4475,7 +4611,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -4508,7 +4644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4541,7 +4677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4574,7 +4710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -4607,7 +4743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4640,7 +4776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4673,7 +4809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4706,7 +4842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4739,7 +4875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4771,8 +4907,11 @@
       <c r="L108" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M108" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -4804,8 +4943,11 @@
       <c r="L109" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M109" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4837,8 +4979,11 @@
       <c r="L110" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M110" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4871,7 +5016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -5441,7 +5586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -5474,7 +5619,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -5507,7 +5652,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <f t="shared" ref="A131:A194" si="2">ROW()-1</f>
         <v>130</v>
@@ -5540,7 +5685,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <f t="shared" si="2"/>
         <v>131</v>
@@ -5573,7 +5718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <f t="shared" si="2"/>
         <v>132</v>
@@ -5606,7 +5751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -5639,7 +5784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -5672,7 +5817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -5705,7 +5850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -5738,7 +5883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5777,7 +5922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5816,7 +5961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5849,7 +5994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5881,8 +6026,11 @@
       <c r="L141" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="142" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M141" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5917,8 +6065,11 @@
       <c r="L142" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M142" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5950,8 +6101,11 @@
       <c r="L143" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M143" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -6524,7 +6678,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -6557,7 +6711,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -6590,7 +6744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -6623,7 +6777,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -6656,7 +6810,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -6689,7 +6843,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -6722,7 +6876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -6755,7 +6909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -6788,7 +6942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -6821,7 +6975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -6854,7 +7008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -6887,7 +7041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -6920,7 +7074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -6953,7 +7107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -6985,8 +7139,11 @@
       <c r="L174" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M174" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -7018,8 +7175,11 @@
       <c r="L175" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="176" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M175" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -7050,6 +7210,9 @@
       </c>
       <c r="L176" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="M176" s="23" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="177" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7580,7 +7743,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -7613,7 +7776,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -7646,7 +7809,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <f t="shared" ref="A195:A258" si="3">ROW()-1</f>
         <v>194</v>
@@ -7685,7 +7848,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <f t="shared" si="3"/>
         <v>195</v>
@@ -7718,7 +7881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <f t="shared" si="3"/>
         <v>196</v>
@@ -7751,7 +7914,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <f t="shared" si="3"/>
         <v>197</v>
@@ -7784,7 +7947,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <f t="shared" si="3"/>
         <v>198</v>
@@ -7817,7 +7980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -7850,7 +8013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -7883,7 +8046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -7916,7 +8079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -7949,7 +8112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -7982,7 +8145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -8015,7 +8178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -8048,7 +8211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -8080,8 +8243,11 @@
       <c r="L207" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="208" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M207" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -8113,8 +8279,11 @@
       <c r="L208" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="209" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M208" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -8146,8 +8315,11 @@
       <c r="L209" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="210" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M209" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -8180,7 +8352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -8212,8 +8384,11 @@
       <c r="L211" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="212" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M211" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -8245,8 +8420,11 @@
       <c r="L212" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="213" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M212" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -8278,8 +8456,11 @@
       <c r="L213" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="214" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M213" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -8312,7 +8493,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -8345,7 +8526,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -8378,7 +8559,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -8411,7 +8592,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -8444,7 +8625,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -8477,7 +8658,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -8510,7 +8691,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -8543,7 +8724,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -8576,7 +8757,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -8609,7 +8790,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -8642,7 +8823,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -8675,7 +8856,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -8708,7 +8889,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -8741,7 +8922,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -8774,7 +8955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -8807,7 +8988,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -8840,7 +9021,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -8873,7 +9054,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -8906,7 +9087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -8939,7 +9120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -8972,7 +9153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -9005,7 +9186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -9038,7 +9219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -9071,7 +9252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -9104,7 +9285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -9136,8 +9317,11 @@
       <c r="L239" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="240" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M239" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -9169,8 +9353,11 @@
       <c r="L240" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="241" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M240" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -9202,8 +9389,11 @@
       <c r="L241" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="242" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M241" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -9236,7 +9426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -9274,8 +9464,11 @@
       <c r="L243" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="244" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M243" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -9307,8 +9500,11 @@
       <c r="L244" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="245" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M244" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -9340,8 +9536,11 @@
       <c r="L245" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="246" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M245" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -9374,7 +9573,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -9407,7 +9606,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -9440,7 +9639,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -9473,7 +9672,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -9506,7 +9705,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -9539,7 +9738,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -9572,7 +9771,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -9611,7 +9810,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -9644,7 +9843,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -9677,7 +9876,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -10255,8 +10454,11 @@
       <c r="L272" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="273" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M272" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <f t="shared" si="4"/>
         <v>272</v>
@@ -10288,8 +10490,11 @@
       <c r="L273" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="274" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M273" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <f t="shared" si="4"/>
         <v>273</v>
@@ -10321,8 +10526,11 @@
       <c r="L274" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="275" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M274" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <f t="shared" si="4"/>
         <v>274</v>
@@ -10355,7 +10563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -10393,8 +10601,11 @@
       <c r="L276" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="277" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M276" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -10426,8 +10637,11 @@
       <c r="L277" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="278" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M277" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -10459,8 +10673,11 @@
       <c r="L278" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="279" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M278" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <f t="shared" si="4"/>
         <v>278</v>
@@ -10493,7 +10710,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -10526,7 +10743,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -10559,7 +10776,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <f t="shared" si="4"/>
         <v>281</v>
@@ -10598,7 +10815,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <f t="shared" si="4"/>
         <v>282</v>
@@ -10631,7 +10848,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -10664,7 +10881,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <f t="shared" si="4"/>
         <v>284</v>
@@ -10697,7 +10914,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <f t="shared" si="4"/>
         <v>285</v>
@@ -10730,7 +10947,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <f t="shared" si="4"/>
         <v>286</v>
@@ -10763,7 +10980,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -11358,8 +11575,11 @@
       <c r="L304" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="305" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M304" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <f t="shared" si="5"/>
         <v>304</v>
@@ -11394,8 +11614,11 @@
       <c r="L305" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="306" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M305" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <f t="shared" si="5"/>
         <v>305</v>
@@ -11430,8 +11653,11 @@
       <c r="L306" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="307" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M306" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <f t="shared" si="5"/>
         <v>306</v>
@@ -11464,7 +11690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <f t="shared" si="5"/>
         <v>307</v>
@@ -11497,7 +11723,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <f t="shared" si="5"/>
         <v>308</v>
@@ -11533,7 +11759,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <f t="shared" si="5"/>
         <v>309</v>
@@ -11566,7 +11792,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <f t="shared" si="5"/>
         <v>310</v>
@@ -11599,7 +11825,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <f t="shared" si="5"/>
         <v>311</v>
@@ -11635,7 +11861,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <f t="shared" si="5"/>
         <v>312</v>
@@ -11671,7 +11897,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <f t="shared" si="5"/>
         <v>313</v>
@@ -11707,7 +11933,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <f t="shared" si="5"/>
         <v>314</v>
@@ -11743,7 +11969,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <f t="shared" si="5"/>
         <v>315</v>
@@ -11779,7 +12005,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <f t="shared" si="5"/>
         <v>316</v>
@@ -11812,7 +12038,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <f t="shared" si="5"/>
         <v>317</v>
@@ -11845,7 +12071,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <f t="shared" si="5"/>
         <v>318</v>
@@ -11878,7 +12104,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <f t="shared" si="5"/>
         <v>319</v>
@@ -11914,7 +12140,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <f t="shared" si="5"/>
         <v>320</v>
@@ -11947,7 +12173,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <f t="shared" si="5"/>
         <v>321</v>
@@ -11986,7 +12212,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <f t="shared" si="5"/>
         <v>322</v>
@@ -12019,7 +12245,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <f t="shared" si="5"/>
         <v>323</v>
@@ -12052,7 +12278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <f t="shared" si="5"/>
         <v>324</v>
@@ -12088,7 +12314,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <f t="shared" si="5"/>
         <v>325</v>
@@ -12121,7 +12347,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <f t="shared" si="5"/>
         <v>326</v>
@@ -12154,7 +12380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <f t="shared" si="5"/>
         <v>327</v>
@@ -12187,7 +12413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <f t="shared" si="5"/>
         <v>328</v>
@@ -12220,7 +12446,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -12253,7 +12479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <f t="shared" si="5"/>
         <v>330</v>
@@ -12286,7 +12512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <f t="shared" si="5"/>
         <v>331</v>
@@ -12319,7 +12545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <f t="shared" si="5"/>
         <v>332</v>
@@ -12352,7 +12578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <f t="shared" si="5"/>
         <v>333</v>
@@ -12385,7 +12611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <f t="shared" si="5"/>
         <v>334</v>
@@ -12417,8 +12643,11 @@
       <c r="L335" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="336" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M335" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <f t="shared" si="5"/>
         <v>335</v>
@@ -12450,8 +12679,11 @@
       <c r="L336" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="337" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M336" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <f t="shared" si="5"/>
         <v>336</v>
@@ -12483,8 +12715,11 @@
       <c r="L337" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="338" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M337" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <f t="shared" si="5"/>
         <v>337</v>
@@ -12517,7 +12752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <f t="shared" si="5"/>
         <v>338</v>
@@ -12550,7 +12785,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <f t="shared" si="5"/>
         <v>339</v>
@@ -12583,7 +12818,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <f t="shared" si="5"/>
         <v>340</v>
@@ -12616,7 +12851,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <f t="shared" si="5"/>
         <v>341</v>
@@ -12649,7 +12884,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <f t="shared" si="5"/>
         <v>342</v>
@@ -12682,7 +12917,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <f t="shared" si="5"/>
         <v>343</v>
@@ -12721,7 +12956,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <f t="shared" si="5"/>
         <v>344</v>
@@ -12754,7 +12989,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <f t="shared" si="5"/>
         <v>345</v>
@@ -12793,7 +13028,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <f t="shared" si="5"/>
         <v>346</v>
@@ -12832,7 +13067,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <f t="shared" si="5"/>
         <v>347</v>
@@ -12865,7 +13100,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <f t="shared" si="5"/>
         <v>348</v>
@@ -12898,7 +13133,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <f t="shared" si="5"/>
         <v>349</v>
@@ -12931,7 +13166,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <f t="shared" si="5"/>
         <v>350</v>
@@ -12970,7 +13205,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <f t="shared" si="5"/>
         <v>351</v>
@@ -13003,7 +13238,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <f t="shared" si="5"/>
         <v>352</v>
@@ -13036,7 +13271,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <f t="shared" si="5"/>
         <v>353</v>
@@ -13069,7 +13304,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <f t="shared" si="5"/>
         <v>354</v>
@@ -13108,7 +13343,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <f t="shared" si="5"/>
         <v>355</v>
@@ -13141,7 +13376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <f t="shared" si="5"/>
         <v>356</v>
@@ -13174,7 +13409,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <f t="shared" si="5"/>
         <v>357</v>
@@ -13207,7 +13442,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <f t="shared" si="5"/>
         <v>358</v>
@@ -13240,7 +13475,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <f t="shared" si="5"/>
         <v>359</v>
@@ -13273,7 +13508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <f t="shared" ref="A361:A424" si="6">ROW()-1</f>
         <v>360</v>
@@ -13306,7 +13541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <f t="shared" si="6"/>
         <v>361</v>
@@ -13339,7 +13574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <f t="shared" si="6"/>
         <v>362</v>
@@ -13372,7 +13607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <f t="shared" si="6"/>
         <v>363</v>
@@ -13408,7 +13643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <f t="shared" si="6"/>
         <v>364</v>
@@ -13444,7 +13679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <f t="shared" si="6"/>
         <v>365</v>
@@ -13477,7 +13712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <f t="shared" si="6"/>
         <v>366</v>
@@ -13513,7 +13748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <f t="shared" si="6"/>
         <v>367</v>
@@ -13545,8 +13780,11 @@
       <c r="L368" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="369" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M368" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <f t="shared" si="6"/>
         <v>368</v>
@@ -13578,8 +13816,11 @@
       <c r="L369" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="370" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M369" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <f t="shared" si="6"/>
         <v>369</v>
@@ -13611,8 +13852,11 @@
       <c r="L370" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="371" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M370" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <f t="shared" si="6"/>
         <v>370</v>
@@ -13645,7 +13889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <f t="shared" si="6"/>
         <v>371</v>
@@ -13678,7 +13922,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <f t="shared" si="6"/>
         <v>372</v>
@@ -13711,7 +13955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <f t="shared" si="6"/>
         <v>373</v>
@@ -13744,7 +13988,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <f t="shared" si="6"/>
         <v>374</v>
@@ -13783,7 +14027,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <f t="shared" si="6"/>
         <v>375</v>
@@ -13822,7 +14066,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <f t="shared" si="6"/>
         <v>376</v>
@@ -13861,7 +14105,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <f t="shared" si="6"/>
         <v>377</v>
@@ -13894,7 +14138,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <f t="shared" si="6"/>
         <v>378</v>
@@ -13933,7 +14177,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <f t="shared" si="6"/>
         <v>379</v>
@@ -13966,7 +14210,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <f t="shared" si="6"/>
         <v>380</v>
@@ -14005,7 +14249,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <f t="shared" si="6"/>
         <v>381</v>
@@ -14044,7 +14288,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <f t="shared" si="6"/>
         <v>382</v>
@@ -14077,7 +14321,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <f t="shared" si="6"/>
         <v>383</v>
@@ -14642,7 +14886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <f t="shared" si="6"/>
         <v>400</v>
@@ -14675,7 +14919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <f t="shared" si="6"/>
         <v>401</v>
@@ -14707,8 +14951,11 @@
       <c r="L402" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="403" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M402" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <f t="shared" si="6"/>
         <v>402</v>
@@ -14740,8 +14987,11 @@
       <c r="L403" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="404" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M403" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <f t="shared" si="6"/>
         <v>403</v>
@@ -14773,8 +15023,11 @@
       <c r="L404" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="405" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M404" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -14807,7 +15060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -14840,7 +15093,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -14873,7 +15126,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -14906,7 +15159,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -14939,7 +15192,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -14972,7 +15225,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -15011,7 +15264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -15044,7 +15297,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -15077,7 +15330,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -15110,7 +15363,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -15143,7 +15396,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -15713,7 +15966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
         <f t="shared" si="7"/>
         <v>432</v>
@@ -15752,7 +16005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
         <f t="shared" si="7"/>
         <v>433</v>
@@ -15785,7 +16038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
         <f t="shared" si="7"/>
         <v>434</v>
@@ -15817,8 +16070,11 @@
       <c r="L435" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="436" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M435" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="436" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <f t="shared" si="7"/>
         <v>435</v>
@@ -15853,8 +16109,11 @@
       <c r="L436" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="437" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M436" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="437" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
         <f t="shared" si="7"/>
         <v>436</v>
@@ -15886,8 +16145,11 @@
       <c r="L437" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="438" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M437" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="438" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
         <f t="shared" si="7"/>
         <v>437</v>
@@ -15920,7 +16182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
         <f t="shared" si="7"/>
         <v>438</v>
@@ -15953,7 +16215,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <f t="shared" si="7"/>
         <v>439</v>
@@ -15986,7 +16248,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <f t="shared" si="7"/>
         <v>440</v>
@@ -16019,7 +16281,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
         <f t="shared" si="7"/>
         <v>441</v>
@@ -16052,7 +16314,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
         <f t="shared" si="7"/>
         <v>442</v>
@@ -16085,7 +16347,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
         <f t="shared" si="7"/>
         <v>443</v>
@@ -16124,7 +16386,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
         <f t="shared" si="7"/>
         <v>444</v>
@@ -16157,7 +16419,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <f t="shared" si="7"/>
         <v>445</v>
@@ -16190,7 +16452,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
         <f t="shared" si="7"/>
         <v>446</v>
@@ -16223,7 +16485,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
         <f t="shared" si="7"/>
         <v>447</v>
@@ -16790,7 +17052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
         <f t="shared" si="7"/>
         <v>464</v>
@@ -16823,7 +17085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <f t="shared" si="7"/>
         <v>465</v>
@@ -16856,7 +17118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
         <f t="shared" si="7"/>
         <v>466</v>
@@ -16889,7 +17151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
         <f t="shared" si="7"/>
         <v>467</v>
@@ -16921,8 +17183,11 @@
       <c r="L468" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="469" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M468" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
         <f t="shared" si="7"/>
         <v>468</v>
@@ -16954,8 +17219,11 @@
       <c r="L469" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="470" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M469" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="470" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
         <f t="shared" si="7"/>
         <v>469</v>
@@ -16987,8 +17255,11 @@
       <c r="L470" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="471" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M470" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <f t="shared" si="7"/>
         <v>470</v>
@@ -17021,7 +17292,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
         <f t="shared" si="7"/>
         <v>471</v>
@@ -17054,7 +17325,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
         <f t="shared" si="7"/>
         <v>472</v>
@@ -17087,7 +17358,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
         <f t="shared" si="7"/>
         <v>473</v>
@@ -17120,7 +17391,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
         <f t="shared" si="7"/>
         <v>474</v>
@@ -17153,7 +17424,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <f t="shared" si="7"/>
         <v>475</v>
@@ -17186,7 +17457,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
         <f t="shared" si="7"/>
         <v>476</v>
@@ -17219,7 +17490,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
         <f t="shared" si="7"/>
         <v>477</v>
@@ -17252,7 +17523,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
         <f t="shared" si="7"/>
         <v>478</v>
@@ -17285,7 +17556,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <f t="shared" si="7"/>
         <v>479</v>
@@ -17852,7 +18123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <f t="shared" si="8"/>
         <v>496</v>
@@ -17885,7 +18156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
         <f t="shared" si="8"/>
         <v>497</v>
@@ -17918,7 +18189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <f t="shared" si="8"/>
         <v>498</v>
@@ -17951,7 +18222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
         <f t="shared" si="8"/>
         <v>499</v>
@@ -17984,7 +18255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
@@ -18016,8 +18287,11 @@
       <c r="L501" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="502" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M501" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="502" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <f t="shared" si="8"/>
         <v>501</v>
@@ -18049,8 +18323,11 @@
       <c r="L502" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="503" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M502" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
         <f t="shared" si="8"/>
         <v>502</v>
@@ -18082,8 +18359,11 @@
       <c r="L503" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="504" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M503" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="504" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
         <f t="shared" si="8"/>
         <v>503</v>
@@ -18116,7 +18396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="505" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <f t="shared" si="8"/>
         <v>504</v>
@@ -18148,8 +18428,11 @@
       <c r="L505" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="506" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M505" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
         <f t="shared" si="8"/>
         <v>505</v>
@@ -18181,8 +18464,11 @@
       <c r="L506" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="507" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M506" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="507" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
         <f t="shared" si="8"/>
         <v>506</v>
@@ -18214,8 +18500,11 @@
       <c r="L507" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="508" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M507" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="508" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
         <f t="shared" si="8"/>
         <v>507</v>
@@ -18248,7 +18537,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
         <f t="shared" si="8"/>
         <v>508</v>
@@ -18281,7 +18570,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
         <f t="shared" si="8"/>
         <v>509</v>
@@ -18314,7 +18603,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="511" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
         <f t="shared" si="8"/>
         <v>510</v>
@@ -18347,7 +18636,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="512" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <f t="shared" si="8"/>
         <v>511</v>
@@ -18908,7 +19197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="529" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
         <f t="shared" si="8"/>
         <v>528</v>
@@ -18941,7 +19230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
         <f t="shared" si="8"/>
         <v>529</v>
@@ -18974,7 +19263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="531" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
         <f t="shared" si="8"/>
         <v>530</v>
@@ -19007,7 +19296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="532" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <f t="shared" si="8"/>
         <v>531</v>
@@ -19040,7 +19329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="533" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
         <f t="shared" si="8"/>
         <v>532</v>
@@ -19072,8 +19361,11 @@
       <c r="L533" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="534" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M533" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
         <f t="shared" si="8"/>
         <v>533</v>
@@ -19105,8 +19397,11 @@
       <c r="L534" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="535" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M534" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
         <f t="shared" si="8"/>
         <v>534</v>
@@ -19138,8 +19433,11 @@
       <c r="L535" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="536" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M535" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
         <f t="shared" si="8"/>
         <v>535</v>
@@ -19172,7 +19470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="537" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -19210,8 +19508,11 @@
       <c r="L537" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="538" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M537" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <f t="shared" si="8"/>
         <v>537</v>
@@ -19243,8 +19544,11 @@
       <c r="L538" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="539" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M538" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
         <f t="shared" si="8"/>
         <v>538</v>
@@ -19276,8 +19580,11 @@
       <c r="L539" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="540" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M539" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
         <f t="shared" si="8"/>
         <v>539</v>
@@ -19310,7 +19617,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="541" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
         <f t="shared" si="8"/>
         <v>540</v>
@@ -19343,7 +19650,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="542" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
         <f t="shared" si="8"/>
         <v>541</v>
@@ -19376,7 +19683,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="543" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
         <f t="shared" si="8"/>
         <v>542</v>
@@ -19409,7 +19716,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="544" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
         <f t="shared" si="8"/>
         <v>543</v>
@@ -19994,7 +20301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
         <f t="shared" si="9"/>
         <v>560</v>
@@ -20027,7 +20334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
         <f t="shared" si="9"/>
         <v>561</v>
@@ -20060,7 +20367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="563" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
         <f t="shared" si="9"/>
         <v>562</v>
@@ -20093,7 +20400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="564" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
         <f t="shared" si="9"/>
         <v>563</v>
@@ -20126,7 +20433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="565" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
         <f t="shared" si="9"/>
         <v>564</v>
@@ -20159,7 +20466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="566" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
         <f t="shared" si="9"/>
         <v>565</v>
@@ -20191,8 +20498,11 @@
       <c r="L566" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="567" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M566" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
         <f t="shared" si="9"/>
         <v>566</v>
@@ -20224,8 +20534,11 @@
       <c r="L567" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="568" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M567" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
         <f t="shared" si="9"/>
         <v>567</v>
@@ -20257,8 +20570,11 @@
       <c r="L568" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="569" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M568" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
         <f t="shared" si="9"/>
         <v>568</v>
@@ -20291,7 +20607,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="570" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
         <f t="shared" si="9"/>
         <v>569</v>
@@ -20329,8 +20645,11 @@
       <c r="L570" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="571" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M570" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
         <f t="shared" si="9"/>
         <v>570</v>
@@ -20362,8 +20681,11 @@
       <c r="L571" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="572" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M571" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
         <f t="shared" si="9"/>
         <v>571</v>
@@ -20395,8 +20717,11 @@
       <c r="L572" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="573" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M572" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
         <f t="shared" si="9"/>
         <v>572</v>
@@ -20429,7 +20754,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="574" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
         <f t="shared" si="9"/>
         <v>573</v>
@@ -20462,7 +20787,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="575" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
         <f t="shared" si="9"/>
         <v>574</v>
@@ -20495,7 +20820,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="576" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
         <f t="shared" si="9"/>
         <v>575</v>
@@ -21078,7 +21403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="593" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1">
         <f t="shared" si="10"/>
         <v>592</v>
@@ -21115,7 +21440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="594" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1">
         <f t="shared" si="10"/>
         <v>593</v>
@@ -21152,7 +21477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="595" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1">
         <f t="shared" si="10"/>
         <v>594</v>
@@ -21189,7 +21514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1">
         <f t="shared" si="10"/>
         <v>595</v>
@@ -21224,7 +21549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="597" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1">
         <f t="shared" si="10"/>
         <v>596</v>
@@ -21258,7 +21583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="598" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1">
         <f t="shared" si="10"/>
         <v>597</v>
@@ -21294,8 +21619,11 @@
       <c r="L598" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="599" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M598" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1">
         <f t="shared" si="10"/>
         <v>598</v>
@@ -21330,8 +21658,11 @@
       <c r="L599" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="600" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M599" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1">
         <f t="shared" si="10"/>
         <v>599</v>
@@ -21366,8 +21697,11 @@
       <c r="L600" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="601" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M600" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1">
         <f t="shared" si="10"/>
         <v>600</v>
@@ -21400,7 +21734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="602" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
         <f t="shared" si="10"/>
         <v>601</v>
@@ -21433,7 +21767,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="603" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1">
         <f t="shared" si="10"/>
         <v>602</v>
@@ -21469,7 +21803,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="604" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1">
         <f t="shared" si="10"/>
         <v>603</v>
@@ -21502,7 +21836,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="605" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1">
         <f t="shared" si="10"/>
         <v>604</v>
@@ -21535,7 +21869,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="606" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1">
         <f t="shared" si="10"/>
         <v>605</v>
@@ -21571,7 +21905,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="607" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1">
         <f t="shared" si="10"/>
         <v>606</v>
@@ -21607,7 +21941,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="608" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1">
         <f t="shared" si="10"/>
         <v>607</v>
@@ -22189,7 +22523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="625" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1">
         <f t="shared" si="10"/>
         <v>624</v>
@@ -22222,7 +22556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="626" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1">
         <f t="shared" si="10"/>
         <v>625</v>
@@ -22255,7 +22589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="627" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1">
         <f t="shared" si="10"/>
         <v>626</v>
@@ -22288,7 +22622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="628" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1">
         <f t="shared" si="10"/>
         <v>627</v>
@@ -22321,7 +22655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1">
         <f t="shared" si="10"/>
         <v>628</v>
@@ -22353,8 +22687,11 @@
       <c r="L629" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="630" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M629" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="630" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1">
         <f t="shared" si="10"/>
         <v>629</v>
@@ -22386,8 +22723,11 @@
       <c r="L630" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="631" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M630" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1">
         <f t="shared" si="10"/>
         <v>630</v>
@@ -22419,8 +22759,11 @@
       <c r="L631" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="632" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M631" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1">
         <f t="shared" si="10"/>
         <v>631</v>
@@ -22453,7 +22796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="633" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1">
         <f t="shared" si="10"/>
         <v>632</v>
@@ -22486,7 +22829,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="634" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1">
         <f t="shared" si="10"/>
         <v>633</v>
@@ -22519,7 +22862,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="635" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1">
         <f t="shared" si="10"/>
         <v>634</v>
@@ -22552,7 +22895,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="636" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1">
         <f t="shared" si="10"/>
         <v>635</v>
@@ -22585,7 +22928,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="637" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1">
         <f t="shared" si="10"/>
         <v>636</v>
@@ -22618,7 +22961,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="638" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1">
         <f t="shared" si="10"/>
         <v>637</v>
@@ -22657,7 +23000,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="639" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="1">
         <f t="shared" si="10"/>
         <v>638</v>
@@ -22690,7 +23033,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="640" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1">
         <f t="shared" si="10"/>
         <v>639</v>
@@ -23275,7 +23618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="657" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="1">
         <f t="shared" si="11"/>
         <v>656</v>
@@ -23308,7 +23651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="658" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="1">
         <f t="shared" si="11"/>
         <v>657</v>
@@ -23344,7 +23687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="659" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="1">
         <f t="shared" si="11"/>
         <v>658</v>
@@ -23380,7 +23723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="1">
         <f t="shared" si="11"/>
         <v>659</v>
@@ -23413,7 +23756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="661" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="1">
         <f t="shared" si="11"/>
         <v>660</v>
@@ -23449,7 +23792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="1">
         <f t="shared" si="11"/>
         <v>661</v>
@@ -23481,8 +23824,11 @@
       <c r="L662" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="663" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M662" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="663" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="1">
         <f t="shared" si="11"/>
         <v>662</v>
@@ -23514,8 +23860,11 @@
       <c r="L663" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="664" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M663" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="664" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="1">
         <f t="shared" si="11"/>
         <v>663</v>
@@ -23547,8 +23896,11 @@
       <c r="L664" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="665" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M664" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="665" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="1">
         <f t="shared" si="11"/>
         <v>664</v>
@@ -23581,7 +23933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="666" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="1">
         <f t="shared" si="11"/>
         <v>665</v>
@@ -23614,7 +23966,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="667" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="1">
         <f t="shared" si="11"/>
         <v>666</v>
@@ -23647,7 +23999,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="668" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="1">
         <f t="shared" si="11"/>
         <v>667</v>
@@ -23680,7 +24032,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="669" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="1">
         <f t="shared" si="11"/>
         <v>668</v>
@@ -23719,7 +24071,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="670" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="1">
         <f t="shared" si="11"/>
         <v>669</v>
@@ -23758,7 +24110,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="671" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="1">
         <f t="shared" si="11"/>
         <v>670</v>
@@ -23797,7 +24149,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="672" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="1">
         <f t="shared" si="11"/>
         <v>671</v>
@@ -24380,7 +24732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="689" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="1">
         <f t="shared" si="11"/>
         <v>688</v>
@@ -24413,7 +24765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="690" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="1">
         <f t="shared" si="11"/>
         <v>689</v>
@@ -24446,7 +24798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="691" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="1">
         <f t="shared" si="11"/>
         <v>690</v>
@@ -24479,7 +24831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="692" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="1">
         <f t="shared" si="11"/>
         <v>691</v>
@@ -24512,7 +24864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="693" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="1">
         <f t="shared" si="11"/>
         <v>692</v>
@@ -24545,7 +24897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="694" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="1">
         <f t="shared" si="11"/>
         <v>693</v>
@@ -24578,7 +24930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="1">
         <f t="shared" si="11"/>
         <v>694</v>
@@ -24611,7 +24963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="696" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="1">
         <f t="shared" si="11"/>
         <v>695</v>
@@ -24643,8 +24995,11 @@
       <c r="L696" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="697" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M696" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="697" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="1">
         <f t="shared" si="11"/>
         <v>696</v>
@@ -24676,8 +25031,11 @@
       <c r="L697" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="698" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M697" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="698" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="1">
         <f t="shared" si="11"/>
         <v>697</v>
@@ -24709,8 +25067,11 @@
       <c r="L698" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="699" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M698" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="699" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="1">
         <f t="shared" si="11"/>
         <v>698</v>
@@ -24743,7 +25104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="700" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1">
         <f t="shared" si="11"/>
         <v>699</v>
@@ -24776,7 +25137,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="701" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="1">
         <f t="shared" si="11"/>
         <v>700</v>
@@ -24809,7 +25170,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="702" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="1">
         <f t="shared" si="11"/>
         <v>701</v>
@@ -24842,7 +25203,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="703" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="1">
         <f t="shared" si="11"/>
         <v>702</v>
@@ -24875,7 +25236,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="704" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="1">
         <f t="shared" si="11"/>
         <v>703</v>
@@ -25445,7 +25806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="721" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="1">
         <f t="shared" si="12"/>
         <v>720</v>
@@ -25478,7 +25839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="722" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="1">
         <f t="shared" si="12"/>
         <v>721</v>
@@ -25511,7 +25872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="723" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="1">
         <f t="shared" si="12"/>
         <v>722</v>
@@ -25544,7 +25905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="724" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="1">
         <f t="shared" si="12"/>
         <v>723</v>
@@ -25577,7 +25938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="725" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="1">
         <f t="shared" si="12"/>
         <v>724</v>
@@ -25610,7 +25971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="726" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="1">
         <f t="shared" si="12"/>
         <v>725</v>
@@ -25649,7 +26010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="727" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="1">
         <f t="shared" si="12"/>
         <v>726</v>
@@ -25688,7 +26049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="728" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="1">
         <f t="shared" si="12"/>
         <v>727</v>
@@ -25721,7 +26082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="729" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="1">
         <f t="shared" si="12"/>
         <v>728</v>
@@ -25753,8 +26114,11 @@
       <c r="L729" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="730" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M729" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="730" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="1">
         <f t="shared" si="12"/>
         <v>729</v>
@@ -25789,8 +26153,11 @@
       <c r="L730" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="731" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M730" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="731" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="1">
         <f t="shared" si="12"/>
         <v>730</v>
@@ -25822,8 +26189,11 @@
       <c r="L731" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="732" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M731" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="732" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="1">
         <f t="shared" si="12"/>
         <v>731</v>
@@ -25856,7 +26226,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="733" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="1">
         <f t="shared" si="12"/>
         <v>732</v>
@@ -25889,7 +26259,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="734" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="1">
         <f t="shared" si="12"/>
         <v>733</v>
@@ -25922,7 +26292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="735" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="1">
         <f t="shared" si="12"/>
         <v>734</v>
@@ -25955,7 +26325,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="736" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="1">
         <f t="shared" si="12"/>
         <v>735</v>
@@ -26528,7 +26898,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="753" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="1">
         <f t="shared" si="12"/>
         <v>752</v>
@@ -26561,7 +26931,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="754" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="1">
         <f t="shared" si="12"/>
         <v>753</v>
@@ -26594,7 +26964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="755" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="1">
         <f t="shared" si="12"/>
         <v>754</v>
@@ -26627,7 +26997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="756" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="1">
         <f t="shared" si="12"/>
         <v>755</v>
@@ -26660,7 +27030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="757" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="1">
         <f t="shared" si="12"/>
         <v>756</v>
@@ -26693,7 +27063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="758" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="1">
         <f t="shared" si="12"/>
         <v>757</v>
@@ -26726,7 +27096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="759" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="1">
         <f t="shared" si="12"/>
         <v>758</v>
@@ -26759,7 +27129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="760" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="1">
         <f t="shared" si="12"/>
         <v>759</v>
@@ -26792,7 +27162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="761" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="1">
         <f t="shared" si="12"/>
         <v>760</v>
@@ -26825,7 +27195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="762" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="1">
         <f t="shared" si="12"/>
         <v>761</v>
@@ -26857,8 +27227,11 @@
       <c r="L762" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="763" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M762" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="763" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="1">
         <f t="shared" si="12"/>
         <v>762</v>
@@ -26890,8 +27263,11 @@
       <c r="L763" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="764" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M763" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="764" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="1">
         <f t="shared" si="12"/>
         <v>763</v>
@@ -26923,8 +27299,11 @@
       <c r="L764" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="765" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M764" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="765" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="1">
         <f t="shared" si="12"/>
         <v>764</v>
@@ -26957,7 +27336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="766" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
         <f t="shared" si="12"/>
         <v>765</v>
@@ -26990,7 +27369,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="767" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="1">
         <f t="shared" si="12"/>
         <v>766</v>
@@ -27023,7 +27402,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="768" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="1">
         <f t="shared" si="12"/>
         <v>767</v>
@@ -27590,7 +27969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="785" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
         <f t="shared" si="13"/>
         <v>784</v>
@@ -27623,7 +28002,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="786" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
         <f t="shared" si="13"/>
         <v>785</v>
@@ -27656,7 +28035,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="787" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
         <f t="shared" si="13"/>
         <v>786</v>
@@ -27689,7 +28068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="788" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
         <f t="shared" si="13"/>
         <v>787</v>
@@ -27722,7 +28101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="789" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
         <f t="shared" si="13"/>
         <v>788</v>
@@ -27755,7 +28134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="790" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
         <f t="shared" si="13"/>
         <v>789</v>
@@ -27788,7 +28167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="791" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
         <f t="shared" si="13"/>
         <v>790</v>
@@ -27821,7 +28200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="792" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
         <f t="shared" si="13"/>
         <v>791</v>
@@ -27854,7 +28233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="793" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="1">
         <f t="shared" si="13"/>
         <v>792</v>
@@ -27887,7 +28266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="794" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
         <f t="shared" si="13"/>
         <v>793</v>
@@ -27920,7 +28299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="795" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
         <f t="shared" si="13"/>
         <v>794</v>
@@ -27952,8 +28331,11 @@
       <c r="L795" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="796" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M795" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="796" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="1">
         <f t="shared" si="13"/>
         <v>795</v>
@@ -27985,8 +28367,11 @@
       <c r="L796" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="797" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M796" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="797" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="1">
         <f t="shared" si="13"/>
         <v>796</v>
@@ -28018,8 +28403,11 @@
       <c r="L797" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="798" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M797" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="798" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="1">
         <f t="shared" si="13"/>
         <v>797</v>
@@ -28052,7 +28440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="799" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
         <f t="shared" si="13"/>
         <v>798</v>
@@ -28084,8 +28472,11 @@
       <c r="L799" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="800" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M799" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="800" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="1">
         <f t="shared" si="13"/>
         <v>799</v>
@@ -28117,8 +28508,11 @@
       <c r="L800" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="801" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M800" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="801" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="1">
         <f t="shared" si="13"/>
         <v>800</v>
@@ -28150,8 +28544,11 @@
       <c r="L801" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="802" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M801" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="802" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="1">
         <f t="shared" si="13"/>
         <v>801</v>
@@ -28184,7 +28581,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="803" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="1">
         <f t="shared" si="13"/>
         <v>802</v>
@@ -28217,7 +28614,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="804" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="1">
         <f t="shared" si="13"/>
         <v>803</v>
@@ -28250,7 +28647,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="805" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="1">
         <f t="shared" si="13"/>
         <v>804</v>
@@ -28283,7 +28680,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="806" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="1">
         <f t="shared" si="13"/>
         <v>805</v>
@@ -28316,7 +28713,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="807" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="1">
         <f t="shared" si="13"/>
         <v>806</v>
@@ -28349,7 +28746,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="808" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="1">
         <f t="shared" si="13"/>
         <v>807</v>
@@ -28382,7 +28779,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="809" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="1">
         <f t="shared" si="13"/>
         <v>808</v>
@@ -28415,7 +28812,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="810" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="1">
         <f t="shared" si="13"/>
         <v>809</v>
@@ -28448,7 +28845,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="811" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="1">
         <f t="shared" si="13"/>
         <v>810</v>
@@ -28481,7 +28878,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="812" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="1">
         <f t="shared" si="13"/>
         <v>811</v>
@@ -28514,7 +28911,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="813" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
         <f t="shared" si="13"/>
         <v>812</v>
@@ -28547,7 +28944,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="814" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="1">
         <f t="shared" si="13"/>
         <v>813</v>
@@ -28580,7 +28977,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="815" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="1">
         <f t="shared" si="13"/>
         <v>814</v>
@@ -28613,7 +29010,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="816" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="1">
         <f t="shared" si="13"/>
         <v>815</v>
@@ -28646,7 +29043,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="817" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="1">
         <f t="shared" si="13"/>
         <v>816</v>
@@ -28679,7 +29076,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="818" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
         <f t="shared" si="13"/>
         <v>817</v>
@@ -28712,7 +29109,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="819" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="1">
         <f t="shared" si="13"/>
         <v>818</v>
@@ -28745,7 +29142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="820" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
         <f t="shared" si="13"/>
         <v>819</v>
@@ -28778,7 +29175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="821" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
         <f t="shared" si="13"/>
         <v>820</v>
@@ -28811,7 +29208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="822" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
         <f t="shared" si="13"/>
         <v>821</v>
@@ -28844,7 +29241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="823" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
         <f t="shared" si="13"/>
         <v>822</v>
@@ -28877,7 +29274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="824" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
         <f t="shared" si="13"/>
         <v>823</v>
@@ -28910,7 +29307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="825" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
         <f t="shared" si="13"/>
         <v>824</v>
@@ -28943,7 +29340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="826" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
         <f t="shared" si="13"/>
         <v>825</v>
@@ -28976,7 +29373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="827" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
         <f t="shared" si="13"/>
         <v>826</v>
@@ -29008,8 +29405,11 @@
       <c r="L827" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="828" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M827" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="828" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
         <f t="shared" si="13"/>
         <v>827</v>
@@ -29041,8 +29441,11 @@
       <c r="L828" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="829" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M828" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="829" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="1">
         <f t="shared" si="13"/>
         <v>828</v>
@@ -29074,8 +29477,11 @@
       <c r="L829" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="830" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M829" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="830" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="1">
         <f t="shared" si="13"/>
         <v>829</v>
@@ -29108,7 +29514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="831" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="1">
         <f t="shared" si="13"/>
         <v>830</v>
@@ -29146,8 +29552,11 @@
       <c r="L831" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="832" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M831" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="832" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="1">
         <f t="shared" si="13"/>
         <v>831</v>
@@ -29178,6 +29587,9 @@
       </c>
       <c r="L832" s="1" t="s">
         <v>56</v>
+      </c>
+      <c r="M832" s="22" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="833" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -29212,6 +29624,9 @@
       <c r="L833" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="M833" s="22" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="834" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="1">
@@ -29717,7 +30132,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="849" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="1">
         <f t="shared" si="14"/>
         <v>848</v>
@@ -29750,7 +30165,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="850" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="1">
         <f t="shared" si="14"/>
         <v>849</v>
@@ -29789,7 +30204,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="851" spans="1:12" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="14">
         <f t="shared" si="14"/>
         <v>850</v>
@@ -29828,7 +30243,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="852" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="1">
         <f t="shared" si="14"/>
         <v>851</v>
@@ -29861,7 +30276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="853" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="1">
         <f t="shared" si="14"/>
         <v>852</v>
@@ -29894,7 +30309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="854" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="1">
         <f t="shared" si="14"/>
         <v>853</v>
@@ -29930,7 +30345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="855" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="1">
         <f t="shared" si="14"/>
         <v>854</v>
@@ -29963,7 +30378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="856" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="1">
         <f t="shared" si="14"/>
         <v>855</v>
@@ -29996,7 +30411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="857" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="1">
         <f t="shared" si="14"/>
         <v>856</v>
@@ -30029,7 +30444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="858" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="1">
         <f t="shared" si="14"/>
         <v>857</v>
@@ -30062,7 +30477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="859" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="1">
         <f t="shared" si="14"/>
         <v>858</v>
@@ -30095,7 +30510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="860" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="1">
         <f t="shared" si="14"/>
         <v>859</v>
@@ -30127,8 +30542,11 @@
       <c r="L860" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="861" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M860" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="861" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="1">
         <f t="shared" si="14"/>
         <v>860</v>
@@ -30160,8 +30578,11 @@
       <c r="L861" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="862" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M861" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="862" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="1">
         <f t="shared" si="14"/>
         <v>861</v>
@@ -30193,8 +30614,11 @@
       <c r="L862" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="863" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M862" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="863" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="1">
         <f t="shared" si="14"/>
         <v>862</v>
@@ -30227,7 +30651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="864" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="1">
         <f t="shared" si="14"/>
         <v>863</v>
@@ -30265,8 +30689,11 @@
       <c r="L864" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="865" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M864" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="865" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="1">
         <f t="shared" si="14"/>
         <v>864</v>
@@ -30298,8 +30725,11 @@
       <c r="L865" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="866" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M865" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="866" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="1">
         <f t="shared" si="14"/>
         <v>865</v>
@@ -30331,8 +30761,11 @@
       <c r="L866" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="867" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M866" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="867" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="1">
         <f t="shared" si="14"/>
         <v>866</v>
@@ -30365,7 +30798,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="868" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="1">
         <f t="shared" si="14"/>
         <v>867</v>
@@ -30398,7 +30831,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="869" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="1">
         <f t="shared" si="14"/>
         <v>868</v>
@@ -30431,7 +30864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="870" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="1">
         <f t="shared" si="14"/>
         <v>869</v>
@@ -30470,7 +30903,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="871" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="1">
         <f t="shared" si="14"/>
         <v>870</v>
@@ -30503,7 +30936,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="872" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="1">
         <f t="shared" si="14"/>
         <v>871</v>
@@ -30536,7 +30969,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="873" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="1">
         <f t="shared" si="14"/>
         <v>872</v>
@@ -30569,7 +31002,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="874" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="1">
         <f t="shared" si="14"/>
         <v>873</v>
@@ -30602,7 +31035,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="875" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="1">
         <f t="shared" si="14"/>
         <v>874</v>
@@ -30635,7 +31068,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="876" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="1">
         <f t="shared" si="14"/>
         <v>875</v>
@@ -30668,7 +31101,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="877" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="1">
         <f t="shared" si="14"/>
         <v>876</v>
@@ -30701,7 +31134,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="878" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="1">
         <f t="shared" si="14"/>
         <v>877</v>
@@ -30734,7 +31167,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="879" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="1">
         <f t="shared" si="14"/>
         <v>878</v>
@@ -30767,7 +31200,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="880" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="1">
         <f t="shared" si="14"/>
         <v>879</v>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v10.2_修正版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C264428-EB34-4947-AA1C-DE8A9B6A8A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0495A504-2407-4E58-A26F-663053928D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4822" uniqueCount="128">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1645,6 +1645,9 @@
       <c r="L13" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M13" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2707,6 +2710,9 @@
       <c r="L44" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M44" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="45" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
@@ -3844,6 +3850,9 @@
       <c r="L77" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M77" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="78" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
@@ -5015,6 +5024,9 @@
       <c r="L111" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M111" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="112" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
@@ -6137,6 +6149,9 @@
       <c r="L144" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M144" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="145" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
@@ -7215,7 +7230,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -7247,8 +7262,11 @@
       <c r="L177" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="178" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M177" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -7281,7 +7299,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -7314,7 +7332,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -7347,7 +7365,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -7380,7 +7398,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -7413,7 +7431,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -7446,7 +7464,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -7479,7 +7497,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -7512,7 +7530,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -7545,7 +7563,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -7578,7 +7596,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -7611,7 +7629,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -7644,7 +7662,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -7677,7 +7695,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -7710,7 +7728,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -8351,6 +8369,9 @@
       <c r="L210" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M210" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="211" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
@@ -9425,6 +9446,9 @@
       <c r="L242" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M242" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="243" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
@@ -10562,6 +10586,9 @@
       <c r="L275" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M275" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="276" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
@@ -11689,6 +11716,9 @@
       <c r="L307" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M307" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="308" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
@@ -12751,6 +12781,9 @@
       <c r="L338" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M338" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="339" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
@@ -13888,6 +13921,9 @@
       <c r="L371" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M371" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="372" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
@@ -15059,6 +15095,9 @@
       <c r="L405" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M405" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="406" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
@@ -16181,6 +16220,9 @@
       <c r="L438" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M438" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="439" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
@@ -17291,6 +17333,9 @@
       <c r="L471" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M471" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="472" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
@@ -18395,6 +18440,9 @@
       <c r="L504" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M504" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="505" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
@@ -19469,6 +19517,9 @@
       <c r="L536" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M536" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="537" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
@@ -20606,6 +20657,9 @@
       <c r="L569" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M569" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="570" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
@@ -21733,6 +21787,9 @@
       <c r="L601" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M601" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="602" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
@@ -22795,6 +22852,9 @@
       <c r="L632" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M632" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="633" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1">
@@ -23932,6 +23992,9 @@
       <c r="L665" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M665" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="666" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="1">
@@ -25103,6 +25166,9 @@
       <c r="L699" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M699" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="700" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1">
@@ -26225,6 +26291,9 @@
       <c r="L732" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M732" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="733" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="1">
@@ -27335,6 +27404,9 @@
       <c r="L765" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M765" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="766" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
@@ -28439,6 +28511,9 @@
       <c r="L798" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M798" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="799" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
@@ -29513,6 +29588,9 @@
       <c r="L830" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="M830" s="23" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="831" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="1">
@@ -30649,6 +30727,9 @@
       </c>
       <c r="L863" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="M863" s="23" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="864" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v10.2_修正版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0495A504-2407-4E58-A26F-663053928D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5623F3B2-7B13-4C51-9163-7B467E9EF301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4822" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4921" uniqueCount="137">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -546,6 +546,36 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>232-115L01-04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>232-115L01-06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>232-115L01-05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>156-115J01-05,(補)</t>
+  </si>
+  <si>
+    <t>156-115J01-07,(補)</t>
+  </si>
+  <si>
+    <t>156-115J01-06,(補)</t>
+  </si>
+  <si>
+    <t>156-115J03-04,(配)</t>
+  </si>
+  <si>
+    <t>156-115J03-06,(配)</t>
+  </si>
+  <si>
+    <t>156-115J03-05,(配)</t>
+  </si>
 </sst>
 </file>
 
@@ -554,7 +584,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -665,6 +695,12 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -707,7 +743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -782,6 +818,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1156,7 +1195,7 @@
     <col min="10" max="10" width="17.875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="59.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.5" style="1" customWidth="1"/>
     <col min="15" max="18" width="9" style="1" customWidth="1"/>
     <col min="19" max="19" width="17.75" style="1" customWidth="1"/>
@@ -1243,6 +1282,7 @@
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="M2" s="24"/>
     </row>
     <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -1280,6 +1320,7 @@
       <c r="L3" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="M3" s="24"/>
     </row>
     <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1314,6 +1355,7 @@
       <c r="L4" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="M4" s="24"/>
     </row>
     <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1351,6 +1393,7 @@
       <c r="L5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M5" s="24"/>
     </row>
     <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1388,6 +1431,7 @@
       <c r="L6" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M6" s="24"/>
     </row>
     <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1751,7 +1795,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1784,7 +1828,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1820,7 +1864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1856,7 +1900,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1892,7 +1936,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1928,7 +1972,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1964,7 +2008,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1997,7 +2041,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2030,7 +2074,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2063,7 +2107,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2099,7 +2143,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2132,7 +2176,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2171,7 +2215,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2204,7 +2248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2237,7 +2281,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2272,8 +2316,11 @@
       <c r="L31" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M31" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2338,6 +2385,7 @@
       <c r="L33" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M33" s="24"/>
     </row>
     <row r="34" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
@@ -2371,6 +2419,7 @@
       <c r="L34" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M34" s="24"/>
     </row>
     <row r="35" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -2404,6 +2453,7 @@
       <c r="L35" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M35" s="24"/>
     </row>
     <row r="36" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
@@ -2437,6 +2487,7 @@
       <c r="L36" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M36" s="24"/>
     </row>
     <row r="37" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
@@ -2470,6 +2521,7 @@
       <c r="L37" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M37" s="24"/>
     </row>
     <row r="38" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -2846,7 +2898,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2879,7 +2931,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -2918,7 +2970,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -2951,7 +3003,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -2990,7 +3042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3029,7 +3081,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3062,7 +3114,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3095,7 +3147,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3128,7 +3180,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3167,7 +3219,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3200,7 +3252,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3233,7 +3285,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3266,7 +3318,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3305,7 +3357,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3338,7 +3390,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3371,7 +3423,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3402,6 +3454,9 @@
       </c>
       <c r="L64" s="1" t="s">
         <v>60</v>
+      </c>
+      <c r="M64" s="12" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4586,6 +4641,9 @@
       <c r="L98" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M98" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="99" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -5663,6 +5721,9 @@
       <c r="L130" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M130" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="131" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
@@ -6824,6 +6885,9 @@
       <c r="L164" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M164" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="165" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
@@ -7931,6 +7995,9 @@
       <c r="L197" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M197" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="198" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
@@ -7997,6 +8064,9 @@
       <c r="L199" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M199" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="200" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
@@ -8030,6 +8100,9 @@
       <c r="L200" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M200" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="201" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
@@ -8063,6 +8136,9 @@
       <c r="L201" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M201" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="202" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
@@ -8096,6 +8172,9 @@
       <c r="L202" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M202" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="203" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
@@ -8129,6 +8208,9 @@
       <c r="L203" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M203" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="204" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
@@ -8162,6 +8244,9 @@
       <c r="L204" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M204" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="205" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
@@ -8195,6 +8280,9 @@
       <c r="L205" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M205" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="206" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
@@ -8228,6 +8316,9 @@
       <c r="L206" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M206" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="207" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
@@ -9008,6 +9099,9 @@
       <c r="L229" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M229" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="230" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
@@ -9074,6 +9168,9 @@
       <c r="L231" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M231" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="232" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
@@ -9107,6 +9204,9 @@
       <c r="L232" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M232" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="233" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
@@ -9140,6 +9240,9 @@
       <c r="L233" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M233" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="234" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
@@ -9173,6 +9276,9 @@
       <c r="L234" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M234" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="235" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
@@ -9206,6 +9312,9 @@
       <c r="L235" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M235" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="236" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
@@ -9239,6 +9348,9 @@
       <c r="L236" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M236" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="237" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
@@ -9272,6 +9384,9 @@
       <c r="L237" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M237" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="238" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
@@ -9305,6 +9420,9 @@
       <c r="L238" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M238" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="239" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
@@ -10100,6 +10218,9 @@
       <c r="L261" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M261" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="262" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
@@ -10211,6 +10332,9 @@
       <c r="L264" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M264" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="265" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
@@ -10244,6 +10368,9 @@
       <c r="L265" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M265" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="266" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
@@ -10280,6 +10407,9 @@
       <c r="L266" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M266" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="267" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
@@ -10313,6 +10443,9 @@
       <c r="L267" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M267" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="268" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
@@ -10346,6 +10479,9 @@
       <c r="L268" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M268" s="24" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="269" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
@@ -10379,6 +10515,9 @@
       <c r="L269" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M269" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="270" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
@@ -10412,6 +10551,9 @@
       <c r="L270" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M270" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="271" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
@@ -10445,6 +10587,9 @@
       <c r="L271" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M271" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="272" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
@@ -11243,6 +11388,9 @@
       <c r="L294" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M294" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="295" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="14">
@@ -12343,6 +12491,9 @@
       <c r="L325" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M325" s="12" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="326" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
@@ -13474,6 +13625,9 @@
       <c r="L358" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M358" s="12" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="359" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
@@ -14393,7 +14547,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <f t="shared" si="6"/>
         <v>384</v>
@@ -14426,7 +14580,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <f t="shared" si="6"/>
         <v>385</v>
@@ -14459,7 +14613,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <f t="shared" si="6"/>
         <v>386</v>
@@ -14492,7 +14646,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <f t="shared" si="6"/>
         <v>387</v>
@@ -14526,7 +14680,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="389" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <f t="shared" si="6"/>
         <v>388</v>
@@ -14559,7 +14713,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="390" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <f t="shared" si="6"/>
         <v>389</v>
@@ -14592,7 +14746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <f t="shared" si="6"/>
         <v>390</v>
@@ -14625,7 +14779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <f t="shared" si="6"/>
         <v>391</v>
@@ -14657,8 +14811,11 @@
       <c r="L392" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="393" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M392" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <f t="shared" si="6"/>
         <v>392</v>
@@ -14691,7 +14848,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <f t="shared" si="6"/>
         <v>393</v>
@@ -14724,7 +14881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <f t="shared" si="6"/>
         <v>394</v>
@@ -14757,7 +14914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <f t="shared" si="6"/>
         <v>395</v>
@@ -14790,7 +14947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <f t="shared" si="6"/>
         <v>396</v>
@@ -14823,7 +14980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <f t="shared" si="6"/>
         <v>397</v>
@@ -14856,7 +15013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <f t="shared" si="6"/>
         <v>398</v>
@@ -14889,7 +15046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <f t="shared" si="6"/>
         <v>399</v>
@@ -15471,7 +15628,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -15504,7 +15661,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -15537,7 +15694,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -15570,7 +15727,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -15603,7 +15760,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -15636,7 +15793,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -15669,7 +15826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -15702,7 +15859,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -15734,8 +15891,11 @@
       <c r="L424" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="425" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M424" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <f t="shared" ref="A425:A488" si="7">ROW()-1</f>
         <v>424</v>
@@ -15768,7 +15928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <f t="shared" si="7"/>
         <v>425</v>
@@ -15801,7 +15961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <f t="shared" si="7"/>
         <v>426</v>
@@ -15834,7 +15994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
         <f t="shared" si="7"/>
         <v>427</v>
@@ -15867,7 +16027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <f t="shared" si="7"/>
         <v>428</v>
@@ -15900,7 +16060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <f t="shared" si="7"/>
         <v>429</v>
@@ -15933,7 +16093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <f t="shared" si="7"/>
         <v>430</v>
@@ -15966,7 +16126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
         <f t="shared" si="7"/>
         <v>431</v>
@@ -16560,7 +16720,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <f t="shared" si="7"/>
         <v>448</v>
@@ -16593,7 +16753,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <f t="shared" si="7"/>
         <v>449</v>
@@ -16626,7 +16786,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <f t="shared" si="7"/>
         <v>450</v>
@@ -16665,7 +16825,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <f t="shared" si="7"/>
         <v>451</v>
@@ -16698,7 +16858,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <f t="shared" si="7"/>
         <v>452</v>
@@ -16731,7 +16891,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <f t="shared" si="7"/>
         <v>453</v>
@@ -16764,7 +16924,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <f t="shared" si="7"/>
         <v>454</v>
@@ -16797,7 +16957,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <f t="shared" si="7"/>
         <v>455</v>
@@ -16830,7 +16990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
         <f t="shared" si="7"/>
         <v>456</v>
@@ -16863,7 +17023,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
         <f t="shared" si="7"/>
         <v>457</v>
@@ -16895,8 +17055,11 @@
       <c r="L458" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="459" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M458" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
         <f t="shared" si="7"/>
         <v>458</v>
@@ -16929,7 +17092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
         <f t="shared" si="7"/>
         <v>459</v>
@@ -16962,7 +17125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <f t="shared" si="7"/>
         <v>460</v>
@@ -16995,7 +17158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <f t="shared" si="7"/>
         <v>461</v>
@@ -17028,7 +17191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
         <f t="shared" si="7"/>
         <v>462</v>
@@ -17061,7 +17224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -17634,7 +17797,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <f t="shared" si="7"/>
         <v>480</v>
@@ -17667,7 +17830,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <f t="shared" si="7"/>
         <v>481</v>
@@ -17700,7 +17863,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <f t="shared" si="7"/>
         <v>482</v>
@@ -17733,7 +17896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <f t="shared" si="7"/>
         <v>483</v>
@@ -17766,7 +17929,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <f t="shared" si="7"/>
         <v>484</v>
@@ -17799,7 +17962,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <f t="shared" si="7"/>
         <v>485</v>
@@ -17832,7 +17995,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <f t="shared" si="7"/>
         <v>486</v>
@@ -17865,7 +18028,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <f t="shared" si="7"/>
         <v>487</v>
@@ -17898,7 +18061,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="489" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <f t="shared" ref="A489:A552" si="8">ROW()-1</f>
         <v>488</v>
@@ -17937,7 +18100,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <f t="shared" si="8"/>
         <v>489</v>
@@ -17970,7 +18133,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <f t="shared" si="8"/>
         <v>490</v>
@@ -18002,8 +18165,11 @@
       <c r="L491" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="492" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M491" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="492" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <f t="shared" si="8"/>
         <v>491</v>
@@ -18036,7 +18202,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
         <f t="shared" si="8"/>
         <v>492</v>
@@ -18068,8 +18234,11 @@
       <c r="L493" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="494" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M493" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="494" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <f t="shared" si="8"/>
         <v>493</v>
@@ -18101,8 +18270,11 @@
       <c r="L494" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="495" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M494" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="495" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <f t="shared" si="8"/>
         <v>494</v>
@@ -18134,8 +18306,11 @@
       <c r="L495" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="496" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M495" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="496" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <f t="shared" si="8"/>
         <v>495</v>
@@ -18166,6 +18341,9 @@
       </c>
       <c r="L496" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="M496" s="22" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="497" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18200,6 +18378,9 @@
       <c r="L497" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M497" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="498" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
@@ -18233,6 +18414,9 @@
       <c r="L498" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M498" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="499" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
@@ -18266,6 +18450,9 @@
       <c r="L499" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M499" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="500" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
@@ -18299,6 +18486,9 @@
       <c r="L500" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M500" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="501" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
@@ -18717,7 +18907,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
         <f t="shared" si="8"/>
         <v>512</v>
@@ -18750,7 +18940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="514" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
         <f t="shared" si="8"/>
         <v>513</v>
@@ -18783,7 +18973,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="515" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
         <f t="shared" si="8"/>
         <v>514</v>
@@ -18816,7 +19006,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
         <f t="shared" si="8"/>
         <v>515</v>
@@ -18849,7 +19039,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="517" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <f t="shared" si="8"/>
         <v>516</v>
@@ -18882,7 +19072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="518" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
         <f t="shared" si="8"/>
         <v>517</v>
@@ -18915,7 +19105,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="519" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
         <f t="shared" si="8"/>
         <v>518</v>
@@ -18948,7 +19138,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="520" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
         <f t="shared" si="8"/>
         <v>519</v>
@@ -18981,7 +19171,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
         <f t="shared" si="8"/>
         <v>520</v>
@@ -19014,7 +19204,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="522" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <f t="shared" si="8"/>
         <v>521</v>
@@ -19047,7 +19237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
         <f t="shared" si="8"/>
         <v>522</v>
@@ -19079,8 +19269,11 @@
       <c r="L523" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="524" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M523" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="524" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
         <f t="shared" si="8"/>
         <v>523</v>
@@ -19113,7 +19306,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="525" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
         <f t="shared" si="8"/>
         <v>524</v>
@@ -19145,8 +19338,11 @@
       <c r="L525" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="526" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M525" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="526" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
         <f t="shared" si="8"/>
         <v>525</v>
@@ -19178,8 +19374,11 @@
       <c r="L526" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="527" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M526" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
         <f t="shared" si="8"/>
         <v>526</v>
@@ -19211,8 +19410,11 @@
       <c r="L527" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="528" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M527" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
         <f t="shared" si="8"/>
         <v>527</v>
@@ -19243,6 +19445,9 @@
       </c>
       <c r="L528" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="M528" s="22" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="529" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19277,6 +19482,9 @@
       <c r="L529" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M529" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="530" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
@@ -19310,6 +19518,9 @@
       <c r="L530" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M530" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="531" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
@@ -19343,6 +19554,9 @@
       <c r="L531" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M531" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="532" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
@@ -19376,6 +19590,9 @@
       <c r="L532" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M532" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="533" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
@@ -20171,6 +20388,9 @@
       <c r="L555" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M555" s="12" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="556" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
@@ -20282,6 +20502,9 @@
       <c r="L558" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M558" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="559" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
@@ -20315,6 +20538,9 @@
       <c r="L559" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M559" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="560" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
@@ -20351,6 +20577,9 @@
       <c r="L560" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M560" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="561" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
@@ -20384,6 +20613,9 @@
       <c r="L561" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M561" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="562" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
@@ -20417,6 +20649,9 @@
       <c r="L562" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M562" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="563" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
@@ -20450,6 +20685,9 @@
       <c r="L563" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M563" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="564" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
@@ -20483,6 +20721,9 @@
       <c r="L564" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M564" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="565" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
@@ -20516,6 +20757,9 @@
       <c r="L565" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M565" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="566" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
@@ -21314,6 +21558,9 @@
       <c r="L588" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M588" s="12" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="589" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="14">
@@ -22034,7 +22281,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="609" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1">
         <f t="shared" si="10"/>
         <v>608</v>
@@ -22070,7 +22317,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="610" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1">
         <f t="shared" si="10"/>
         <v>609</v>
@@ -22106,7 +22353,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="611" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1">
         <f t="shared" si="10"/>
         <v>610</v>
@@ -22139,7 +22386,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="612" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1">
         <f t="shared" si="10"/>
         <v>611</v>
@@ -22172,7 +22419,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="613" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1">
         <f t="shared" si="10"/>
         <v>612</v>
@@ -22205,7 +22452,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="614" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1">
         <f t="shared" si="10"/>
         <v>613</v>
@@ -22241,7 +22488,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="615" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1">
         <f t="shared" si="10"/>
         <v>614</v>
@@ -22274,7 +22521,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="616" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1">
         <f t="shared" si="10"/>
         <v>615</v>
@@ -22313,7 +22560,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="617" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1">
         <f t="shared" si="10"/>
         <v>616</v>
@@ -22346,7 +22593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="618" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1">
         <f t="shared" si="10"/>
         <v>617</v>
@@ -22379,7 +22626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="619" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1">
         <f t="shared" si="10"/>
         <v>618</v>
@@ -22414,8 +22661,11 @@
       <c r="L619" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="620" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M619" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1">
         <f t="shared" si="10"/>
         <v>619</v>
@@ -22448,7 +22698,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="621" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1">
         <f t="shared" si="10"/>
         <v>620</v>
@@ -22481,7 +22731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="622" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1">
         <f t="shared" si="10"/>
         <v>621</v>
@@ -22514,7 +22764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="623" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1">
         <f t="shared" si="10"/>
         <v>622</v>
@@ -22547,7 +22797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="624" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1">
         <f t="shared" si="10"/>
         <v>623</v>
@@ -23132,7 +23382,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="641" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="1">
         <f t="shared" si="10"/>
         <v>640</v>
@@ -23171,7 +23421,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="642" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="1">
         <f t="shared" si="10"/>
         <v>641</v>
@@ -23204,7 +23454,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="643" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1">
         <f t="shared" si="10"/>
         <v>642</v>
@@ -23237,7 +23487,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="644" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="1">
         <f t="shared" si="10"/>
         <v>643</v>
@@ -23270,7 +23520,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="645" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="1">
         <f t="shared" si="10"/>
         <v>644</v>
@@ -23309,7 +23559,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="646" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="1">
         <f t="shared" si="10"/>
         <v>645</v>
@@ -23342,7 +23592,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="647" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="1">
         <f t="shared" si="10"/>
         <v>646</v>
@@ -23375,7 +23625,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="648" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1">
         <f t="shared" si="10"/>
         <v>647</v>
@@ -23408,7 +23658,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="649" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="1">
         <f t="shared" si="10"/>
         <v>648</v>
@@ -23447,7 +23697,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="650" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="1">
         <f t="shared" si="10"/>
         <v>649</v>
@@ -23480,7 +23730,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="651" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="1">
         <f t="shared" si="10"/>
         <v>650</v>
@@ -23513,7 +23763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="652" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="1">
         <f t="shared" si="10"/>
         <v>651</v>
@@ -23545,8 +23795,11 @@
       <c r="L652" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="653" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M652" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="1">
         <f t="shared" si="10"/>
         <v>652</v>
@@ -23579,7 +23832,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="654" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="1">
         <f t="shared" si="10"/>
         <v>653</v>
@@ -23612,7 +23865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="655" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="1">
         <f t="shared" ref="A655:A718" si="11">ROW()-1</f>
         <v>654</v>
@@ -23645,7 +23898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="656" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="1">
         <f t="shared" si="11"/>
         <v>655</v>
@@ -24245,7 +24498,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="673" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="1">
         <f t="shared" si="11"/>
         <v>672</v>
@@ -24284,7 +24537,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="674" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="1">
         <f t="shared" si="11"/>
         <v>673</v>
@@ -24317,7 +24570,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="675" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="1">
         <f t="shared" si="11"/>
         <v>674</v>
@@ -24356,7 +24609,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="676" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="1">
         <f t="shared" si="11"/>
         <v>675</v>
@@ -24395,7 +24648,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="677" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="1">
         <f t="shared" si="11"/>
         <v>676</v>
@@ -24428,7 +24681,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="678" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
         <f t="shared" si="11"/>
         <v>677</v>
@@ -24464,7 +24717,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="679" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="1">
         <f t="shared" si="11"/>
         <v>678</v>
@@ -24497,7 +24750,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="680" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="1">
         <f t="shared" si="11"/>
         <v>679</v>
@@ -24530,7 +24783,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="681" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="1">
         <f t="shared" si="11"/>
         <v>680</v>
@@ -24563,7 +24816,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="682" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="1">
         <f t="shared" si="11"/>
         <v>681</v>
@@ -24597,7 +24850,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="683" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
         <f t="shared" si="11"/>
         <v>682</v>
@@ -24630,7 +24883,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="684" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="1">
         <f t="shared" si="11"/>
         <v>683</v>
@@ -24663,7 +24916,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="1">
         <f t="shared" si="11"/>
         <v>684</v>
@@ -24696,7 +24949,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="1">
         <f t="shared" si="11"/>
         <v>685</v>
@@ -24728,8 +24981,11 @@
       <c r="L686" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="687" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M686" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="687" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="1">
         <f t="shared" si="11"/>
         <v>686</v>
@@ -24762,7 +25018,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="688" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="1">
         <f t="shared" si="11"/>
         <v>687</v>
@@ -25335,7 +25591,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="705" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="1">
         <f t="shared" si="11"/>
         <v>704</v>
@@ -25374,7 +25630,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="706" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="1">
         <f t="shared" si="11"/>
         <v>705</v>
@@ -25407,7 +25663,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="707" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="1">
         <f t="shared" si="11"/>
         <v>706</v>
@@ -25440,7 +25696,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="708" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="1">
         <f t="shared" si="11"/>
         <v>707</v>
@@ -25473,7 +25729,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="709" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="1">
         <f t="shared" si="11"/>
         <v>708</v>
@@ -25506,7 +25762,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="710" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="1">
         <f t="shared" si="11"/>
         <v>709</v>
@@ -25542,7 +25798,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="711" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="1">
         <f t="shared" si="11"/>
         <v>710</v>
@@ -25575,7 +25831,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="712" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="1">
         <f t="shared" si="11"/>
         <v>711</v>
@@ -25608,7 +25864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="713" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="1">
         <f t="shared" si="11"/>
         <v>712</v>
@@ -25641,7 +25897,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="714" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="1">
         <f t="shared" si="11"/>
         <v>713</v>
@@ -25674,7 +25930,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="715" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="1">
         <f t="shared" si="11"/>
         <v>714</v>
@@ -25707,7 +25963,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="716" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="1">
         <f t="shared" si="11"/>
         <v>715</v>
@@ -25740,7 +25996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="1">
         <f t="shared" si="11"/>
         <v>716</v>
@@ -25773,7 +26029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="718" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="1">
         <f t="shared" si="11"/>
         <v>717</v>
@@ -25805,8 +26061,11 @@
       <c r="L718" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="719" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M718" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="719" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="1">
         <f t="shared" ref="A719:A782" si="12">ROW()-1</f>
         <v>718</v>
@@ -25839,7 +26098,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="720" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="1">
         <f t="shared" si="12"/>
         <v>719</v>
@@ -26427,7 +26686,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="737" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="1">
         <f t="shared" si="12"/>
         <v>736</v>
@@ -26460,7 +26719,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="738" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="1">
         <f t="shared" si="12"/>
         <v>737</v>
@@ -26499,7 +26758,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="739" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="1">
         <f t="shared" si="12"/>
         <v>738</v>
@@ -26532,7 +26791,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="740" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="1">
         <f t="shared" si="12"/>
         <v>739</v>
@@ -26565,7 +26824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="741" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="1">
         <f t="shared" si="12"/>
         <v>740</v>
@@ -26598,7 +26857,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="742" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="1">
         <f t="shared" si="12"/>
         <v>741</v>
@@ -26631,7 +26890,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="743" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="1">
         <f t="shared" si="12"/>
         <v>742</v>
@@ -26664,7 +26923,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="744" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="1">
         <f t="shared" si="12"/>
         <v>743</v>
@@ -26697,7 +26956,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="745" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="1">
         <f t="shared" si="12"/>
         <v>744</v>
@@ -26736,7 +26995,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="746" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="1">
         <f t="shared" si="12"/>
         <v>745</v>
@@ -26769,7 +27028,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="747" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="1">
         <f t="shared" si="12"/>
         <v>746</v>
@@ -26802,7 +27061,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="748" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="1">
         <f t="shared" si="12"/>
         <v>747</v>
@@ -26835,7 +27094,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="749" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="1">
         <f t="shared" si="12"/>
         <v>748</v>
@@ -26868,7 +27127,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="750" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="1">
         <f t="shared" si="12"/>
         <v>749</v>
@@ -26901,7 +27160,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="1">
         <f t="shared" si="12"/>
         <v>750</v>
@@ -26934,7 +27193,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="1">
         <f t="shared" si="12"/>
         <v>751</v>
@@ -26965,6 +27224,9 @@
       </c>
       <c r="L752" s="1" t="s">
         <v>60</v>
+      </c>
+      <c r="M752" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="753" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -28073,6 +28335,9 @@
       <c r="L785" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M785" s="12" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="786" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
@@ -28139,6 +28404,9 @@
       <c r="L787" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M787" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="788" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
@@ -28172,6 +28440,9 @@
       <c r="L788" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M788" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="789" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
@@ -28205,6 +28476,9 @@
       <c r="L789" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M789" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="790" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
@@ -28238,6 +28512,9 @@
       <c r="L790" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M790" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="791" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
@@ -28271,6 +28548,9 @@
       <c r="L791" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M791" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="792" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
@@ -28304,6 +28584,9 @@
       <c r="L792" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M792" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="793" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="1">
@@ -28337,6 +28620,9 @@
       <c r="L793" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M793" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="794" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
@@ -28370,6 +28656,9 @@
       <c r="L794" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M794" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="795" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
@@ -29150,6 +29439,9 @@
       <c r="L817" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M817" s="12" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="818" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
@@ -29216,6 +29508,9 @@
       <c r="L819" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M819" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="820" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
@@ -29249,6 +29544,9 @@
       <c r="L820" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M820" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="821" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
@@ -29282,6 +29580,9 @@
       <c r="L821" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M821" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="822" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
@@ -29315,6 +29616,9 @@
       <c r="L822" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M822" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="823" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
@@ -29348,6 +29652,9 @@
       <c r="L823" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M823" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="824" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
@@ -29381,6 +29688,9 @@
       <c r="L824" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M824" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="825" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
@@ -29414,6 +29724,9 @@
       <c r="L825" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M825" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="826" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
@@ -29447,6 +29760,9 @@
       <c r="L826" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M826" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="827" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
@@ -30242,6 +30558,9 @@
       <c r="L849" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="M849" s="12" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="850" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="1">
@@ -30353,6 +30672,9 @@
       <c r="L852" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M852" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="853" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="1">
@@ -30386,6 +30708,9 @@
       <c r="L853" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M853" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="854" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="1">
@@ -30422,6 +30747,9 @@
       <c r="L854" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M854" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="855" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="1">
@@ -30455,6 +30783,9 @@
       <c r="L855" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M855" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="856" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="1">
@@ -30488,6 +30819,9 @@
       <c r="L856" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M856" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="857" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="1">
@@ -30521,6 +30855,9 @@
       <c r="L857" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M857" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="858" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="1">
@@ -30554,6 +30891,9 @@
       <c r="L858" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M858" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="859" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="1">
@@ -30587,6 +30927,9 @@
       <c r="L859" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M859" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="860" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="1">
@@ -31384,6 +31727,9 @@
       </c>
       <c r="L882" s="1" t="s">
         <v>60</v>
+      </c>
+      <c r="M882" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="883" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v10.2_修正版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B92419-A91E-4A26-B821-57091DBCEE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66496E05-7203-4CCA-BE93-F696FE230927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11111,7 +11111,7 @@
         <v>58</v>
       </c>
       <c r="M275" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="276" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -21386,7 +21386,7 @@
         <v>58</v>
       </c>
       <c r="M562" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="563" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -31661,7 +31661,7 @@
         <v>58</v>
       </c>
       <c r="M849" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="850" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v10.2_修正版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66496E05-7203-4CCA-BE93-F696FE230927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE8A1B7-A76C-49B5-BB3D-026CBBCECA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="資料頁" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$M$862</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料頁!$A$1:$N$862</definedName>
     <definedName name="全健康保險費" localSheetId="0">資料頁!#REF!</definedName>
     <definedName name="序號" localSheetId="0">資料頁!$A$2:$A$10</definedName>
     <definedName name="投保薪額">資料頁!$F$2:$F$10</definedName>
@@ -30,7 +30,7 @@
     <definedName name="業務承辦人" localSheetId="0">資料頁!$J$2:$J$10</definedName>
     <definedName name="資料" localSheetId="0">資料頁!$A$1:$J$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5152" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5342" uniqueCount="152">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -626,6 +626,14 @@
   </si>
   <si>
     <t>151-115Z01-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已核對繳款單</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1232,7 +1240,7 @@
   <sheetPr codeName="工作表2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M862"/>
+  <dimension ref="A1:N862"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1" bestFit="1" customWidth="1"/>
@@ -1257,7 +1265,7 @@
     <col min="54" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="11" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="11" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
@@ -1297,8 +1305,11 @@
       <c r="M1" s="10" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>ROW()-1</f>
         <v>1</v>
@@ -1336,7 +1347,7 @@
       </c>
       <c r="M2" s="24"/>
     </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f t="shared" ref="A3:A66" si="0">ROW()-1</f>
         <v>2</v>
@@ -1374,7 +1385,7 @@
       </c>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1409,7 +1420,7 @@
       </c>
       <c r="M4" s="24"/>
     </row>
-    <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1447,7 +1458,7 @@
       </c>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1485,7 +1496,7 @@
       </c>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1522,7 +1533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1557,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1591,7 +1602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1631,7 +1642,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1670,7 +1681,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1709,7 +1720,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1745,7 +1756,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1778,7 +1789,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1814,7 +1825,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -8102,7 +8113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <f t="shared" si="3"/>
         <v>192</v>
@@ -8138,7 +8149,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <f t="shared" si="3"/>
         <v>193</v>
@@ -8171,7 +8182,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <f t="shared" si="3"/>
         <v>194</v>
@@ -8206,8 +8217,11 @@
       <c r="M195" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="196" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N195" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <f t="shared" si="3"/>
         <v>195</v>
@@ -8242,8 +8256,11 @@
       <c r="M196" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="197" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N196" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <f t="shared" si="3"/>
         <v>196</v>
@@ -8278,8 +8295,11 @@
       <c r="M197" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="198" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N197" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <f t="shared" si="3"/>
         <v>197</v>
@@ -8314,8 +8334,11 @@
       <c r="M198" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="199" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N198" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <f t="shared" si="3"/>
         <v>198</v>
@@ -8350,8 +8373,11 @@
       <c r="M199" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="200" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N199" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -8386,8 +8412,11 @@
       <c r="M200" s="22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="201" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N200" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -8422,8 +8451,11 @@
       <c r="M201" s="22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="202" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N201" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -8458,8 +8490,11 @@
       <c r="M202" s="22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="203" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N202" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -8494,8 +8529,11 @@
       <c r="M203" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="204" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N203" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -8530,8 +8568,11 @@
       <c r="M204" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="205" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N204" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -8566,8 +8607,11 @@
       <c r="M205" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="206" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N205" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -8602,8 +8646,11 @@
       <c r="M206" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="207" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N206" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -8638,8 +8685,11 @@
       <c r="M207" s="22" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="208" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N207" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -8674,8 +8724,11 @@
       <c r="M208" s="22" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="209" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N208" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -8710,8 +8763,11 @@
       <c r="M209" s="22" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="210" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N209" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -8746,8 +8802,11 @@
       <c r="M210" s="20" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="211" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N210" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -8782,8 +8841,11 @@
       <c r="M211" s="12" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="212" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N211" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -8818,8 +8880,11 @@
       <c r="M212" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="213" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N212" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -8854,8 +8919,11 @@
       <c r="M213" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="214" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N213" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -8890,8 +8958,11 @@
       <c r="M214" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="215" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N214" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -8926,8 +8997,11 @@
       <c r="M215" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="216" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N215" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -8962,8 +9036,11 @@
       <c r="M216" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="217" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N216" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -8998,8 +9075,11 @@
       <c r="M217" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="218" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N217" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -9034,8 +9114,11 @@
       <c r="M218" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="219" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N218" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -9070,8 +9153,11 @@
       <c r="M219" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="220" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N219" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -9106,8 +9192,11 @@
       <c r="M220" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="221" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N220" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -9142,8 +9231,11 @@
       <c r="M221" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="222" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N221" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -9178,8 +9270,11 @@
       <c r="M222" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="223" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N222" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -9211,8 +9306,11 @@
       <c r="L223" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="224" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N223" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -9247,8 +9345,11 @@
       <c r="M224" s="12" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="225" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N224" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -9280,8 +9381,11 @@
       <c r="L225" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="226" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N225" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -9316,8 +9420,11 @@
       <c r="M226" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="227" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N226" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -9352,8 +9459,11 @@
       <c r="M227" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="228" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N227" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -9388,8 +9498,11 @@
       <c r="M228" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="229" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N228" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -9424,8 +9537,11 @@
       <c r="M229" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="230" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N229" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -9460,8 +9576,11 @@
       <c r="M230" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="231" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N230" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -9496,8 +9615,11 @@
       <c r="M231" s="22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="232" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N231" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -9532,8 +9654,11 @@
       <c r="M232" s="22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="233" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N232" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -9568,8 +9693,11 @@
       <c r="M233" s="22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="234" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N233" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -9604,8 +9732,11 @@
       <c r="M234" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="235" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N234" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -9640,8 +9771,11 @@
       <c r="M235" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="236" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N235" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -9676,8 +9810,11 @@
       <c r="M236" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="237" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N236" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -9712,8 +9849,11 @@
       <c r="M237" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="238" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N237" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -9754,8 +9894,11 @@
       <c r="M238" s="22" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="239" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N238" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -9790,8 +9933,11 @@
       <c r="M239" s="22" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="240" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N239" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -9826,8 +9972,11 @@
       <c r="M240" s="22" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="241" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N240" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -9862,8 +10011,11 @@
       <c r="M241" s="20" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="242" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N241" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -9898,8 +10050,11 @@
       <c r="M242" s="12" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="243" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N242" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -9934,8 +10089,11 @@
       <c r="M243" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="244" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N243" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -9970,8 +10128,11 @@
       <c r="M244" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="245" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N244" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -10006,8 +10167,11 @@
       <c r="M245" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="246" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N245" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -10042,8 +10206,11 @@
       <c r="M246" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="247" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N246" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -10084,8 +10251,11 @@
       <c r="M247" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="248" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N247" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -10120,8 +10290,11 @@
       <c r="M248" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="249" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N248" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -10156,8 +10329,11 @@
       <c r="M249" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="250" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N249" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -10192,8 +10368,11 @@
       <c r="M250" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="251" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N250" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -10228,8 +10407,11 @@
       <c r="M251" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="252" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N251" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -10264,8 +10446,11 @@
       <c r="M252" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="253" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N252" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <f t="shared" ref="A253:A288" si="4">ROW()-1</f>
         <v>252</v>
@@ -10300,8 +10485,11 @@
       <c r="M253" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="254" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N253" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <f t="shared" si="4"/>
         <v>253</v>
@@ -10336,8 +10524,11 @@
       <c r="M254" s="20" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="255" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N254" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <f t="shared" si="4"/>
         <v>254</v>
@@ -10372,8 +10563,11 @@
       <c r="M255" s="12" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="256" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N255" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <f t="shared" si="4"/>
         <v>255</v>
@@ -10411,8 +10605,11 @@
       <c r="L256" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="257" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N256" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="14">
         <f t="shared" si="4"/>
         <v>256</v>
@@ -10450,8 +10647,11 @@
       <c r="L257" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="258" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N257" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <f t="shared" si="4"/>
         <v>257</v>
@@ -10487,7 +10687,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="259" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <f t="shared" si="4"/>
         <v>258</v>
@@ -10523,7 +10723,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="260" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <f t="shared" si="4"/>
         <v>259</v>
@@ -10562,7 +10762,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <f t="shared" si="4"/>
         <v>260</v>
@@ -10598,7 +10798,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <f t="shared" si="4"/>
         <v>261</v>
@@ -10634,7 +10834,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="263" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <f t="shared" si="4"/>
         <v>262</v>
@@ -10670,7 +10870,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="264" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -10706,7 +10906,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="265" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -10742,7 +10942,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="266" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -10778,7 +10978,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="267" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -10814,7 +11014,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="268" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -10850,7 +11050,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="269" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -10886,7 +11086,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="270" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -10928,7 +11128,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -10964,7 +11164,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -18413,7 +18613,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="481" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <f t="shared" si="8"/>
         <v>480</v>
@@ -18446,7 +18646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="482" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <f t="shared" si="8"/>
         <v>481</v>
@@ -18481,8 +18681,11 @@
       <c r="M482" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="483" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N482" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <f t="shared" si="8"/>
         <v>482</v>
@@ -18517,8 +18720,11 @@
       <c r="M483" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="484" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N483" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="484" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <f t="shared" si="8"/>
         <v>483</v>
@@ -18553,8 +18759,11 @@
       <c r="M484" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="485" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N484" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="485" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <f t="shared" si="8"/>
         <v>484</v>
@@ -18589,8 +18798,11 @@
       <c r="M485" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="486" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N485" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <f t="shared" si="8"/>
         <v>485</v>
@@ -18625,8 +18837,11 @@
       <c r="M486" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="487" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N486" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <f t="shared" si="8"/>
         <v>486</v>
@@ -18661,8 +18876,11 @@
       <c r="M487" s="22" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="488" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N487" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <f t="shared" si="8"/>
         <v>487</v>
@@ -18697,8 +18915,11 @@
       <c r="M488" s="22" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="489" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N488" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <f t="shared" si="8"/>
         <v>488</v>
@@ -18733,8 +18954,11 @@
       <c r="M489" s="22" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="490" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N489" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <f t="shared" si="8"/>
         <v>489</v>
@@ -18769,8 +18993,11 @@
       <c r="M490" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="491" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N490" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <f t="shared" si="8"/>
         <v>490</v>
@@ -18805,8 +19032,11 @@
       <c r="M491" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="492" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N491" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <f t="shared" si="8"/>
         <v>491</v>
@@ -18841,8 +19071,11 @@
       <c r="M492" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="493" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N492" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
         <f t="shared" si="8"/>
         <v>492</v>
@@ -18877,8 +19110,11 @@
       <c r="M493" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="494" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N493" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <f t="shared" si="8"/>
         <v>493</v>
@@ -18913,8 +19149,11 @@
       <c r="M494" s="22" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="495" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N494" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <f t="shared" si="8"/>
         <v>494</v>
@@ -18949,8 +19188,11 @@
       <c r="M495" s="22" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="496" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N495" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <f t="shared" si="8"/>
         <v>495</v>
@@ -18985,8 +19227,11 @@
       <c r="M496" s="22" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="497" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N496" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <f t="shared" si="8"/>
         <v>496</v>
@@ -19021,8 +19266,11 @@
       <c r="M497" s="20" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="498" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N497" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
         <f t="shared" si="8"/>
         <v>497</v>
@@ -19057,8 +19305,11 @@
       <c r="M498" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="499" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N498" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <f t="shared" si="8"/>
         <v>498</v>
@@ -19093,8 +19344,11 @@
       <c r="M499" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="500" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N499" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
         <f t="shared" si="8"/>
         <v>499</v>
@@ -19129,8 +19383,11 @@
       <c r="M500" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="501" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N500" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
@@ -19165,8 +19422,11 @@
       <c r="M501" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="502" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N501" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <f t="shared" si="8"/>
         <v>501</v>
@@ -19201,8 +19461,11 @@
       <c r="M502" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="503" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N502" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
         <f t="shared" si="8"/>
         <v>502</v>
@@ -19237,8 +19500,11 @@
       <c r="M503" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="504" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N503" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="504" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
         <f t="shared" si="8"/>
         <v>503</v>
@@ -19273,8 +19539,11 @@
       <c r="M504" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="505" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N504" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="505" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <f t="shared" si="8"/>
         <v>504</v>
@@ -19309,8 +19578,11 @@
       <c r="M505" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="506" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N505" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="506" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
         <f t="shared" si="8"/>
         <v>505</v>
@@ -19345,8 +19617,11 @@
       <c r="M506" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="507" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N506" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="507" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
         <f t="shared" si="8"/>
         <v>506</v>
@@ -19381,8 +19656,11 @@
       <c r="M507" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="508" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N507" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="508" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
         <f t="shared" si="8"/>
         <v>507</v>
@@ -19417,8 +19695,11 @@
       <c r="M508" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="509" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N508" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="509" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
         <f t="shared" si="8"/>
         <v>508</v>
@@ -19453,8 +19734,11 @@
       <c r="M509" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="510" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N509" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="510" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
         <f t="shared" si="8"/>
         <v>509</v>
@@ -19486,8 +19770,11 @@
       <c r="L510" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="511" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N510" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="511" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
         <f t="shared" si="8"/>
         <v>510</v>
@@ -19522,8 +19809,11 @@
       <c r="M511" s="12" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="512" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N511" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="512" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <f t="shared" si="8"/>
         <v>511</v>
@@ -19555,8 +19845,11 @@
       <c r="L512" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="513" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N512" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="513" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
         <f t="shared" si="8"/>
         <v>512</v>
@@ -19591,8 +19884,11 @@
       <c r="M513" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="514" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N513" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="514" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
         <f t="shared" si="8"/>
         <v>513</v>
@@ -19627,8 +19923,11 @@
       <c r="M514" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="515" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N514" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="515" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
         <f t="shared" si="8"/>
         <v>514</v>
@@ -19663,8 +19962,11 @@
       <c r="M515" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="516" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N515" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="516" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
         <f t="shared" si="8"/>
         <v>515</v>
@@ -19699,8 +20001,11 @@
       <c r="M516" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="517" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N516" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="517" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <f t="shared" si="8"/>
         <v>516</v>
@@ -19735,8 +20040,11 @@
       <c r="M517" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="518" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N517" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="518" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
         <f t="shared" si="8"/>
         <v>517</v>
@@ -19771,8 +20079,11 @@
       <c r="M518" s="22" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="519" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N518" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="519" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
         <f t="shared" si="8"/>
         <v>518</v>
@@ -19807,8 +20118,11 @@
       <c r="M519" s="22" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="520" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N519" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="520" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
         <f t="shared" si="8"/>
         <v>519</v>
@@ -19843,8 +20157,11 @@
       <c r="M520" s="22" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="521" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N520" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="521" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
         <f t="shared" si="8"/>
         <v>520</v>
@@ -19879,8 +20196,11 @@
       <c r="M521" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="522" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N521" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="522" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <f t="shared" si="8"/>
         <v>521</v>
@@ -19915,8 +20235,11 @@
       <c r="M522" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="523" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N522" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="523" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
         <f t="shared" si="8"/>
         <v>522</v>
@@ -19951,8 +20274,11 @@
       <c r="M523" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="524" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N523" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="524" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
         <f t="shared" si="8"/>
         <v>523</v>
@@ -19987,8 +20313,11 @@
       <c r="M524" s="23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="525" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N524" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="525" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
         <f t="shared" si="8"/>
         <v>524</v>
@@ -20029,8 +20358,11 @@
       <c r="M525" s="22" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="526" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N525" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="526" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
         <f t="shared" si="8"/>
         <v>525</v>
@@ -20065,8 +20397,11 @@
       <c r="M526" s="22" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="527" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N526" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="527" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
         <f t="shared" si="8"/>
         <v>526</v>
@@ -20101,8 +20436,11 @@
       <c r="M527" s="22" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="528" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N527" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="528" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
         <f t="shared" si="8"/>
         <v>527</v>
@@ -20137,8 +20475,11 @@
       <c r="M528" s="20" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="529" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N528" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="529" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
         <f t="shared" si="8"/>
         <v>528</v>
@@ -20173,8 +20514,11 @@
       <c r="M529" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="530" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N529" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="530" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
         <f t="shared" si="8"/>
         <v>529</v>
@@ -20209,8 +20553,11 @@
       <c r="M530" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="531" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N530" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="531" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
         <f t="shared" si="8"/>
         <v>530</v>
@@ -20245,8 +20592,11 @@
       <c r="M531" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="532" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N531" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="532" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <f t="shared" si="8"/>
         <v>531</v>
@@ -20281,8 +20631,11 @@
       <c r="M532" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="533" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N532" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="533" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
         <f t="shared" si="8"/>
         <v>532</v>
@@ -20317,8 +20670,11 @@
       <c r="M533" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="534" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N533" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="534" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
         <f t="shared" si="8"/>
         <v>533</v>
@@ -20359,8 +20715,11 @@
       <c r="M534" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="535" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N534" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="535" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
         <f t="shared" si="8"/>
         <v>534</v>
@@ -20395,8 +20754,11 @@
       <c r="M535" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="536" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N535" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="536" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
         <f t="shared" si="8"/>
         <v>535</v>
@@ -20431,8 +20793,11 @@
       <c r="M536" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="537" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N536" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="537" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -20467,8 +20832,11 @@
       <c r="M537" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="538" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N537" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="538" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <f t="shared" si="8"/>
         <v>537</v>
@@ -20503,8 +20871,11 @@
       <c r="M538" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="539" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N538" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="539" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
         <f t="shared" si="8"/>
         <v>538</v>
@@ -20539,8 +20910,11 @@
       <c r="M539" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="540" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N539" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="540" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
         <f t="shared" ref="A540:A575" si="9">ROW()-1</f>
         <v>539</v>
@@ -20575,8 +20949,11 @@
       <c r="M540" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="541" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N540" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="541" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
         <f t="shared" si="9"/>
         <v>540</v>
@@ -20611,8 +20988,11 @@
       <c r="M541" s="20" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="542" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N541" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="542" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
         <f t="shared" si="9"/>
         <v>541</v>
@@ -20647,8 +21027,11 @@
       <c r="M542" s="12" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="543" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N542" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="543" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
         <f t="shared" si="9"/>
         <v>542</v>
@@ -20686,8 +21069,11 @@
       <c r="L543" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="544" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N543" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="544" spans="1:14" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="14">
         <f t="shared" si="9"/>
         <v>543</v>
@@ -20724,6 +21110,9 @@
       </c>
       <c r="L544" s="1" t="s">
         <v>111</v>
+      </c>
+      <c r="N544" s="20" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="545" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -28721,7 +29110,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="769" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
         <f t="shared" si="13"/>
         <v>768</v>
@@ -28756,8 +29145,11 @@
       <c r="M769" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="770" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N769" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="770" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
         <f t="shared" si="13"/>
         <v>769</v>
@@ -28792,8 +29184,11 @@
       <c r="M770" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="771" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N770" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="771" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="1">
         <f t="shared" si="13"/>
         <v>770</v>
@@ -28828,8 +29223,11 @@
       <c r="M771" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="772" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N771" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="772" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
         <f t="shared" si="13"/>
         <v>771</v>
@@ -28864,8 +29262,11 @@
       <c r="M772" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="773" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N772" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="773" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
         <f t="shared" si="13"/>
         <v>772</v>
@@ -28900,8 +29301,11 @@
       <c r="M773" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="774" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N773" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="774" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
         <f t="shared" si="13"/>
         <v>773</v>
@@ -28936,8 +29340,11 @@
       <c r="M774" s="22" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="775" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N774" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="775" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="1">
         <f t="shared" si="13"/>
         <v>774</v>
@@ -28972,8 +29379,11 @@
       <c r="M775" s="22" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="776" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N775" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="776" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="1">
         <f t="shared" si="13"/>
         <v>775</v>
@@ -29008,8 +29418,11 @@
       <c r="M776" s="22" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="777" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N776" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="777" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
         <f t="shared" si="13"/>
         <v>776</v>
@@ -29044,8 +29457,11 @@
       <c r="M777" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="778" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N777" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="778" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
         <f t="shared" si="13"/>
         <v>777</v>
@@ -29080,8 +29496,11 @@
       <c r="M778" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="779" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N778" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="779" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
         <f t="shared" si="13"/>
         <v>778</v>
@@ -29116,8 +29535,11 @@
       <c r="M779" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="780" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N779" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="780" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="1">
         <f t="shared" si="13"/>
         <v>779</v>
@@ -29152,8 +29574,11 @@
       <c r="M780" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="781" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N780" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="781" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
         <f t="shared" si="13"/>
         <v>780</v>
@@ -29188,8 +29613,11 @@
       <c r="M781" s="22" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="782" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N781" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="782" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="1">
         <f t="shared" si="13"/>
         <v>781</v>
@@ -29224,8 +29652,11 @@
       <c r="M782" s="22" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="783" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N782" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="783" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
         <f t="shared" si="13"/>
         <v>782</v>
@@ -29260,8 +29691,11 @@
       <c r="M783" s="22" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="784" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N783" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="784" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
         <f t="shared" si="13"/>
         <v>783</v>
@@ -29296,8 +29730,11 @@
       <c r="M784" s="20" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="785" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N784" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="785" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
         <f t="shared" si="13"/>
         <v>784</v>
@@ -29332,8 +29769,11 @@
       <c r="M785" s="12" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="786" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N785" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="786" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
         <f t="shared" si="13"/>
         <v>785</v>
@@ -29368,8 +29808,11 @@
       <c r="M786" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="787" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N786" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="787" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
         <f t="shared" si="13"/>
         <v>786</v>
@@ -29404,8 +29847,11 @@
       <c r="M787" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="788" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N787" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="788" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
         <f t="shared" si="13"/>
         <v>787</v>
@@ -29440,8 +29886,11 @@
       <c r="M788" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="789" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N788" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="789" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
         <f t="shared" si="13"/>
         <v>788</v>
@@ -29476,8 +29925,11 @@
       <c r="M789" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="790" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N789" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="790" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
         <f t="shared" si="13"/>
         <v>789</v>
@@ -29512,8 +29964,11 @@
       <c r="M790" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="791" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N790" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="791" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
         <f t="shared" si="13"/>
         <v>790</v>
@@ -29548,8 +30003,11 @@
       <c r="M791" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="792" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N791" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="792" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
         <f t="shared" si="13"/>
         <v>791</v>
@@ -29584,8 +30042,11 @@
       <c r="M792" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="793" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N792" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="793" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="1">
         <f t="shared" si="13"/>
         <v>792</v>
@@ -29620,8 +30081,11 @@
       <c r="M793" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="794" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N793" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="794" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
         <f t="shared" si="13"/>
         <v>793</v>
@@ -29656,8 +30120,11 @@
       <c r="M794" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="795" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N794" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="795" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
         <f t="shared" si="13"/>
         <v>794</v>
@@ -29692,8 +30159,11 @@
       <c r="M795" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="796" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N795" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="796" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="1">
         <f t="shared" si="13"/>
         <v>795</v>
@@ -29728,8 +30198,11 @@
       <c r="M796" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="797" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N796" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="797" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="1">
         <f t="shared" si="13"/>
         <v>796</v>
@@ -29761,8 +30234,11 @@
       <c r="L797" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="798" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N797" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="798" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="1">
         <f t="shared" si="13"/>
         <v>797</v>
@@ -29797,8 +30273,11 @@
       <c r="M798" s="12" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="799" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N798" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="799" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
         <f t="shared" si="13"/>
         <v>798</v>
@@ -29830,8 +30309,11 @@
       <c r="L799" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="800" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N799" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="800" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="1">
         <f t="shared" si="13"/>
         <v>799</v>
@@ -29866,8 +30348,11 @@
       <c r="M800" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="801" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N800" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="801" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="1">
         <f t="shared" si="13"/>
         <v>800</v>
@@ -29902,8 +30387,11 @@
       <c r="M801" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="802" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N801" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="802" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="1">
         <f t="shared" si="13"/>
         <v>801</v>
@@ -29938,8 +30426,11 @@
       <c r="M802" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="803" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N802" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="803" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="1">
         <f t="shared" si="13"/>
         <v>802</v>
@@ -29974,8 +30465,11 @@
       <c r="M803" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="804" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N803" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="804" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="1">
         <f t="shared" si="13"/>
         <v>803</v>
@@ -30010,8 +30504,11 @@
       <c r="M804" s="22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="805" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N804" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="805" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="1">
         <f t="shared" si="13"/>
         <v>804</v>
@@ -30046,8 +30543,11 @@
       <c r="M805" s="22" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="806" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N805" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="806" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="1">
         <f t="shared" si="13"/>
         <v>805</v>
@@ -30082,8 +30582,11 @@
       <c r="M806" s="22" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="807" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N806" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="807" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="1">
         <f t="shared" si="13"/>
         <v>806</v>
@@ -30118,8 +30621,11 @@
       <c r="M807" s="22" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="808" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N807" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="808" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="1">
         <f t="shared" si="13"/>
         <v>807</v>
@@ -30154,8 +30660,11 @@
       <c r="M808" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="809" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N808" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="809" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="1">
         <f t="shared" si="13"/>
         <v>808</v>
@@ -30190,8 +30699,11 @@
       <c r="M809" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="810" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N809" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="810" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="1">
         <f t="shared" si="13"/>
         <v>809</v>
@@ -30226,8 +30738,11 @@
       <c r="M810" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="811" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N810" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="811" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="1">
         <f t="shared" si="13"/>
         <v>810</v>
@@ -30262,8 +30777,11 @@
       <c r="M811" s="23" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="812" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N811" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="812" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="1">
         <f t="shared" si="13"/>
         <v>811</v>
@@ -30304,8 +30822,11 @@
       <c r="M812" s="22" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="813" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N812" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="813" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
         <f t="shared" si="13"/>
         <v>812</v>
@@ -30340,8 +30861,11 @@
       <c r="M813" s="22" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="814" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N813" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="814" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="1">
         <f t="shared" si="13"/>
         <v>813</v>
@@ -30376,8 +30900,11 @@
       <c r="M814" s="22" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="815" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N814" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="815" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="1">
         <f t="shared" si="13"/>
         <v>814</v>
@@ -30412,8 +30939,11 @@
       <c r="M815" s="20" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="816" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N815" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="816" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="1">
         <f t="shared" si="13"/>
         <v>815</v>
@@ -30448,8 +30978,11 @@
       <c r="M816" s="12" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="817" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N816" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="817" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="1">
         <f t="shared" si="13"/>
         <v>816</v>
@@ -30484,8 +31017,11 @@
       <c r="M817" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="818" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N817" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="818" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
         <f t="shared" si="13"/>
         <v>817</v>
@@ -30520,8 +31056,11 @@
       <c r="M818" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="819" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N818" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="819" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="1">
         <f t="shared" si="13"/>
         <v>818</v>
@@ -30556,8 +31095,11 @@
       <c r="M819" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="820" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N819" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="820" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
         <f t="shared" si="13"/>
         <v>819</v>
@@ -30592,8 +31134,11 @@
       <c r="M820" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="821" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N820" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="821" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
         <f t="shared" si="13"/>
         <v>820</v>
@@ -30634,8 +31179,11 @@
       <c r="M821" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="822" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N821" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="822" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
         <f t="shared" si="13"/>
         <v>821</v>
@@ -30670,8 +31218,11 @@
       <c r="M822" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="823" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N822" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="823" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
         <f t="shared" si="13"/>
         <v>822</v>
@@ -30706,8 +31257,11 @@
       <c r="M823" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="824" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N823" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="824" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
         <f t="shared" si="13"/>
         <v>823</v>
@@ -30742,8 +31296,11 @@
       <c r="M824" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="825" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N824" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="825" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
         <f t="shared" si="13"/>
         <v>824</v>
@@ -30778,8 +31335,11 @@
       <c r="M825" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="826" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N825" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="826" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
         <f t="shared" si="13"/>
         <v>825</v>
@@ -30814,8 +31374,11 @@
       <c r="M826" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="827" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N826" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="827" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
         <f t="shared" ref="A827:A862" si="14">ROW()-1</f>
         <v>826</v>
@@ -30850,8 +31413,11 @@
       <c r="M827" s="12" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="828" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N827" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="828" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
         <f t="shared" si="14"/>
         <v>827</v>
@@ -30886,8 +31452,11 @@
       <c r="M828" s="20" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="829" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N828" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="829" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="1">
         <f t="shared" si="14"/>
         <v>828</v>
@@ -30922,8 +31491,11 @@
       <c r="M829" s="12" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="830" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N829" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="830" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="1">
         <f t="shared" si="14"/>
         <v>829</v>
@@ -30961,8 +31533,11 @@
       <c r="L830" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="831" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N830" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="831" spans="1:14" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="14">
         <f t="shared" si="14"/>
         <v>830</v>
@@ -31000,8 +31575,11 @@
       <c r="L831" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="832" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N831" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="832" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="1">
         <f t="shared" si="14"/>
         <v>831</v>

--- a/專案計畫人員保費查詢.xlsx
+++ b/專案計畫人員保費查詢.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.　保險相關\保險\健、勞保、勞退\專案計畫人員保費查詢系統\專案計畫人員保費查詢系統_v10.2_修正版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE8A1B7-A76C-49B5-BB3D-026CBBCECA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559A5455-F1AE-45A4-ABAE-720C3A6D3C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,8 +633,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>是</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Y</t>
   </si>
 </sst>
 </file>
